--- a/tests/integration/test_data/mappings_attributions_for_tests.xlsx
+++ b/tests/integration/test_data/mappings_attributions_for_tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/amendements-intelligents/tests/integration/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204FC208-8424-CC45-8F6D-FC0A17E4012A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096F565F-BAF3-7B4C-9A53-CB843C0AF657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{5BF04301-CB7D-4341-BBF7-1B79619915A7}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{5BF04301-CB7D-4341-BBF7-1B79619915A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Code et Article" sheetId="2" r:id="rId1"/>

--- a/tests/integration/test_data/mappings_attributions_for_tests.xlsx
+++ b/tests/integration/test_data/mappings_attributions_for_tests.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/amendements-intelligents/tests/integration/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF11C3D1-8888-E745-B592-BB227C76785B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0676A3-88E4-404B-AD70-DD89B63BDB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Code et Article" sheetId="1" r:id="rId1"/>
     <sheet name="Mots clés" sheetId="2" r:id="rId2"/>
     <sheet name="Prénom Nom Mail" sheetId="3" r:id="rId3"/>
-    <sheet name="Attribution par défault" sheetId="4" r:id="rId4"/>
+    <sheet name="Attribution par défaut" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Code et Article'!$E$1:$E$773</definedName>

--- a/tests/integration/test_data/mappings_attributions_for_tests.xlsx
+++ b/tests/integration/test_data/mappings_attributions_for_tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/amendements-intelligents/tests/integration/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0676A3-88E4-404B-AD70-DD89B63BDB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53208F71-1C9F-E14E-B237-6395DFC473EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="68800" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Code et Article" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="73">
   <si>
     <t>Bureau</t>
   </si>
@@ -195,9 +195,6 @@
     <t>Mots clés</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>cotisations de l'employeur</t>
   </si>
   <si>
@@ -242,6 +239,18 @@
   <si>
     <t>121-2-1</t>
   </si>
+  <si>
+    <t>montant M</t>
+  </si>
+  <si>
+    <t>jmm@sante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Jean-Michel Montant</t>
+  </si>
+  <si>
+    <t>montant Z</t>
+  </si>
 </sst>
 </file>
 
@@ -251,7 +260,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="165" formatCode="yyyy\-m"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -273,6 +282,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -283,6 +293,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -295,21 +306,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Docs-Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -331,6 +334,26 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -358,10 +381,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -388,49 +412,49 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -851,8 +875,8 @@
       <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>69</v>
+      <c r="C11" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>7</v>
@@ -2067,5041 +2091,5037 @@
   <dimension ref="A1:D1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="40.1640625" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" customWidth="1"/>
-    <col min="3" max="3" width="39.1640625" customWidth="1"/>
-    <col min="4" max="26" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="39.1640625" style="23" customWidth="1"/>
+    <col min="4" max="26" width="8.83203125" style="23" customWidth="1"/>
+    <col min="27" max="16384" width="11.1640625" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="22"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A2" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="15" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="13" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A3" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="11"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A4" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="15" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="14" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="19"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="24"/>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="19"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="20"/>
+      <c r="A7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A8" s="19"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A10" s="19"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A11" s="19"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A12" s="19"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A13" s="19"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="21"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="22"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="19"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="19"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="19"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="19"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="19"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="19"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="19"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="19"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="19"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="19"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="19"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="19"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A37" s="19"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A38" s="19"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A39" s="19"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A40" s="19"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
+      <c r="A40" s="13"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="A41" s="13"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
     </row>
     <row r="42" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A42" s="19"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
     </row>
     <row r="43" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A43" s="19"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
+      <c r="A43" s="13"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A44" s="19"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
+      <c r="A44" s="13"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A45" s="19"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
+      <c r="A45" s="13"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A46" s="19"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="A46" s="13"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A47" s="19"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
+      <c r="A47" s="13"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A48" s="19"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
+      <c r="A48" s="13"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A49" s="19"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A50" s="19"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A51" s="19"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A52" s="19"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A53" s="19"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="A53" s="13"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A54" s="19"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
+      <c r="A54" s="13"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A55" s="19"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
+      <c r="A55" s="13"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A56" s="19"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
+      <c r="A56" s="13"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A57" s="19"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A58" s="19"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
+      <c r="A58" s="13"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
     </row>
     <row r="59" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A59" s="19"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
+      <c r="A59" s="13"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
     </row>
     <row r="60" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A60" s="19"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
+      <c r="A60" s="13"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A61" s="19"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
+      <c r="A61" s="13"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
     </row>
     <row r="62" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A62" s="19"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
+      <c r="A62" s="13"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A63" s="19"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
+      <c r="A63" s="13"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A64" s="19"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
+      <c r="A64" s="13"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
     </row>
     <row r="65" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A65" s="19"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
+      <c r="A65" s="13"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
     </row>
     <row r="66" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A66" s="19"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
+      <c r="A66" s="13"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
     </row>
     <row r="67" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A67" s="19"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
+      <c r="A67" s="13"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
     </row>
     <row r="68" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A68" s="19"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
+      <c r="A68" s="13"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
     </row>
     <row r="69" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A69" s="19"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
+      <c r="A69" s="13"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
     </row>
     <row r="70" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A70" s="19"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
+      <c r="A70" s="13"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
     </row>
     <row r="71" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A71" s="19"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
+      <c r="A71" s="13"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
     </row>
     <row r="72" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A72" s="19"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
+      <c r="A72" s="13"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
     </row>
     <row r="73" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A73" s="19"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
+      <c r="A73" s="13"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
     </row>
     <row r="74" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A74" s="19"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
+      <c r="A74" s="13"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
     </row>
     <row r="75" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A75" s="19"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
+      <c r="A75" s="13"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
     </row>
     <row r="76" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A76" s="19"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
+      <c r="A76" s="13"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
     </row>
     <row r="77" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A77" s="19"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
+      <c r="A77" s="13"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
     </row>
     <row r="78" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A78" s="19"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
+      <c r="A78" s="13"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
     </row>
     <row r="79" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A79" s="19"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
+      <c r="A79" s="13"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
     </row>
     <row r="80" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A80" s="19"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
+      <c r="A80" s="13"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
     </row>
     <row r="81" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A81" s="19"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
+      <c r="A81" s="13"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
     </row>
     <row r="82" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A82" s="19"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
+      <c r="A82" s="13"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
     </row>
     <row r="83" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A83" s="19"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
+      <c r="A83" s="13"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
     </row>
     <row r="84" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A84" s="19"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
+      <c r="A84" s="13"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
     </row>
     <row r="85" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A85" s="19"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
+      <c r="A85" s="13"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
     </row>
     <row r="86" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A86" s="19"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
+      <c r="A86" s="13"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
     </row>
     <row r="87" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A87" s="19"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
+      <c r="A87" s="13"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
     </row>
     <row r="88" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A88" s="19"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
+      <c r="A88" s="13"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
     </row>
     <row r="89" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A89" s="19"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
+      <c r="A89" s="13"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
     </row>
     <row r="90" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A90" s="19"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
+      <c r="A90" s="13"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
     </row>
     <row r="91" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A91" s="19"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
+      <c r="A91" s="13"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
     </row>
     <row r="92" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A92" s="19"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
+      <c r="A92" s="13"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
     </row>
     <row r="93" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A93" s="19"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
+      <c r="A93" s="13"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
     </row>
     <row r="94" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A94" s="19"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
+      <c r="A94" s="13"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
     </row>
     <row r="95" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A95" s="19"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
+      <c r="A95" s="13"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
     </row>
     <row r="96" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A96" s="19"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
+      <c r="A96" s="13"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
     </row>
     <row r="97" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A97" s="19"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
+      <c r="A97" s="13"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
     </row>
     <row r="98" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A98" s="19"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="17"/>
+      <c r="A98" s="13"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
     </row>
     <row r="99" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A99" s="19"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="17"/>
+      <c r="A99" s="13"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
     </row>
     <row r="100" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A100" s="19"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="17"/>
+      <c r="A100" s="13"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
     </row>
     <row r="101" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A101" s="19"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="17"/>
+      <c r="A101" s="13"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
     </row>
     <row r="102" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A102" s="19"/>
-      <c r="B102" s="17"/>
-      <c r="C102" s="17"/>
+      <c r="A102" s="13"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
     </row>
     <row r="103" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A103" s="19"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="17"/>
+      <c r="A103" s="13"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
     </row>
     <row r="104" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A104" s="19"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="17"/>
+      <c r="A104" s="13"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
     </row>
     <row r="105" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A105" s="19"/>
-      <c r="B105" s="17"/>
-      <c r="C105" s="17"/>
+      <c r="A105" s="13"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
     </row>
     <row r="106" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A106" s="19"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="17"/>
+      <c r="A106" s="13"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
     </row>
     <row r="107" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A107" s="19"/>
-      <c r="B107" s="17"/>
-      <c r="C107" s="17"/>
+      <c r="A107" s="13"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
     </row>
     <row r="108" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A108" s="19"/>
-      <c r="B108" s="17"/>
-      <c r="C108" s="17"/>
+      <c r="A108" s="13"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
     </row>
     <row r="109" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A109" s="19"/>
-      <c r="B109" s="17"/>
-      <c r="C109" s="17"/>
+      <c r="A109" s="13"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
     </row>
     <row r="110" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A110" s="19"/>
-      <c r="B110" s="17"/>
-      <c r="C110" s="17"/>
+      <c r="A110" s="13"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
     </row>
     <row r="111" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A111" s="19"/>
-      <c r="B111" s="17"/>
-      <c r="C111" s="17"/>
+      <c r="A111" s="13"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
     </row>
     <row r="112" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A112" s="19"/>
-      <c r="B112" s="17"/>
-      <c r="C112" s="17"/>
+      <c r="A112" s="13"/>
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
     </row>
     <row r="113" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A113" s="19"/>
-      <c r="B113" s="17"/>
-      <c r="C113" s="17"/>
+      <c r="A113" s="13"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
     </row>
     <row r="114" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A114" s="19"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="17"/>
+      <c r="A114" s="13"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
     </row>
     <row r="115" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A115" s="19"/>
-      <c r="B115" s="17"/>
-      <c r="C115" s="17"/>
+      <c r="A115" s="13"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
     </row>
     <row r="116" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A116" s="19"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
+      <c r="A116" s="13"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="11"/>
     </row>
     <row r="117" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A117" s="19"/>
-      <c r="B117" s="17"/>
-      <c r="C117" s="17"/>
+      <c r="A117" s="13"/>
+      <c r="B117" s="11"/>
+      <c r="C117" s="11"/>
     </row>
     <row r="118" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A118" s="19"/>
-      <c r="B118" s="17"/>
-      <c r="C118" s="17"/>
+      <c r="A118" s="13"/>
+      <c r="B118" s="11"/>
+      <c r="C118" s="11"/>
     </row>
     <row r="119" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A119" s="19"/>
-      <c r="B119" s="17"/>
-      <c r="C119" s="17"/>
+      <c r="A119" s="13"/>
+      <c r="B119" s="11"/>
+      <c r="C119" s="11"/>
     </row>
     <row r="120" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A120" s="19"/>
-      <c r="B120" s="17"/>
-      <c r="C120" s="17"/>
+      <c r="A120" s="13"/>
+      <c r="B120" s="11"/>
+      <c r="C120" s="11"/>
     </row>
     <row r="121" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A121" s="19"/>
-      <c r="B121" s="17"/>
-      <c r="C121" s="17"/>
+      <c r="A121" s="13"/>
+      <c r="B121" s="11"/>
+      <c r="C121" s="11"/>
     </row>
     <row r="122" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A122" s="19"/>
-      <c r="B122" s="17"/>
-      <c r="C122" s="17"/>
+      <c r="A122" s="13"/>
+      <c r="B122" s="11"/>
+      <c r="C122" s="11"/>
     </row>
     <row r="123" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A123" s="19"/>
-      <c r="B123" s="17"/>
-      <c r="C123" s="17"/>
+      <c r="A123" s="13"/>
+      <c r="B123" s="11"/>
+      <c r="C123" s="11"/>
     </row>
     <row r="124" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A124" s="19"/>
-      <c r="B124" s="17"/>
-      <c r="C124" s="17"/>
+      <c r="A124" s="13"/>
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
     </row>
     <row r="125" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A125" s="19"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="17"/>
+      <c r="A125" s="13"/>
+      <c r="B125" s="11"/>
+      <c r="C125" s="11"/>
     </row>
     <row r="126" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A126" s="19"/>
-      <c r="B126" s="17"/>
-      <c r="C126" s="17"/>
+      <c r="A126" s="13"/>
+      <c r="B126" s="11"/>
+      <c r="C126" s="11"/>
     </row>
     <row r="127" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A127" s="19"/>
-      <c r="B127" s="17"/>
-      <c r="C127" s="17"/>
+      <c r="A127" s="13"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
     </row>
     <row r="128" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A128" s="19"/>
-      <c r="B128" s="17"/>
-      <c r="C128" s="17"/>
+      <c r="A128" s="13"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
     </row>
     <row r="129" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A129" s="19"/>
-      <c r="B129" s="17"/>
-      <c r="C129" s="17"/>
+      <c r="A129" s="13"/>
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
     </row>
     <row r="130" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A130" s="19"/>
-      <c r="B130" s="17"/>
-      <c r="C130" s="17"/>
+      <c r="A130" s="13"/>
+      <c r="B130" s="11"/>
+      <c r="C130" s="11"/>
     </row>
     <row r="131" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A131" s="19"/>
-      <c r="B131" s="17"/>
-      <c r="C131" s="17"/>
+      <c r="A131" s="13"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
     </row>
     <row r="132" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A132" s="19"/>
-      <c r="B132" s="17"/>
-      <c r="C132" s="17"/>
+      <c r="A132" s="13"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
     </row>
     <row r="133" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A133" s="19"/>
-      <c r="B133" s="17"/>
-      <c r="C133" s="17"/>
+      <c r="A133" s="13"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
     </row>
     <row r="134" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A134" s="19"/>
-      <c r="B134" s="17"/>
-      <c r="C134" s="17"/>
+      <c r="A134" s="13"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="11"/>
     </row>
     <row r="135" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A135" s="19"/>
-      <c r="B135" s="17"/>
-      <c r="C135" s="17"/>
+      <c r="A135" s="13"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="11"/>
     </row>
     <row r="136" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A136" s="19"/>
-      <c r="B136" s="17"/>
-      <c r="C136" s="17"/>
+      <c r="A136" s="13"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
     </row>
     <row r="137" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A137" s="19"/>
-      <c r="B137" s="17"/>
-      <c r="C137" s="17"/>
+      <c r="A137" s="13"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
     </row>
     <row r="138" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A138" s="19"/>
-      <c r="B138" s="17"/>
-      <c r="C138" s="17"/>
+      <c r="A138" s="13"/>
+      <c r="B138" s="11"/>
+      <c r="C138" s="11"/>
     </row>
     <row r="139" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A139" s="19"/>
-      <c r="B139" s="17"/>
-      <c r="C139" s="17"/>
+      <c r="A139" s="13"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
     </row>
     <row r="140" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A140" s="19"/>
-      <c r="B140" s="17"/>
-      <c r="C140" s="17"/>
+      <c r="A140" s="13"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="11"/>
     </row>
     <row r="141" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A141" s="19"/>
-      <c r="B141" s="17"/>
-      <c r="C141" s="17"/>
+      <c r="A141" s="13"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="11"/>
     </row>
     <row r="142" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A142" s="19"/>
-      <c r="B142" s="17"/>
-      <c r="C142" s="17"/>
+      <c r="A142" s="13"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
     </row>
     <row r="143" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A143" s="19"/>
-      <c r="B143" s="17"/>
-      <c r="C143" s="17"/>
+      <c r="A143" s="13"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
     </row>
     <row r="144" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A144" s="19"/>
-      <c r="B144" s="17"/>
-      <c r="C144" s="17"/>
+      <c r="A144" s="13"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="11"/>
     </row>
     <row r="145" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A145" s="19"/>
-      <c r="B145" s="17"/>
-      <c r="C145" s="17"/>
+      <c r="A145" s="13"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="11"/>
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A146" s="19"/>
-      <c r="B146" s="17"/>
-      <c r="C146" s="17"/>
+      <c r="A146" s="13"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A147" s="19"/>
-      <c r="B147" s="17"/>
-      <c r="C147" s="17"/>
+      <c r="A147" s="13"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
     </row>
     <row r="148" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A148" s="19"/>
-      <c r="B148" s="17"/>
-      <c r="C148" s="17"/>
+      <c r="A148" s="13"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
     </row>
     <row r="149" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A149" s="19"/>
-      <c r="B149" s="17"/>
-      <c r="C149" s="17"/>
+      <c r="A149" s="13"/>
+      <c r="B149" s="11"/>
+      <c r="C149" s="11"/>
     </row>
     <row r="150" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A150" s="19"/>
-      <c r="B150" s="17"/>
-      <c r="C150" s="17"/>
+      <c r="A150" s="13"/>
+      <c r="B150" s="11"/>
+      <c r="C150" s="11"/>
     </row>
     <row r="151" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A151" s="19"/>
-      <c r="B151" s="17"/>
-      <c r="C151" s="17"/>
+      <c r="A151" s="13"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="11"/>
     </row>
     <row r="152" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A152" s="19"/>
-      <c r="B152" s="17"/>
-      <c r="C152" s="17"/>
+      <c r="A152" s="13"/>
+      <c r="B152" s="11"/>
+      <c r="C152" s="11"/>
     </row>
     <row r="153" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A153" s="19"/>
-      <c r="B153" s="17"/>
-      <c r="C153" s="17"/>
+      <c r="A153" s="13"/>
+      <c r="B153" s="11"/>
+      <c r="C153" s="11"/>
     </row>
     <row r="154" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A154" s="19"/>
-      <c r="B154" s="17"/>
-      <c r="C154" s="17"/>
+      <c r="A154" s="13"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="11"/>
     </row>
     <row r="155" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A155" s="19"/>
-      <c r="B155" s="17"/>
-      <c r="C155" s="17"/>
+      <c r="A155" s="13"/>
+      <c r="B155" s="11"/>
+      <c r="C155" s="11"/>
     </row>
     <row r="156" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A156" s="19"/>
-      <c r="B156" s="17"/>
-      <c r="C156" s="17"/>
+      <c r="A156" s="13"/>
+      <c r="B156" s="11"/>
+      <c r="C156" s="11"/>
     </row>
     <row r="157" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A157" s="19"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="17"/>
+      <c r="A157" s="13"/>
+      <c r="B157" s="11"/>
+      <c r="C157" s="11"/>
     </row>
     <row r="158" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A158" s="19"/>
-      <c r="B158" s="17"/>
-      <c r="C158" s="17"/>
+      <c r="A158" s="13"/>
+      <c r="B158" s="11"/>
+      <c r="C158" s="11"/>
     </row>
     <row r="159" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A159" s="19"/>
-      <c r="B159" s="17"/>
-      <c r="C159" s="17"/>
+      <c r="A159" s="13"/>
+      <c r="B159" s="11"/>
+      <c r="C159" s="11"/>
     </row>
     <row r="160" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A160" s="19"/>
-      <c r="B160" s="17"/>
-      <c r="C160" s="17"/>
+      <c r="A160" s="13"/>
+      <c r="B160" s="11"/>
+      <c r="C160" s="11"/>
     </row>
     <row r="161" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A161" s="19"/>
-      <c r="B161" s="17"/>
-      <c r="C161" s="17"/>
+      <c r="A161" s="13"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="11"/>
     </row>
     <row r="162" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A162" s="19"/>
-      <c r="B162" s="17"/>
-      <c r="C162" s="17"/>
+      <c r="A162" s="13"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="11"/>
     </row>
     <row r="163" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A163" s="19"/>
-      <c r="B163" s="17"/>
-      <c r="C163" s="17"/>
+      <c r="A163" s="13"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="11"/>
     </row>
     <row r="164" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A164" s="19"/>
-      <c r="B164" s="17"/>
-      <c r="C164" s="17"/>
+      <c r="A164" s="13"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="11"/>
     </row>
     <row r="165" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A165" s="19"/>
-      <c r="B165" s="17"/>
-      <c r="C165" s="17"/>
+      <c r="A165" s="13"/>
+      <c r="B165" s="11"/>
+      <c r="C165" s="11"/>
     </row>
     <row r="166" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A166" s="19"/>
-      <c r="B166" s="17"/>
-      <c r="C166" s="17"/>
+      <c r="A166" s="13"/>
+      <c r="B166" s="11"/>
+      <c r="C166" s="11"/>
     </row>
     <row r="167" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A167" s="19"/>
-      <c r="B167" s="17"/>
-      <c r="C167" s="17"/>
+      <c r="A167" s="13"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="11"/>
     </row>
     <row r="168" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A168" s="19"/>
-      <c r="B168" s="17"/>
-      <c r="C168" s="17"/>
+      <c r="A168" s="13"/>
+      <c r="B168" s="11"/>
+      <c r="C168" s="11"/>
     </row>
     <row r="169" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A169" s="19"/>
-      <c r="B169" s="17"/>
-      <c r="C169" s="17"/>
+      <c r="A169" s="13"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="11"/>
     </row>
     <row r="170" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A170" s="19"/>
-      <c r="B170" s="17"/>
-      <c r="C170" s="17"/>
+      <c r="A170" s="13"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="11"/>
     </row>
     <row r="171" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A171" s="19"/>
-      <c r="B171" s="17"/>
-      <c r="C171" s="17"/>
+      <c r="A171" s="13"/>
+      <c r="B171" s="11"/>
+      <c r="C171" s="11"/>
     </row>
     <row r="172" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A172" s="19"/>
-      <c r="B172" s="17"/>
-      <c r="C172" s="17"/>
+      <c r="A172" s="13"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="11"/>
     </row>
     <row r="173" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A173" s="19"/>
-      <c r="B173" s="17"/>
-      <c r="C173" s="17"/>
+      <c r="A173" s="13"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="11"/>
     </row>
     <row r="174" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A174" s="19"/>
-      <c r="B174" s="17"/>
-      <c r="C174" s="17"/>
+      <c r="A174" s="13"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="11"/>
     </row>
     <row r="175" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A175" s="19"/>
-      <c r="B175" s="17"/>
-      <c r="C175" s="17"/>
+      <c r="A175" s="13"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="11"/>
     </row>
     <row r="176" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A176" s="19"/>
-      <c r="B176" s="17"/>
-      <c r="C176" s="17"/>
+      <c r="A176" s="13"/>
+      <c r="B176" s="11"/>
+      <c r="C176" s="11"/>
     </row>
     <row r="177" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A177" s="19"/>
-      <c r="B177" s="17"/>
-      <c r="C177" s="17"/>
+      <c r="A177" s="13"/>
+      <c r="B177" s="11"/>
+      <c r="C177" s="11"/>
     </row>
     <row r="178" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A178" s="19"/>
-      <c r="B178" s="17"/>
-      <c r="C178" s="17"/>
+      <c r="A178" s="13"/>
+      <c r="B178" s="11"/>
+      <c r="C178" s="11"/>
     </row>
     <row r="179" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A179" s="19"/>
-      <c r="B179" s="17"/>
-      <c r="C179" s="17"/>
+      <c r="A179" s="13"/>
+      <c r="B179" s="11"/>
+      <c r="C179" s="11"/>
     </row>
     <row r="180" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A180" s="19"/>
-      <c r="B180" s="17"/>
-      <c r="C180" s="17"/>
+      <c r="A180" s="13"/>
+      <c r="B180" s="11"/>
+      <c r="C180" s="11"/>
     </row>
     <row r="181" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A181" s="19"/>
-      <c r="B181" s="17"/>
-      <c r="C181" s="17"/>
+      <c r="A181" s="13"/>
+      <c r="B181" s="11"/>
+      <c r="C181" s="11"/>
     </row>
     <row r="182" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A182" s="19"/>
-      <c r="B182" s="17"/>
-      <c r="C182" s="17"/>
+      <c r="A182" s="13"/>
+      <c r="B182" s="11"/>
+      <c r="C182" s="11"/>
     </row>
     <row r="183" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A183" s="19"/>
-      <c r="B183" s="17"/>
-      <c r="C183" s="17"/>
+      <c r="A183" s="13"/>
+      <c r="B183" s="11"/>
+      <c r="C183" s="11"/>
     </row>
     <row r="184" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A184" s="19"/>
-      <c r="B184" s="17"/>
-      <c r="C184" s="17"/>
+      <c r="A184" s="13"/>
+      <c r="B184" s="11"/>
+      <c r="C184" s="11"/>
     </row>
     <row r="185" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A185" s="19"/>
-      <c r="B185" s="17"/>
-      <c r="C185" s="17"/>
+      <c r="A185" s="13"/>
+      <c r="B185" s="11"/>
+      <c r="C185" s="11"/>
     </row>
     <row r="186" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A186" s="19"/>
-      <c r="B186" s="17"/>
-      <c r="C186" s="17"/>
+      <c r="A186" s="13"/>
+      <c r="B186" s="11"/>
+      <c r="C186" s="11"/>
     </row>
     <row r="187" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A187" s="19"/>
-      <c r="B187" s="17"/>
-      <c r="C187" s="17"/>
+      <c r="A187" s="13"/>
+      <c r="B187" s="11"/>
+      <c r="C187" s="11"/>
     </row>
     <row r="188" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A188" s="19"/>
-      <c r="B188" s="17"/>
-      <c r="C188" s="17"/>
+      <c r="A188" s="13"/>
+      <c r="B188" s="11"/>
+      <c r="C188" s="11"/>
     </row>
     <row r="189" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A189" s="19"/>
-      <c r="B189" s="17"/>
-      <c r="C189" s="17"/>
+      <c r="A189" s="13"/>
+      <c r="B189" s="11"/>
+      <c r="C189" s="11"/>
     </row>
     <row r="190" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A190" s="19"/>
-      <c r="B190" s="17"/>
-      <c r="C190" s="17"/>
+      <c r="A190" s="13"/>
+      <c r="B190" s="11"/>
+      <c r="C190" s="11"/>
     </row>
     <row r="191" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A191" s="19"/>
-      <c r="B191" s="17"/>
-      <c r="C191" s="17"/>
+      <c r="A191" s="13"/>
+      <c r="B191" s="11"/>
+      <c r="C191" s="11"/>
     </row>
     <row r="192" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A192" s="19"/>
-      <c r="B192" s="17"/>
-      <c r="C192" s="17"/>
+      <c r="A192" s="13"/>
+      <c r="B192" s="11"/>
+      <c r="C192" s="11"/>
     </row>
     <row r="193" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A193" s="19"/>
-      <c r="B193" s="17"/>
-      <c r="C193" s="17"/>
+      <c r="A193" s="13"/>
+      <c r="B193" s="11"/>
+      <c r="C193" s="11"/>
     </row>
     <row r="194" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A194" s="19"/>
-      <c r="B194" s="17"/>
-      <c r="C194" s="17"/>
+      <c r="A194" s="13"/>
+      <c r="B194" s="11"/>
+      <c r="C194" s="11"/>
     </row>
     <row r="195" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A195" s="19"/>
-      <c r="B195" s="17"/>
-      <c r="C195" s="17"/>
+      <c r="A195" s="13"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="11"/>
     </row>
     <row r="196" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A196" s="19"/>
-      <c r="B196" s="17"/>
-      <c r="C196" s="17"/>
+      <c r="A196" s="13"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="11"/>
     </row>
     <row r="197" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A197" s="19"/>
-      <c r="B197" s="17"/>
-      <c r="C197" s="17"/>
+      <c r="A197" s="13"/>
+      <c r="B197" s="11"/>
+      <c r="C197" s="11"/>
     </row>
     <row r="198" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A198" s="19"/>
-      <c r="B198" s="17"/>
-      <c r="C198" s="17"/>
+      <c r="A198" s="13"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="11"/>
     </row>
     <row r="199" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A199" s="19"/>
-      <c r="B199" s="17"/>
-      <c r="C199" s="17"/>
+      <c r="A199" s="13"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="11"/>
     </row>
     <row r="200" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A200" s="19"/>
-      <c r="B200" s="17"/>
-      <c r="C200" s="17"/>
+      <c r="A200" s="13"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="11"/>
     </row>
     <row r="201" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A201" s="19"/>
-      <c r="B201" s="17"/>
-      <c r="C201" s="17"/>
+      <c r="A201" s="13"/>
+      <c r="B201" s="11"/>
+      <c r="C201" s="11"/>
     </row>
     <row r="202" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A202" s="19"/>
-      <c r="B202" s="17"/>
-      <c r="C202" s="17"/>
+      <c r="A202" s="13"/>
+      <c r="B202" s="11"/>
+      <c r="C202" s="11"/>
     </row>
     <row r="203" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A203" s="19"/>
-      <c r="B203" s="17"/>
-      <c r="C203" s="17"/>
+      <c r="A203" s="13"/>
+      <c r="B203" s="11"/>
+      <c r="C203" s="11"/>
     </row>
     <row r="204" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A204" s="19"/>
-      <c r="B204" s="17"/>
-      <c r="C204" s="17"/>
+      <c r="A204" s="13"/>
+      <c r="B204" s="11"/>
+      <c r="C204" s="11"/>
     </row>
     <row r="205" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A205" s="19"/>
-      <c r="B205" s="17"/>
-      <c r="C205" s="17"/>
+      <c r="A205" s="13"/>
+      <c r="B205" s="11"/>
+      <c r="C205" s="11"/>
     </row>
     <row r="206" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A206" s="19"/>
-      <c r="B206" s="17"/>
-      <c r="C206" s="17"/>
+      <c r="A206" s="13"/>
+      <c r="B206" s="11"/>
+      <c r="C206" s="11"/>
     </row>
     <row r="207" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A207" s="19"/>
-      <c r="B207" s="17"/>
-      <c r="C207" s="17"/>
+      <c r="A207" s="13"/>
+      <c r="B207" s="11"/>
+      <c r="C207" s="11"/>
     </row>
     <row r="208" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A208" s="19"/>
-      <c r="B208" s="17"/>
-      <c r="C208" s="17"/>
+      <c r="A208" s="13"/>
+      <c r="B208" s="11"/>
+      <c r="C208" s="11"/>
     </row>
     <row r="209" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A209" s="19"/>
-      <c r="B209" s="17"/>
-      <c r="C209" s="17"/>
+      <c r="A209" s="13"/>
+      <c r="B209" s="11"/>
+      <c r="C209" s="11"/>
     </row>
     <row r="210" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A210" s="19"/>
-      <c r="B210" s="17"/>
-      <c r="C210" s="17"/>
+      <c r="A210" s="13"/>
+      <c r="B210" s="11"/>
+      <c r="C210" s="11"/>
     </row>
     <row r="211" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A211" s="19"/>
-      <c r="B211" s="17"/>
-      <c r="C211" s="17"/>
+      <c r="A211" s="13"/>
+      <c r="B211" s="11"/>
+      <c r="C211" s="11"/>
     </row>
     <row r="212" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A212" s="19"/>
-      <c r="B212" s="17"/>
-      <c r="C212" s="17"/>
+      <c r="A212" s="13"/>
+      <c r="B212" s="11"/>
+      <c r="C212" s="11"/>
     </row>
     <row r="213" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A213" s="19"/>
-      <c r="B213" s="17"/>
-      <c r="C213" s="17"/>
+      <c r="A213" s="13"/>
+      <c r="B213" s="11"/>
+      <c r="C213" s="11"/>
     </row>
     <row r="214" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A214" s="19"/>
-      <c r="B214" s="17"/>
-      <c r="C214" s="17"/>
+      <c r="A214" s="13"/>
+      <c r="B214" s="11"/>
+      <c r="C214" s="11"/>
     </row>
     <row r="215" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A215" s="19"/>
-      <c r="B215" s="17"/>
-      <c r="C215" s="17"/>
+      <c r="A215" s="13"/>
+      <c r="B215" s="11"/>
+      <c r="C215" s="11"/>
     </row>
     <row r="216" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A216" s="19"/>
-      <c r="B216" s="17"/>
-      <c r="C216" s="17"/>
+      <c r="A216" s="13"/>
+      <c r="B216" s="11"/>
+      <c r="C216" s="11"/>
     </row>
     <row r="217" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A217" s="19"/>
-      <c r="B217" s="17"/>
-      <c r="C217" s="17"/>
+      <c r="A217" s="13"/>
+      <c r="B217" s="11"/>
+      <c r="C217" s="11"/>
     </row>
     <row r="218" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A218" s="19"/>
-      <c r="B218" s="17"/>
-      <c r="C218" s="17"/>
+      <c r="A218" s="13"/>
+      <c r="B218" s="11"/>
+      <c r="C218" s="11"/>
     </row>
     <row r="219" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A219" s="19"/>
-      <c r="B219" s="17"/>
-      <c r="C219" s="17"/>
+      <c r="A219" s="13"/>
+      <c r="B219" s="11"/>
+      <c r="C219" s="11"/>
     </row>
     <row r="220" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A220" s="19"/>
-      <c r="B220" s="17"/>
-      <c r="C220" s="17"/>
+      <c r="A220" s="13"/>
+      <c r="B220" s="11"/>
+      <c r="C220" s="11"/>
     </row>
     <row r="221" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A221" s="19"/>
-      <c r="B221" s="17"/>
-      <c r="C221" s="17"/>
+      <c r="A221" s="13"/>
+      <c r="B221" s="11"/>
+      <c r="C221" s="11"/>
     </row>
     <row r="222" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A222" s="19"/>
-      <c r="B222" s="17"/>
-      <c r="C222" s="17"/>
+      <c r="A222" s="13"/>
+      <c r="B222" s="11"/>
+      <c r="C222" s="11"/>
     </row>
     <row r="223" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A223" s="19"/>
-      <c r="B223" s="17"/>
-      <c r="C223" s="17"/>
+      <c r="A223" s="13"/>
+      <c r="B223" s="11"/>
+      <c r="C223" s="11"/>
     </row>
     <row r="224" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A224" s="19"/>
-      <c r="B224" s="17"/>
-      <c r="C224" s="17"/>
+      <c r="A224" s="13"/>
+      <c r="B224" s="11"/>
+      <c r="C224" s="11"/>
     </row>
     <row r="225" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A225" s="19"/>
-      <c r="B225" s="17"/>
-      <c r="C225" s="17"/>
+      <c r="A225" s="13"/>
+      <c r="B225" s="11"/>
+      <c r="C225" s="11"/>
     </row>
     <row r="226" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A226" s="19"/>
-      <c r="B226" s="17"/>
-      <c r="C226" s="17"/>
+      <c r="A226" s="13"/>
+      <c r="B226" s="11"/>
+      <c r="C226" s="11"/>
     </row>
     <row r="227" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A227" s="19"/>
-      <c r="B227" s="17"/>
-      <c r="C227" s="17"/>
+      <c r="A227" s="13"/>
+      <c r="B227" s="11"/>
+      <c r="C227" s="11"/>
     </row>
     <row r="228" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A228" s="19"/>
-      <c r="B228" s="17"/>
-      <c r="C228" s="17"/>
+      <c r="A228" s="13"/>
+      <c r="B228" s="11"/>
+      <c r="C228" s="11"/>
     </row>
     <row r="229" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A229" s="19"/>
-      <c r="B229" s="17"/>
-      <c r="C229" s="17"/>
+      <c r="A229" s="13"/>
+      <c r="B229" s="11"/>
+      <c r="C229" s="11"/>
     </row>
     <row r="230" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A230" s="19"/>
-      <c r="B230" s="17"/>
-      <c r="C230" s="17"/>
+      <c r="A230" s="13"/>
+      <c r="B230" s="11"/>
+      <c r="C230" s="11"/>
     </row>
     <row r="231" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A231" s="19"/>
-      <c r="B231" s="17"/>
-      <c r="C231" s="17"/>
+      <c r="A231" s="13"/>
+      <c r="B231" s="11"/>
+      <c r="C231" s="11"/>
     </row>
     <row r="232" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A232" s="19"/>
-      <c r="B232" s="17"/>
-      <c r="C232" s="17"/>
+      <c r="A232" s="13"/>
+      <c r="B232" s="11"/>
+      <c r="C232" s="11"/>
     </row>
     <row r="233" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A233" s="19"/>
-      <c r="B233" s="17"/>
-      <c r="C233" s="17"/>
+      <c r="A233" s="13"/>
+      <c r="B233" s="11"/>
+      <c r="C233" s="11"/>
     </row>
     <row r="234" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A234" s="19"/>
-      <c r="B234" s="17"/>
-      <c r="C234" s="17"/>
+      <c r="A234" s="13"/>
+      <c r="B234" s="11"/>
+      <c r="C234" s="11"/>
     </row>
     <row r="235" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A235" s="19"/>
-      <c r="B235" s="17"/>
-      <c r="C235" s="17"/>
+      <c r="A235" s="13"/>
+      <c r="B235" s="11"/>
+      <c r="C235" s="11"/>
     </row>
     <row r="236" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A236" s="19"/>
-      <c r="B236" s="17"/>
-      <c r="C236" s="17"/>
+      <c r="A236" s="13"/>
+      <c r="B236" s="11"/>
+      <c r="C236" s="11"/>
     </row>
     <row r="237" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A237" s="19"/>
-      <c r="B237" s="17"/>
-      <c r="C237" s="17"/>
+      <c r="A237" s="13"/>
+      <c r="B237" s="11"/>
+      <c r="C237" s="11"/>
     </row>
     <row r="238" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A238" s="19"/>
-      <c r="B238" s="17"/>
-      <c r="C238" s="17"/>
+      <c r="A238" s="13"/>
+      <c r="B238" s="11"/>
+      <c r="C238" s="11"/>
     </row>
     <row r="239" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A239" s="19"/>
-      <c r="B239" s="17"/>
-      <c r="C239" s="17"/>
+      <c r="A239" s="13"/>
+      <c r="B239" s="11"/>
+      <c r="C239" s="11"/>
     </row>
     <row r="240" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A240" s="19"/>
-      <c r="B240" s="17"/>
-      <c r="C240" s="17"/>
+      <c r="A240" s="13"/>
+      <c r="B240" s="11"/>
+      <c r="C240" s="11"/>
     </row>
     <row r="241" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A241" s="19"/>
-      <c r="B241" s="17"/>
-      <c r="C241" s="17"/>
+      <c r="A241" s="13"/>
+      <c r="B241" s="11"/>
+      <c r="C241" s="11"/>
     </row>
     <row r="242" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A242" s="19"/>
-      <c r="B242" s="17"/>
-      <c r="C242" s="17"/>
+      <c r="A242" s="13"/>
+      <c r="B242" s="11"/>
+      <c r="C242" s="11"/>
     </row>
     <row r="243" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A243" s="19"/>
-      <c r="B243" s="17"/>
-      <c r="C243" s="17"/>
+      <c r="A243" s="13"/>
+      <c r="B243" s="11"/>
+      <c r="C243" s="11"/>
     </row>
     <row r="244" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A244" s="19"/>
-      <c r="B244" s="17"/>
-      <c r="C244" s="17"/>
+      <c r="A244" s="13"/>
+      <c r="B244" s="11"/>
+      <c r="C244" s="11"/>
     </row>
     <row r="245" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A245" s="19"/>
-      <c r="B245" s="17"/>
-      <c r="C245" s="17"/>
+      <c r="A245" s="13"/>
+      <c r="B245" s="11"/>
+      <c r="C245" s="11"/>
     </row>
     <row r="246" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A246" s="19"/>
-      <c r="B246" s="17"/>
-      <c r="C246" s="17"/>
+      <c r="A246" s="13"/>
+      <c r="B246" s="11"/>
+      <c r="C246" s="11"/>
     </row>
     <row r="247" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A247" s="19"/>
-      <c r="B247" s="17"/>
-      <c r="C247" s="17"/>
+      <c r="A247" s="13"/>
+      <c r="B247" s="11"/>
+      <c r="C247" s="11"/>
     </row>
     <row r="248" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A248" s="19"/>
-      <c r="B248" s="17"/>
-      <c r="C248" s="17"/>
+      <c r="A248" s="13"/>
+      <c r="B248" s="11"/>
+      <c r="C248" s="11"/>
     </row>
     <row r="249" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A249" s="19"/>
-      <c r="B249" s="17"/>
-      <c r="C249" s="17"/>
+      <c r="A249" s="13"/>
+      <c r="B249" s="11"/>
+      <c r="C249" s="11"/>
     </row>
     <row r="250" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A250" s="19"/>
-      <c r="B250" s="17"/>
-      <c r="C250" s="17"/>
+      <c r="A250" s="13"/>
+      <c r="B250" s="11"/>
+      <c r="C250" s="11"/>
     </row>
     <row r="251" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A251" s="19"/>
-      <c r="B251" s="17"/>
-      <c r="C251" s="17"/>
+      <c r="A251" s="13"/>
+      <c r="B251" s="11"/>
+      <c r="C251" s="11"/>
     </row>
     <row r="252" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A252" s="19"/>
-      <c r="B252" s="17"/>
-      <c r="C252" s="17"/>
+      <c r="A252" s="13"/>
+      <c r="B252" s="11"/>
+      <c r="C252" s="11"/>
     </row>
     <row r="253" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A253" s="19"/>
-      <c r="B253" s="17"/>
-      <c r="C253" s="17"/>
+      <c r="A253" s="13"/>
+      <c r="B253" s="11"/>
+      <c r="C253" s="11"/>
     </row>
     <row r="254" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A254" s="19"/>
-      <c r="B254" s="17"/>
-      <c r="C254" s="17"/>
+      <c r="A254" s="13"/>
+      <c r="B254" s="11"/>
+      <c r="C254" s="11"/>
     </row>
     <row r="255" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A255" s="19"/>
-      <c r="B255" s="17"/>
-      <c r="C255" s="17"/>
+      <c r="A255" s="13"/>
+      <c r="B255" s="11"/>
+      <c r="C255" s="11"/>
     </row>
     <row r="256" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A256" s="19"/>
-      <c r="B256" s="17"/>
-      <c r="C256" s="17"/>
+      <c r="A256" s="13"/>
+      <c r="B256" s="11"/>
+      <c r="C256" s="11"/>
     </row>
     <row r="257" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A257" s="19"/>
-      <c r="B257" s="17"/>
-      <c r="C257" s="17"/>
+      <c r="A257" s="13"/>
+      <c r="B257" s="11"/>
+      <c r="C257" s="11"/>
     </row>
     <row r="258" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A258" s="19"/>
-      <c r="B258" s="17"/>
-      <c r="C258" s="17"/>
+      <c r="A258" s="13"/>
+      <c r="B258" s="11"/>
+      <c r="C258" s="11"/>
     </row>
     <row r="259" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A259" s="19"/>
-      <c r="B259" s="17"/>
-      <c r="C259" s="17"/>
+      <c r="A259" s="13"/>
+      <c r="B259" s="11"/>
+      <c r="C259" s="11"/>
     </row>
     <row r="260" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A260" s="19"/>
-      <c r="B260" s="17"/>
-      <c r="C260" s="17"/>
+      <c r="A260" s="13"/>
+      <c r="B260" s="11"/>
+      <c r="C260" s="11"/>
     </row>
     <row r="261" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A261" s="19"/>
-      <c r="B261" s="17"/>
-      <c r="C261" s="17"/>
+      <c r="A261" s="13"/>
+      <c r="B261" s="11"/>
+      <c r="C261" s="11"/>
     </row>
     <row r="262" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A262" s="19"/>
-      <c r="B262" s="17"/>
-      <c r="C262" s="17"/>
+      <c r="A262" s="13"/>
+      <c r="B262" s="11"/>
+      <c r="C262" s="11"/>
     </row>
     <row r="263" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A263" s="19"/>
-      <c r="B263" s="17"/>
-      <c r="C263" s="17"/>
+      <c r="A263" s="13"/>
+      <c r="B263" s="11"/>
+      <c r="C263" s="11"/>
     </row>
     <row r="264" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A264" s="19"/>
-      <c r="B264" s="17"/>
-      <c r="C264" s="17"/>
+      <c r="A264" s="13"/>
+      <c r="B264" s="11"/>
+      <c r="C264" s="11"/>
     </row>
     <row r="265" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A265" s="19"/>
-      <c r="B265" s="17"/>
-      <c r="C265" s="17"/>
+      <c r="A265" s="13"/>
+      <c r="B265" s="11"/>
+      <c r="C265" s="11"/>
     </row>
     <row r="266" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A266" s="19"/>
-      <c r="B266" s="17"/>
-      <c r="C266" s="17"/>
+      <c r="A266" s="13"/>
+      <c r="B266" s="11"/>
+      <c r="C266" s="11"/>
     </row>
     <row r="267" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A267" s="19"/>
-      <c r="B267" s="17"/>
-      <c r="C267" s="17"/>
+      <c r="A267" s="13"/>
+      <c r="B267" s="11"/>
+      <c r="C267" s="11"/>
     </row>
     <row r="268" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A268" s="19"/>
-      <c r="B268" s="17"/>
-      <c r="C268" s="17"/>
+      <c r="A268" s="13"/>
+      <c r="B268" s="11"/>
+      <c r="C268" s="11"/>
     </row>
     <row r="269" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A269" s="19"/>
-      <c r="B269" s="17"/>
-      <c r="C269" s="17"/>
+      <c r="A269" s="13"/>
+      <c r="B269" s="11"/>
+      <c r="C269" s="11"/>
     </row>
     <row r="270" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A270" s="19"/>
-      <c r="B270" s="17"/>
-      <c r="C270" s="17"/>
+      <c r="A270" s="13"/>
+      <c r="B270" s="11"/>
+      <c r="C270" s="11"/>
     </row>
     <row r="271" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A271" s="19"/>
-      <c r="B271" s="17"/>
-      <c r="C271" s="17"/>
+      <c r="A271" s="13"/>
+      <c r="B271" s="11"/>
+      <c r="C271" s="11"/>
     </row>
     <row r="272" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A272" s="19"/>
-      <c r="B272" s="17"/>
-      <c r="C272" s="17"/>
+      <c r="A272" s="13"/>
+      <c r="B272" s="11"/>
+      <c r="C272" s="11"/>
     </row>
     <row r="273" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A273" s="19"/>
-      <c r="B273" s="17"/>
-      <c r="C273" s="17"/>
+      <c r="A273" s="13"/>
+      <c r="B273" s="11"/>
+      <c r="C273" s="11"/>
     </row>
     <row r="274" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A274" s="19"/>
-      <c r="B274" s="17"/>
-      <c r="C274" s="17"/>
+      <c r="A274" s="13"/>
+      <c r="B274" s="11"/>
+      <c r="C274" s="11"/>
     </row>
     <row r="275" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A275" s="19"/>
-      <c r="B275" s="17"/>
-      <c r="C275" s="17"/>
+      <c r="A275" s="13"/>
+      <c r="B275" s="11"/>
+      <c r="C275" s="11"/>
     </row>
     <row r="276" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A276" s="19"/>
-      <c r="B276" s="17"/>
-      <c r="C276" s="17"/>
+      <c r="A276" s="13"/>
+      <c r="B276" s="11"/>
+      <c r="C276" s="11"/>
     </row>
     <row r="277" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A277" s="19"/>
-      <c r="B277" s="17"/>
-      <c r="C277" s="17"/>
+      <c r="A277" s="13"/>
+      <c r="B277" s="11"/>
+      <c r="C277" s="11"/>
     </row>
     <row r="278" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A278" s="19"/>
-      <c r="B278" s="17"/>
-      <c r="C278" s="17"/>
+      <c r="A278" s="13"/>
+      <c r="B278" s="11"/>
+      <c r="C278" s="11"/>
     </row>
     <row r="279" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A279" s="19"/>
-      <c r="B279" s="17"/>
-      <c r="C279" s="17"/>
+      <c r="A279" s="13"/>
+      <c r="B279" s="11"/>
+      <c r="C279" s="11"/>
     </row>
     <row r="280" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A280" s="19"/>
-      <c r="B280" s="17"/>
-      <c r="C280" s="17"/>
+      <c r="A280" s="13"/>
+      <c r="B280" s="11"/>
+      <c r="C280" s="11"/>
     </row>
     <row r="281" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A281" s="19"/>
-      <c r="B281" s="17"/>
-      <c r="C281" s="17"/>
+      <c r="A281" s="13"/>
+      <c r="B281" s="11"/>
+      <c r="C281" s="11"/>
     </row>
     <row r="282" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A282" s="19"/>
-      <c r="B282" s="17"/>
-      <c r="C282" s="17"/>
+      <c r="A282" s="13"/>
+      <c r="B282" s="11"/>
+      <c r="C282" s="11"/>
     </row>
     <row r="283" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A283" s="19"/>
-      <c r="B283" s="17"/>
-      <c r="C283" s="17"/>
+      <c r="A283" s="13"/>
+      <c r="B283" s="11"/>
+      <c r="C283" s="11"/>
     </row>
     <row r="284" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A284" s="19"/>
-      <c r="B284" s="17"/>
-      <c r="C284" s="17"/>
+      <c r="A284" s="13"/>
+      <c r="B284" s="11"/>
+      <c r="C284" s="11"/>
     </row>
     <row r="285" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A285" s="19"/>
-      <c r="B285" s="17"/>
-      <c r="C285" s="17"/>
+      <c r="A285" s="13"/>
+      <c r="B285" s="11"/>
+      <c r="C285" s="11"/>
     </row>
     <row r="286" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A286" s="19"/>
-      <c r="B286" s="17"/>
-      <c r="C286" s="17"/>
+      <c r="A286" s="13"/>
+      <c r="B286" s="11"/>
+      <c r="C286" s="11"/>
     </row>
     <row r="287" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A287" s="19"/>
-      <c r="B287" s="17"/>
-      <c r="C287" s="17"/>
+      <c r="A287" s="13"/>
+      <c r="B287" s="11"/>
+      <c r="C287" s="11"/>
     </row>
     <row r="288" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A288" s="19"/>
-      <c r="B288" s="17"/>
-      <c r="C288" s="17"/>
+      <c r="A288" s="13"/>
+      <c r="B288" s="11"/>
+      <c r="C288" s="11"/>
     </row>
     <row r="289" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A289" s="19"/>
-      <c r="B289" s="17"/>
-      <c r="C289" s="17"/>
+      <c r="A289" s="13"/>
+      <c r="B289" s="11"/>
+      <c r="C289" s="11"/>
     </row>
     <row r="290" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A290" s="19"/>
-      <c r="B290" s="17"/>
-      <c r="C290" s="17"/>
+      <c r="A290" s="13"/>
+      <c r="B290" s="11"/>
+      <c r="C290" s="11"/>
     </row>
     <row r="291" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A291" s="19"/>
-      <c r="B291" s="17"/>
-      <c r="C291" s="17"/>
+      <c r="A291" s="13"/>
+      <c r="B291" s="11"/>
+      <c r="C291" s="11"/>
     </row>
     <row r="292" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A292" s="19"/>
-      <c r="B292" s="17"/>
-      <c r="C292" s="17"/>
+      <c r="A292" s="13"/>
+      <c r="B292" s="11"/>
+      <c r="C292" s="11"/>
     </row>
     <row r="293" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A293" s="19"/>
-      <c r="B293" s="17"/>
-      <c r="C293" s="17"/>
+      <c r="A293" s="13"/>
+      <c r="B293" s="11"/>
+      <c r="C293" s="11"/>
     </row>
     <row r="294" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A294" s="19"/>
-      <c r="B294" s="17"/>
-      <c r="C294" s="17"/>
+      <c r="A294" s="13"/>
+      <c r="B294" s="11"/>
+      <c r="C294" s="11"/>
     </row>
     <row r="295" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A295" s="19"/>
-      <c r="B295" s="17"/>
-      <c r="C295" s="17"/>
+      <c r="A295" s="13"/>
+      <c r="B295" s="11"/>
+      <c r="C295" s="11"/>
     </row>
     <row r="296" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A296" s="19"/>
-      <c r="B296" s="17"/>
-      <c r="C296" s="17"/>
+      <c r="A296" s="13"/>
+      <c r="B296" s="11"/>
+      <c r="C296" s="11"/>
     </row>
     <row r="297" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A297" s="19"/>
-      <c r="B297" s="17"/>
-      <c r="C297" s="17"/>
+      <c r="A297" s="13"/>
+      <c r="B297" s="11"/>
+      <c r="C297" s="11"/>
     </row>
     <row r="298" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A298" s="19"/>
-      <c r="B298" s="17"/>
-      <c r="C298" s="17"/>
+      <c r="A298" s="13"/>
+      <c r="B298" s="11"/>
+      <c r="C298" s="11"/>
     </row>
     <row r="299" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A299" s="19"/>
-      <c r="B299" s="17"/>
-      <c r="C299" s="17"/>
+      <c r="A299" s="13"/>
+      <c r="B299" s="11"/>
+      <c r="C299" s="11"/>
     </row>
     <row r="300" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A300" s="19"/>
-      <c r="B300" s="17"/>
-      <c r="C300" s="17"/>
+      <c r="A300" s="13"/>
+      <c r="B300" s="11"/>
+      <c r="C300" s="11"/>
     </row>
     <row r="301" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A301" s="19"/>
-      <c r="B301" s="17"/>
-      <c r="C301" s="17"/>
+      <c r="A301" s="13"/>
+      <c r="B301" s="11"/>
+      <c r="C301" s="11"/>
     </row>
     <row r="302" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A302" s="19"/>
-      <c r="B302" s="17"/>
-      <c r="C302" s="17"/>
+      <c r="A302" s="13"/>
+      <c r="B302" s="11"/>
+      <c r="C302" s="11"/>
     </row>
     <row r="303" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A303" s="19"/>
-      <c r="B303" s="17"/>
-      <c r="C303" s="17"/>
+      <c r="A303" s="13"/>
+      <c r="B303" s="11"/>
+      <c r="C303" s="11"/>
     </row>
     <row r="304" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A304" s="19"/>
-      <c r="B304" s="17"/>
-      <c r="C304" s="17"/>
+      <c r="A304" s="13"/>
+      <c r="B304" s="11"/>
+      <c r="C304" s="11"/>
     </row>
     <row r="305" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A305" s="19"/>
-      <c r="B305" s="17"/>
-      <c r="C305" s="17"/>
+      <c r="A305" s="13"/>
+      <c r="B305" s="11"/>
+      <c r="C305" s="11"/>
     </row>
     <row r="306" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A306" s="19"/>
-      <c r="B306" s="17"/>
-      <c r="C306" s="17"/>
+      <c r="A306" s="13"/>
+      <c r="B306" s="11"/>
+      <c r="C306" s="11"/>
     </row>
     <row r="307" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A307" s="19"/>
-      <c r="B307" s="17"/>
-      <c r="C307" s="17"/>
+      <c r="A307" s="13"/>
+      <c r="B307" s="11"/>
+      <c r="C307" s="11"/>
     </row>
     <row r="308" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A308" s="19"/>
-      <c r="B308" s="17"/>
-      <c r="C308" s="17"/>
+      <c r="A308" s="13"/>
+      <c r="B308" s="11"/>
+      <c r="C308" s="11"/>
     </row>
     <row r="309" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A309" s="19"/>
-      <c r="B309" s="17"/>
-      <c r="C309" s="17"/>
+      <c r="A309" s="13"/>
+      <c r="B309" s="11"/>
+      <c r="C309" s="11"/>
     </row>
     <row r="310" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A310" s="19"/>
-      <c r="B310" s="17"/>
-      <c r="C310" s="17"/>
+      <c r="A310" s="13"/>
+      <c r="B310" s="11"/>
+      <c r="C310" s="11"/>
     </row>
     <row r="311" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A311" s="19"/>
-      <c r="B311" s="17"/>
-      <c r="C311" s="17"/>
+      <c r="A311" s="13"/>
+      <c r="B311" s="11"/>
+      <c r="C311" s="11"/>
     </row>
     <row r="312" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A312" s="19"/>
-      <c r="B312" s="17"/>
-      <c r="C312" s="17"/>
+      <c r="A312" s="13"/>
+      <c r="B312" s="11"/>
+      <c r="C312" s="11"/>
     </row>
     <row r="313" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A313" s="19"/>
-      <c r="B313" s="17"/>
-      <c r="C313" s="17"/>
+      <c r="A313" s="13"/>
+      <c r="B313" s="11"/>
+      <c r="C313" s="11"/>
     </row>
     <row r="314" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A314" s="19"/>
-      <c r="B314" s="17"/>
-      <c r="C314" s="17"/>
+      <c r="A314" s="13"/>
+      <c r="B314" s="11"/>
+      <c r="C314" s="11"/>
     </row>
     <row r="315" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A315" s="19"/>
-      <c r="B315" s="17"/>
-      <c r="C315" s="17"/>
+      <c r="A315" s="13"/>
+      <c r="B315" s="11"/>
+      <c r="C315" s="11"/>
     </row>
     <row r="316" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A316" s="19"/>
-      <c r="B316" s="17"/>
-      <c r="C316" s="17"/>
+      <c r="A316" s="13"/>
+      <c r="B316" s="11"/>
+      <c r="C316" s="11"/>
     </row>
     <row r="317" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A317" s="19"/>
-      <c r="B317" s="17"/>
-      <c r="C317" s="17"/>
+      <c r="A317" s="13"/>
+      <c r="B317" s="11"/>
+      <c r="C317" s="11"/>
     </row>
     <row r="318" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A318" s="19"/>
-      <c r="B318" s="17"/>
-      <c r="C318" s="17"/>
+      <c r="A318" s="13"/>
+      <c r="B318" s="11"/>
+      <c r="C318" s="11"/>
     </row>
     <row r="319" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A319" s="19"/>
-      <c r="B319" s="17"/>
-      <c r="C319" s="17"/>
+      <c r="A319" s="13"/>
+      <c r="B319" s="11"/>
+      <c r="C319" s="11"/>
     </row>
     <row r="320" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A320" s="19"/>
-      <c r="B320" s="17"/>
-      <c r="C320" s="17"/>
+      <c r="A320" s="13"/>
+      <c r="B320" s="11"/>
+      <c r="C320" s="11"/>
     </row>
     <row r="321" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A321" s="19"/>
-      <c r="B321" s="17"/>
-      <c r="C321" s="17"/>
+      <c r="A321" s="13"/>
+      <c r="B321" s="11"/>
+      <c r="C321" s="11"/>
     </row>
     <row r="322" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A322" s="19"/>
-      <c r="B322" s="17"/>
-      <c r="C322" s="17"/>
+      <c r="A322" s="13"/>
+      <c r="B322" s="11"/>
+      <c r="C322" s="11"/>
     </row>
     <row r="323" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A323" s="19"/>
-      <c r="B323" s="17"/>
-      <c r="C323" s="17"/>
+      <c r="A323" s="13"/>
+      <c r="B323" s="11"/>
+      <c r="C323" s="11"/>
     </row>
     <row r="324" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A324" s="19"/>
-      <c r="B324" s="17"/>
-      <c r="C324" s="17"/>
+      <c r="A324" s="13"/>
+      <c r="B324" s="11"/>
+      <c r="C324" s="11"/>
     </row>
     <row r="325" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A325" s="19"/>
-      <c r="B325" s="17"/>
-      <c r="C325" s="17"/>
+      <c r="A325" s="13"/>
+      <c r="B325" s="11"/>
+      <c r="C325" s="11"/>
     </row>
     <row r="326" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A326" s="19"/>
-      <c r="B326" s="17"/>
-      <c r="C326" s="17"/>
+      <c r="A326" s="13"/>
+      <c r="B326" s="11"/>
+      <c r="C326" s="11"/>
     </row>
     <row r="327" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A327" s="19"/>
-      <c r="B327" s="17"/>
-      <c r="C327" s="17"/>
+      <c r="A327" s="13"/>
+      <c r="B327" s="11"/>
+      <c r="C327" s="11"/>
     </row>
     <row r="328" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A328" s="19"/>
-      <c r="B328" s="17"/>
-      <c r="C328" s="17"/>
+      <c r="A328" s="13"/>
+      <c r="B328" s="11"/>
+      <c r="C328" s="11"/>
     </row>
     <row r="329" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A329" s="19"/>
-      <c r="B329" s="17"/>
-      <c r="C329" s="17"/>
+      <c r="A329" s="13"/>
+      <c r="B329" s="11"/>
+      <c r="C329" s="11"/>
     </row>
     <row r="330" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A330" s="19"/>
-      <c r="B330" s="17"/>
-      <c r="C330" s="17"/>
+      <c r="A330" s="13"/>
+      <c r="B330" s="11"/>
+      <c r="C330" s="11"/>
     </row>
     <row r="331" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A331" s="19"/>
-      <c r="B331" s="17"/>
-      <c r="C331" s="17"/>
+      <c r="A331" s="13"/>
+      <c r="B331" s="11"/>
+      <c r="C331" s="11"/>
     </row>
     <row r="332" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A332" s="19"/>
-      <c r="B332" s="17"/>
-      <c r="C332" s="17"/>
+      <c r="A332" s="13"/>
+      <c r="B332" s="11"/>
+      <c r="C332" s="11"/>
     </row>
     <row r="333" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A333" s="19"/>
-      <c r="B333" s="17"/>
-      <c r="C333" s="17"/>
+      <c r="A333" s="13"/>
+      <c r="B333" s="11"/>
+      <c r="C333" s="11"/>
     </row>
     <row r="334" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A334" s="19"/>
-      <c r="B334" s="17"/>
-      <c r="C334" s="17"/>
+      <c r="A334" s="13"/>
+      <c r="B334" s="11"/>
+      <c r="C334" s="11"/>
     </row>
     <row r="335" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A335" s="19"/>
-      <c r="B335" s="17"/>
-      <c r="C335" s="17"/>
+      <c r="A335" s="13"/>
+      <c r="B335" s="11"/>
+      <c r="C335" s="11"/>
     </row>
     <row r="336" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A336" s="19"/>
-      <c r="B336" s="17"/>
-      <c r="C336" s="17"/>
+      <c r="A336" s="13"/>
+      <c r="B336" s="11"/>
+      <c r="C336" s="11"/>
     </row>
     <row r="337" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A337" s="19"/>
-      <c r="B337" s="17"/>
-      <c r="C337" s="17"/>
+      <c r="A337" s="13"/>
+      <c r="B337" s="11"/>
+      <c r="C337" s="11"/>
     </row>
     <row r="338" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A338" s="19"/>
-      <c r="B338" s="17"/>
-      <c r="C338" s="17"/>
+      <c r="A338" s="13"/>
+      <c r="B338" s="11"/>
+      <c r="C338" s="11"/>
     </row>
     <row r="339" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A339" s="19"/>
-      <c r="B339" s="17"/>
-      <c r="C339" s="17"/>
+      <c r="A339" s="13"/>
+      <c r="B339" s="11"/>
+      <c r="C339" s="11"/>
     </row>
     <row r="340" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A340" s="19"/>
-      <c r="B340" s="17"/>
-      <c r="C340" s="17"/>
+      <c r="A340" s="13"/>
+      <c r="B340" s="11"/>
+      <c r="C340" s="11"/>
     </row>
     <row r="341" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A341" s="19"/>
-      <c r="B341" s="17"/>
-      <c r="C341" s="17"/>
+      <c r="A341" s="13"/>
+      <c r="B341" s="11"/>
+      <c r="C341" s="11"/>
     </row>
     <row r="342" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A342" s="19"/>
-      <c r="B342" s="17"/>
-      <c r="C342" s="17"/>
+      <c r="A342" s="13"/>
+      <c r="B342" s="11"/>
+      <c r="C342" s="11"/>
     </row>
     <row r="343" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A343" s="19"/>
-      <c r="B343" s="17"/>
-      <c r="C343" s="17"/>
+      <c r="A343" s="13"/>
+      <c r="B343" s="11"/>
+      <c r="C343" s="11"/>
     </row>
     <row r="344" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A344" s="19"/>
-      <c r="B344" s="17"/>
-      <c r="C344" s="17"/>
+      <c r="A344" s="13"/>
+      <c r="B344" s="11"/>
+      <c r="C344" s="11"/>
     </row>
     <row r="345" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A345" s="19"/>
-      <c r="B345" s="17"/>
-      <c r="C345" s="17"/>
+      <c r="A345" s="13"/>
+      <c r="B345" s="11"/>
+      <c r="C345" s="11"/>
     </row>
     <row r="346" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A346" s="19"/>
-      <c r="B346" s="17"/>
-      <c r="C346" s="17"/>
+      <c r="A346" s="13"/>
+      <c r="B346" s="11"/>
+      <c r="C346" s="11"/>
     </row>
     <row r="347" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A347" s="19"/>
-      <c r="B347" s="17"/>
-      <c r="C347" s="17"/>
+      <c r="A347" s="13"/>
+      <c r="B347" s="11"/>
+      <c r="C347" s="11"/>
     </row>
     <row r="348" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A348" s="19"/>
-      <c r="B348" s="17"/>
-      <c r="C348" s="17"/>
+      <c r="A348" s="13"/>
+      <c r="B348" s="11"/>
+      <c r="C348" s="11"/>
     </row>
     <row r="349" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A349" s="19"/>
-      <c r="B349" s="17"/>
-      <c r="C349" s="17"/>
+      <c r="A349" s="13"/>
+      <c r="B349" s="11"/>
+      <c r="C349" s="11"/>
     </row>
     <row r="350" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A350" s="19"/>
-      <c r="B350" s="17"/>
-      <c r="C350" s="17"/>
+      <c r="A350" s="13"/>
+      <c r="B350" s="11"/>
+      <c r="C350" s="11"/>
     </row>
     <row r="351" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A351" s="19"/>
-      <c r="B351" s="17"/>
-      <c r="C351" s="17"/>
+      <c r="A351" s="13"/>
+      <c r="B351" s="11"/>
+      <c r="C351" s="11"/>
     </row>
     <row r="352" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A352" s="19"/>
-      <c r="B352" s="17"/>
-      <c r="C352" s="17"/>
+      <c r="A352" s="13"/>
+      <c r="B352" s="11"/>
+      <c r="C352" s="11"/>
     </row>
     <row r="353" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A353" s="19"/>
-      <c r="B353" s="17"/>
-      <c r="C353" s="17"/>
+      <c r="A353" s="13"/>
+      <c r="B353" s="11"/>
+      <c r="C353" s="11"/>
     </row>
     <row r="354" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A354" s="19"/>
-      <c r="B354" s="17"/>
-      <c r="C354" s="17"/>
+      <c r="A354" s="13"/>
+      <c r="B354" s="11"/>
+      <c r="C354" s="11"/>
     </row>
     <row r="355" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A355" s="19"/>
-      <c r="B355" s="17"/>
-      <c r="C355" s="17"/>
+      <c r="A355" s="13"/>
+      <c r="B355" s="11"/>
+      <c r="C355" s="11"/>
     </row>
     <row r="356" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A356" s="19"/>
-      <c r="B356" s="17"/>
-      <c r="C356" s="17"/>
+      <c r="A356" s="13"/>
+      <c r="B356" s="11"/>
+      <c r="C356" s="11"/>
     </row>
     <row r="357" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A357" s="19"/>
-      <c r="B357" s="17"/>
-      <c r="C357" s="17"/>
+      <c r="A357" s="13"/>
+      <c r="B357" s="11"/>
+      <c r="C357" s="11"/>
     </row>
     <row r="358" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A358" s="19"/>
-      <c r="B358" s="17"/>
-      <c r="C358" s="17"/>
+      <c r="A358" s="13"/>
+      <c r="B358" s="11"/>
+      <c r="C358" s="11"/>
     </row>
     <row r="359" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A359" s="19"/>
-      <c r="B359" s="17"/>
-      <c r="C359" s="17"/>
+      <c r="A359" s="13"/>
+      <c r="B359" s="11"/>
+      <c r="C359" s="11"/>
     </row>
     <row r="360" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A360" s="19"/>
-      <c r="B360" s="17"/>
-      <c r="C360" s="17"/>
+      <c r="A360" s="13"/>
+      <c r="B360" s="11"/>
+      <c r="C360" s="11"/>
     </row>
     <row r="361" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A361" s="19"/>
-      <c r="B361" s="17"/>
-      <c r="C361" s="17"/>
+      <c r="A361" s="13"/>
+      <c r="B361" s="11"/>
+      <c r="C361" s="11"/>
     </row>
     <row r="362" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A362" s="19"/>
-      <c r="B362" s="17"/>
-      <c r="C362" s="17"/>
+      <c r="A362" s="13"/>
+      <c r="B362" s="11"/>
+      <c r="C362" s="11"/>
     </row>
     <row r="363" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A363" s="19"/>
-      <c r="B363" s="17"/>
-      <c r="C363" s="17"/>
+      <c r="A363" s="13"/>
+      <c r="B363" s="11"/>
+      <c r="C363" s="11"/>
     </row>
     <row r="364" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A364" s="19"/>
-      <c r="B364" s="17"/>
-      <c r="C364" s="17"/>
+      <c r="A364" s="13"/>
+      <c r="B364" s="11"/>
+      <c r="C364" s="11"/>
     </row>
     <row r="365" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A365" s="19"/>
-      <c r="B365" s="17"/>
-      <c r="C365" s="17"/>
+      <c r="A365" s="13"/>
+      <c r="B365" s="11"/>
+      <c r="C365" s="11"/>
     </row>
     <row r="366" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A366" s="19"/>
-      <c r="B366" s="17"/>
-      <c r="C366" s="17"/>
+      <c r="A366" s="13"/>
+      <c r="B366" s="11"/>
+      <c r="C366" s="11"/>
     </row>
     <row r="367" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A367" s="19"/>
-      <c r="B367" s="17"/>
-      <c r="C367" s="17"/>
+      <c r="A367" s="13"/>
+      <c r="B367" s="11"/>
+      <c r="C367" s="11"/>
     </row>
     <row r="368" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A368" s="19"/>
-      <c r="B368" s="17"/>
-      <c r="C368" s="17"/>
+      <c r="A368" s="13"/>
+      <c r="B368" s="11"/>
+      <c r="C368" s="11"/>
     </row>
     <row r="369" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A369" s="19"/>
-      <c r="B369" s="17"/>
-      <c r="C369" s="17"/>
+      <c r="A369" s="13"/>
+      <c r="B369" s="11"/>
+      <c r="C369" s="11"/>
     </row>
     <row r="370" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A370" s="19"/>
-      <c r="B370" s="17"/>
-      <c r="C370" s="17"/>
+      <c r="A370" s="13"/>
+      <c r="B370" s="11"/>
+      <c r="C370" s="11"/>
     </row>
     <row r="371" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A371" s="19"/>
-      <c r="B371" s="17"/>
-      <c r="C371" s="17"/>
+      <c r="A371" s="13"/>
+      <c r="B371" s="11"/>
+      <c r="C371" s="11"/>
     </row>
     <row r="372" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A372" s="19"/>
-      <c r="B372" s="17"/>
-      <c r="C372" s="17"/>
+      <c r="A372" s="13"/>
+      <c r="B372" s="11"/>
+      <c r="C372" s="11"/>
     </row>
     <row r="373" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A373" s="19"/>
-      <c r="B373" s="17"/>
-      <c r="C373" s="17"/>
+      <c r="A373" s="13"/>
+      <c r="B373" s="11"/>
+      <c r="C373" s="11"/>
     </row>
     <row r="374" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A374" s="19"/>
-      <c r="B374" s="17"/>
-      <c r="C374" s="17"/>
+      <c r="A374" s="13"/>
+      <c r="B374" s="11"/>
+      <c r="C374" s="11"/>
     </row>
     <row r="375" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A375" s="19"/>
-      <c r="B375" s="17"/>
-      <c r="C375" s="17"/>
+      <c r="A375" s="13"/>
+      <c r="B375" s="11"/>
+      <c r="C375" s="11"/>
     </row>
     <row r="376" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A376" s="19"/>
-      <c r="B376" s="17"/>
-      <c r="C376" s="17"/>
+      <c r="A376" s="13"/>
+      <c r="B376" s="11"/>
+      <c r="C376" s="11"/>
     </row>
     <row r="377" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A377" s="19"/>
-      <c r="B377" s="17"/>
-      <c r="C377" s="17"/>
+      <c r="A377" s="13"/>
+      <c r="B377" s="11"/>
+      <c r="C377" s="11"/>
     </row>
     <row r="378" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A378" s="19"/>
-      <c r="B378" s="17"/>
-      <c r="C378" s="17"/>
+      <c r="A378" s="13"/>
+      <c r="B378" s="11"/>
+      <c r="C378" s="11"/>
     </row>
     <row r="379" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A379" s="19"/>
-      <c r="B379" s="17"/>
-      <c r="C379" s="17"/>
+      <c r="A379" s="13"/>
+      <c r="B379" s="11"/>
+      <c r="C379" s="11"/>
     </row>
     <row r="380" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A380" s="19"/>
-      <c r="B380" s="17"/>
-      <c r="C380" s="17"/>
+      <c r="A380" s="13"/>
+      <c r="B380" s="11"/>
+      <c r="C380" s="11"/>
     </row>
     <row r="381" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A381" s="19"/>
-      <c r="B381" s="17"/>
-      <c r="C381" s="17"/>
+      <c r="A381" s="13"/>
+      <c r="B381" s="11"/>
+      <c r="C381" s="11"/>
     </row>
     <row r="382" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A382" s="19"/>
-      <c r="B382" s="17"/>
-      <c r="C382" s="17"/>
+      <c r="A382" s="13"/>
+      <c r="B382" s="11"/>
+      <c r="C382" s="11"/>
     </row>
     <row r="383" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A383" s="19"/>
-      <c r="B383" s="17"/>
-      <c r="C383" s="17"/>
+      <c r="A383" s="13"/>
+      <c r="B383" s="11"/>
+      <c r="C383" s="11"/>
     </row>
     <row r="384" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A384" s="19"/>
-      <c r="B384" s="17"/>
-      <c r="C384" s="17"/>
+      <c r="A384" s="13"/>
+      <c r="B384" s="11"/>
+      <c r="C384" s="11"/>
     </row>
     <row r="385" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A385" s="19"/>
-      <c r="B385" s="17"/>
-      <c r="C385" s="17"/>
+      <c r="A385" s="13"/>
+      <c r="B385" s="11"/>
+      <c r="C385" s="11"/>
     </row>
     <row r="386" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A386" s="19"/>
-      <c r="B386" s="17"/>
-      <c r="C386" s="17"/>
+      <c r="A386" s="13"/>
+      <c r="B386" s="11"/>
+      <c r="C386" s="11"/>
     </row>
     <row r="387" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A387" s="19"/>
-      <c r="B387" s="17"/>
-      <c r="C387" s="17"/>
+      <c r="A387" s="13"/>
+      <c r="B387" s="11"/>
+      <c r="C387" s="11"/>
     </row>
     <row r="388" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A388" s="19"/>
-      <c r="B388" s="17"/>
-      <c r="C388" s="17"/>
+      <c r="A388" s="13"/>
+      <c r="B388" s="11"/>
+      <c r="C388" s="11"/>
     </row>
     <row r="389" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A389" s="19"/>
-      <c r="B389" s="17"/>
-      <c r="C389" s="17"/>
+      <c r="A389" s="13"/>
+      <c r="B389" s="11"/>
+      <c r="C389" s="11"/>
     </row>
     <row r="390" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A390" s="19"/>
-      <c r="B390" s="17"/>
-      <c r="C390" s="17"/>
+      <c r="A390" s="13"/>
+      <c r="B390" s="11"/>
+      <c r="C390" s="11"/>
     </row>
     <row r="391" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A391" s="19"/>
-      <c r="B391" s="17"/>
-      <c r="C391" s="17"/>
+      <c r="A391" s="13"/>
+      <c r="B391" s="11"/>
+      <c r="C391" s="11"/>
     </row>
     <row r="392" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A392" s="19"/>
-      <c r="B392" s="17"/>
-      <c r="C392" s="17"/>
+      <c r="A392" s="13"/>
+      <c r="B392" s="11"/>
+      <c r="C392" s="11"/>
     </row>
     <row r="393" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A393" s="19"/>
-      <c r="B393" s="17"/>
-      <c r="C393" s="17"/>
+      <c r="A393" s="13"/>
+      <c r="B393" s="11"/>
+      <c r="C393" s="11"/>
     </row>
     <row r="394" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A394" s="19"/>
-      <c r="B394" s="17"/>
-      <c r="C394" s="17"/>
+      <c r="A394" s="13"/>
+      <c r="B394" s="11"/>
+      <c r="C394" s="11"/>
     </row>
     <row r="395" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A395" s="19"/>
-      <c r="B395" s="17"/>
-      <c r="C395" s="17"/>
+      <c r="A395" s="13"/>
+      <c r="B395" s="11"/>
+      <c r="C395" s="11"/>
     </row>
     <row r="396" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A396" s="19"/>
-      <c r="B396" s="17"/>
-      <c r="C396" s="17"/>
+      <c r="A396" s="13"/>
+      <c r="B396" s="11"/>
+      <c r="C396" s="11"/>
     </row>
     <row r="397" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A397" s="19"/>
-      <c r="B397" s="17"/>
-      <c r="C397" s="17"/>
+      <c r="A397" s="13"/>
+      <c r="B397" s="11"/>
+      <c r="C397" s="11"/>
     </row>
     <row r="398" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A398" s="19"/>
-      <c r="B398" s="17"/>
-      <c r="C398" s="17"/>
+      <c r="A398" s="13"/>
+      <c r="B398" s="11"/>
+      <c r="C398" s="11"/>
     </row>
     <row r="399" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A399" s="19"/>
-      <c r="B399" s="17"/>
-      <c r="C399" s="17"/>
+      <c r="A399" s="13"/>
+      <c r="B399" s="11"/>
+      <c r="C399" s="11"/>
     </row>
     <row r="400" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A400" s="19"/>
-      <c r="B400" s="17"/>
-      <c r="C400" s="17"/>
+      <c r="A400" s="13"/>
+      <c r="B400" s="11"/>
+      <c r="C400" s="11"/>
     </row>
     <row r="401" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A401" s="19"/>
-      <c r="B401" s="17"/>
-      <c r="C401" s="17"/>
+      <c r="A401" s="13"/>
+      <c r="B401" s="11"/>
+      <c r="C401" s="11"/>
     </row>
     <row r="402" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A402" s="19"/>
-      <c r="B402" s="17"/>
-      <c r="C402" s="17"/>
+      <c r="A402" s="13"/>
+      <c r="B402" s="11"/>
+      <c r="C402" s="11"/>
     </row>
     <row r="403" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A403" s="19"/>
-      <c r="B403" s="17"/>
-      <c r="C403" s="17"/>
+      <c r="A403" s="13"/>
+      <c r="B403" s="11"/>
+      <c r="C403" s="11"/>
     </row>
     <row r="404" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A404" s="19"/>
-      <c r="B404" s="17"/>
-      <c r="C404" s="17"/>
+      <c r="A404" s="13"/>
+      <c r="B404" s="11"/>
+      <c r="C404" s="11"/>
     </row>
     <row r="405" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A405" s="19"/>
-      <c r="B405" s="17"/>
-      <c r="C405" s="17"/>
+      <c r="A405" s="13"/>
+      <c r="B405" s="11"/>
+      <c r="C405" s="11"/>
     </row>
     <row r="406" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A406" s="19"/>
-      <c r="B406" s="17"/>
-      <c r="C406" s="17"/>
+      <c r="A406" s="13"/>
+      <c r="B406" s="11"/>
+      <c r="C406" s="11"/>
     </row>
     <row r="407" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A407" s="19"/>
-      <c r="B407" s="17"/>
-      <c r="C407" s="17"/>
+      <c r="A407" s="13"/>
+      <c r="B407" s="11"/>
+      <c r="C407" s="11"/>
     </row>
     <row r="408" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A408" s="19"/>
-      <c r="B408" s="17"/>
-      <c r="C408" s="17"/>
+      <c r="A408" s="13"/>
+      <c r="B408" s="11"/>
+      <c r="C408" s="11"/>
     </row>
     <row r="409" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A409" s="19"/>
-      <c r="B409" s="17"/>
-      <c r="C409" s="17"/>
+      <c r="A409" s="13"/>
+      <c r="B409" s="11"/>
+      <c r="C409" s="11"/>
     </row>
     <row r="410" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A410" s="19"/>
-      <c r="B410" s="17"/>
-      <c r="C410" s="17"/>
+      <c r="A410" s="13"/>
+      <c r="B410" s="11"/>
+      <c r="C410" s="11"/>
     </row>
     <row r="411" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A411" s="19"/>
-      <c r="B411" s="17"/>
-      <c r="C411" s="17"/>
+      <c r="A411" s="13"/>
+      <c r="B411" s="11"/>
+      <c r="C411" s="11"/>
     </row>
     <row r="412" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A412" s="19"/>
-      <c r="B412" s="17"/>
-      <c r="C412" s="17"/>
+      <c r="A412" s="13"/>
+      <c r="B412" s="11"/>
+      <c r="C412" s="11"/>
     </row>
     <row r="413" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A413" s="19"/>
-      <c r="B413" s="17"/>
-      <c r="C413" s="17"/>
+      <c r="A413" s="13"/>
+      <c r="B413" s="11"/>
+      <c r="C413" s="11"/>
     </row>
     <row r="414" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A414" s="19"/>
-      <c r="B414" s="17"/>
-      <c r="C414" s="17"/>
+      <c r="A414" s="13"/>
+      <c r="B414" s="11"/>
+      <c r="C414" s="11"/>
     </row>
     <row r="415" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A415" s="19"/>
-      <c r="B415" s="17"/>
-      <c r="C415" s="17"/>
+      <c r="A415" s="13"/>
+      <c r="B415" s="11"/>
+      <c r="C415" s="11"/>
     </row>
     <row r="416" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A416" s="19"/>
-      <c r="B416" s="17"/>
-      <c r="C416" s="17"/>
+      <c r="A416" s="13"/>
+      <c r="B416" s="11"/>
+      <c r="C416" s="11"/>
     </row>
     <row r="417" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A417" s="19"/>
-      <c r="B417" s="17"/>
-      <c r="C417" s="17"/>
+      <c r="A417" s="13"/>
+      <c r="B417" s="11"/>
+      <c r="C417" s="11"/>
     </row>
     <row r="418" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A418" s="19"/>
-      <c r="B418" s="17"/>
-      <c r="C418" s="17"/>
+      <c r="A418" s="13"/>
+      <c r="B418" s="11"/>
+      <c r="C418" s="11"/>
     </row>
     <row r="419" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A419" s="19"/>
-      <c r="B419" s="17"/>
-      <c r="C419" s="17"/>
+      <c r="A419" s="13"/>
+      <c r="B419" s="11"/>
+      <c r="C419" s="11"/>
     </row>
     <row r="420" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A420" s="19"/>
-      <c r="B420" s="17"/>
-      <c r="C420" s="17"/>
+      <c r="A420" s="13"/>
+      <c r="B420" s="11"/>
+      <c r="C420" s="11"/>
     </row>
     <row r="421" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A421" s="19"/>
-      <c r="B421" s="17"/>
-      <c r="C421" s="17"/>
+      <c r="A421" s="13"/>
+      <c r="B421" s="11"/>
+      <c r="C421" s="11"/>
     </row>
     <row r="422" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A422" s="19"/>
-      <c r="B422" s="17"/>
-      <c r="C422" s="17"/>
+      <c r="A422" s="13"/>
+      <c r="B422" s="11"/>
+      <c r="C422" s="11"/>
     </row>
     <row r="423" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A423" s="19"/>
-      <c r="B423" s="17"/>
-      <c r="C423" s="17"/>
+      <c r="A423" s="13"/>
+      <c r="B423" s="11"/>
+      <c r="C423" s="11"/>
     </row>
     <row r="424" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A424" s="19"/>
-      <c r="B424" s="17"/>
-      <c r="C424" s="17"/>
+      <c r="A424" s="13"/>
+      <c r="B424" s="11"/>
+      <c r="C424" s="11"/>
     </row>
     <row r="425" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A425" s="19"/>
-      <c r="B425" s="17"/>
-      <c r="C425" s="17"/>
+      <c r="A425" s="13"/>
+      <c r="B425" s="11"/>
+      <c r="C425" s="11"/>
     </row>
     <row r="426" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A426" s="19"/>
-      <c r="B426" s="17"/>
-      <c r="C426" s="17"/>
+      <c r="A426" s="13"/>
+      <c r="B426" s="11"/>
+      <c r="C426" s="11"/>
     </row>
     <row r="427" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A427" s="19"/>
-      <c r="B427" s="17"/>
-      <c r="C427" s="17"/>
+      <c r="A427" s="13"/>
+      <c r="B427" s="11"/>
+      <c r="C427" s="11"/>
     </row>
     <row r="428" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A428" s="19"/>
-      <c r="B428" s="17"/>
-      <c r="C428" s="17"/>
+      <c r="A428" s="13"/>
+      <c r="B428" s="11"/>
+      <c r="C428" s="11"/>
     </row>
     <row r="429" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A429" s="19"/>
-      <c r="B429" s="17"/>
-      <c r="C429" s="17"/>
+      <c r="A429" s="13"/>
+      <c r="B429" s="11"/>
+      <c r="C429" s="11"/>
     </row>
     <row r="430" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A430" s="19"/>
-      <c r="B430" s="17"/>
-      <c r="C430" s="17"/>
+      <c r="A430" s="13"/>
+      <c r="B430" s="11"/>
+      <c r="C430" s="11"/>
     </row>
     <row r="431" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A431" s="19"/>
-      <c r="B431" s="17"/>
-      <c r="C431" s="17"/>
+      <c r="A431" s="13"/>
+      <c r="B431" s="11"/>
+      <c r="C431" s="11"/>
     </row>
     <row r="432" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A432" s="19"/>
-      <c r="B432" s="17"/>
-      <c r="C432" s="17"/>
+      <c r="A432" s="13"/>
+      <c r="B432" s="11"/>
+      <c r="C432" s="11"/>
     </row>
     <row r="433" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A433" s="19"/>
-      <c r="B433" s="17"/>
-      <c r="C433" s="17"/>
+      <c r="A433" s="13"/>
+      <c r="B433" s="11"/>
+      <c r="C433" s="11"/>
     </row>
     <row r="434" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A434" s="19"/>
-      <c r="B434" s="17"/>
-      <c r="C434" s="17"/>
+      <c r="A434" s="13"/>
+      <c r="B434" s="11"/>
+      <c r="C434" s="11"/>
     </row>
     <row r="435" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A435" s="19"/>
-      <c r="B435" s="17"/>
-      <c r="C435" s="17"/>
+      <c r="A435" s="13"/>
+      <c r="B435" s="11"/>
+      <c r="C435" s="11"/>
     </row>
     <row r="436" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A436" s="19"/>
-      <c r="B436" s="17"/>
-      <c r="C436" s="17"/>
+      <c r="A436" s="13"/>
+      <c r="B436" s="11"/>
+      <c r="C436" s="11"/>
     </row>
     <row r="437" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A437" s="19"/>
-      <c r="B437" s="17"/>
-      <c r="C437" s="17"/>
+      <c r="A437" s="13"/>
+      <c r="B437" s="11"/>
+      <c r="C437" s="11"/>
     </row>
     <row r="438" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A438" s="19"/>
-      <c r="B438" s="17"/>
-      <c r="C438" s="17"/>
+      <c r="A438" s="13"/>
+      <c r="B438" s="11"/>
+      <c r="C438" s="11"/>
     </row>
     <row r="439" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A439" s="19"/>
-      <c r="B439" s="17"/>
-      <c r="C439" s="17"/>
+      <c r="A439" s="13"/>
+      <c r="B439" s="11"/>
+      <c r="C439" s="11"/>
     </row>
     <row r="440" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A440" s="19"/>
-      <c r="B440" s="17"/>
-      <c r="C440" s="17"/>
+      <c r="A440" s="13"/>
+      <c r="B440" s="11"/>
+      <c r="C440" s="11"/>
     </row>
     <row r="441" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A441" s="19"/>
-      <c r="B441" s="17"/>
-      <c r="C441" s="17"/>
+      <c r="A441" s="13"/>
+      <c r="B441" s="11"/>
+      <c r="C441" s="11"/>
     </row>
     <row r="442" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A442" s="19"/>
-      <c r="B442" s="17"/>
-      <c r="C442" s="17"/>
+      <c r="A442" s="13"/>
+      <c r="B442" s="11"/>
+      <c r="C442" s="11"/>
     </row>
     <row r="443" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A443" s="19"/>
-      <c r="B443" s="17"/>
-      <c r="C443" s="17"/>
+      <c r="A443" s="13"/>
+      <c r="B443" s="11"/>
+      <c r="C443" s="11"/>
     </row>
     <row r="444" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A444" s="19"/>
-      <c r="B444" s="17"/>
-      <c r="C444" s="17"/>
+      <c r="A444" s="13"/>
+      <c r="B444" s="11"/>
+      <c r="C444" s="11"/>
     </row>
     <row r="445" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A445" s="19"/>
-      <c r="B445" s="17"/>
-      <c r="C445" s="17"/>
+      <c r="A445" s="13"/>
+      <c r="B445" s="11"/>
+      <c r="C445" s="11"/>
     </row>
     <row r="446" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A446" s="19"/>
-      <c r="B446" s="17"/>
-      <c r="C446" s="17"/>
+      <c r="A446" s="13"/>
+      <c r="B446" s="11"/>
+      <c r="C446" s="11"/>
     </row>
     <row r="447" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A447" s="19"/>
-      <c r="B447" s="17"/>
-      <c r="C447" s="17"/>
+      <c r="A447" s="13"/>
+      <c r="B447" s="11"/>
+      <c r="C447" s="11"/>
     </row>
     <row r="448" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A448" s="19"/>
-      <c r="B448" s="17"/>
-      <c r="C448" s="17"/>
+      <c r="A448" s="13"/>
+      <c r="B448" s="11"/>
+      <c r="C448" s="11"/>
     </row>
     <row r="449" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A449" s="19"/>
-      <c r="B449" s="17"/>
-      <c r="C449" s="17"/>
+      <c r="A449" s="13"/>
+      <c r="B449" s="11"/>
+      <c r="C449" s="11"/>
     </row>
     <row r="450" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A450" s="19"/>
-      <c r="B450" s="17"/>
-      <c r="C450" s="17"/>
+      <c r="A450" s="13"/>
+      <c r="B450" s="11"/>
+      <c r="C450" s="11"/>
     </row>
     <row r="451" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A451" s="19"/>
-      <c r="B451" s="17"/>
-      <c r="C451" s="17"/>
+      <c r="A451" s="13"/>
+      <c r="B451" s="11"/>
+      <c r="C451" s="11"/>
     </row>
     <row r="452" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A452" s="19"/>
-      <c r="B452" s="17"/>
-      <c r="C452" s="17"/>
+      <c r="A452" s="13"/>
+      <c r="B452" s="11"/>
+      <c r="C452" s="11"/>
     </row>
     <row r="453" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A453" s="19"/>
-      <c r="B453" s="17"/>
-      <c r="C453" s="17"/>
+      <c r="A453" s="13"/>
+      <c r="B453" s="11"/>
+      <c r="C453" s="11"/>
     </row>
     <row r="454" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A454" s="19"/>
-      <c r="B454" s="17"/>
-      <c r="C454" s="17"/>
+      <c r="A454" s="13"/>
+      <c r="B454" s="11"/>
+      <c r="C454" s="11"/>
     </row>
     <row r="455" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A455" s="19"/>
-      <c r="B455" s="17"/>
-      <c r="C455" s="17"/>
+      <c r="A455" s="13"/>
+      <c r="B455" s="11"/>
+      <c r="C455" s="11"/>
     </row>
     <row r="456" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A456" s="19"/>
-      <c r="B456" s="17"/>
-      <c r="C456" s="17"/>
+      <c r="A456" s="13"/>
+      <c r="B456" s="11"/>
+      <c r="C456" s="11"/>
     </row>
     <row r="457" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A457" s="19"/>
-      <c r="B457" s="17"/>
-      <c r="C457" s="17"/>
+      <c r="A457" s="13"/>
+      <c r="B457" s="11"/>
+      <c r="C457" s="11"/>
     </row>
     <row r="458" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A458" s="19"/>
-      <c r="B458" s="17"/>
-      <c r="C458" s="17"/>
+      <c r="A458" s="13"/>
+      <c r="B458" s="11"/>
+      <c r="C458" s="11"/>
     </row>
     <row r="459" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A459" s="19"/>
-      <c r="B459" s="17"/>
-      <c r="C459" s="17"/>
+      <c r="A459" s="13"/>
+      <c r="B459" s="11"/>
+      <c r="C459" s="11"/>
     </row>
     <row r="460" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A460" s="19"/>
-      <c r="B460" s="17"/>
-      <c r="C460" s="17"/>
+      <c r="A460" s="13"/>
+      <c r="B460" s="11"/>
+      <c r="C460" s="11"/>
     </row>
     <row r="461" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A461" s="19"/>
-      <c r="B461" s="17"/>
-      <c r="C461" s="17"/>
+      <c r="A461" s="13"/>
+      <c r="B461" s="11"/>
+      <c r="C461" s="11"/>
     </row>
     <row r="462" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A462" s="19"/>
-      <c r="B462" s="17"/>
-      <c r="C462" s="17"/>
+      <c r="A462" s="13"/>
+      <c r="B462" s="11"/>
+      <c r="C462" s="11"/>
     </row>
     <row r="463" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A463" s="19"/>
-      <c r="B463" s="17"/>
-      <c r="C463" s="17"/>
+      <c r="A463" s="13"/>
+      <c r="B463" s="11"/>
+      <c r="C463" s="11"/>
     </row>
     <row r="464" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A464" s="19"/>
-      <c r="B464" s="17"/>
-      <c r="C464" s="17"/>
+      <c r="A464" s="13"/>
+      <c r="B464" s="11"/>
+      <c r="C464" s="11"/>
     </row>
     <row r="465" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A465" s="19"/>
-      <c r="B465" s="17"/>
-      <c r="C465" s="17"/>
+      <c r="A465" s="13"/>
+      <c r="B465" s="11"/>
+      <c r="C465" s="11"/>
     </row>
     <row r="466" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A466" s="19"/>
-      <c r="B466" s="17"/>
-      <c r="C466" s="17"/>
+      <c r="A466" s="13"/>
+      <c r="B466" s="11"/>
+      <c r="C466" s="11"/>
     </row>
     <row r="467" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A467" s="19"/>
-      <c r="B467" s="17"/>
-      <c r="C467" s="17"/>
+      <c r="A467" s="13"/>
+      <c r="B467" s="11"/>
+      <c r="C467" s="11"/>
     </row>
     <row r="468" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A468" s="19"/>
-      <c r="B468" s="17"/>
-      <c r="C468" s="17"/>
+      <c r="A468" s="13"/>
+      <c r="B468" s="11"/>
+      <c r="C468" s="11"/>
     </row>
     <row r="469" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A469" s="19"/>
-      <c r="B469" s="17"/>
-      <c r="C469" s="17"/>
+      <c r="A469" s="13"/>
+      <c r="B469" s="11"/>
+      <c r="C469" s="11"/>
     </row>
     <row r="470" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A470" s="19"/>
-      <c r="B470" s="17"/>
-      <c r="C470" s="17"/>
+      <c r="A470" s="13"/>
+      <c r="B470" s="11"/>
+      <c r="C470" s="11"/>
     </row>
     <row r="471" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A471" s="19"/>
-      <c r="B471" s="17"/>
-      <c r="C471" s="17"/>
+      <c r="A471" s="13"/>
+      <c r="B471" s="11"/>
+      <c r="C471" s="11"/>
     </row>
     <row r="472" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A472" s="19"/>
-      <c r="B472" s="17"/>
-      <c r="C472" s="17"/>
+      <c r="A472" s="13"/>
+      <c r="B472" s="11"/>
+      <c r="C472" s="11"/>
     </row>
     <row r="473" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A473" s="19"/>
-      <c r="B473" s="17"/>
-      <c r="C473" s="17"/>
+      <c r="A473" s="13"/>
+      <c r="B473" s="11"/>
+      <c r="C473" s="11"/>
     </row>
     <row r="474" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A474" s="19"/>
-      <c r="B474" s="17"/>
-      <c r="C474" s="17"/>
+      <c r="A474" s="13"/>
+      <c r="B474" s="11"/>
+      <c r="C474" s="11"/>
     </row>
     <row r="475" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A475" s="19"/>
-      <c r="B475" s="17"/>
-      <c r="C475" s="17"/>
+      <c r="A475" s="13"/>
+      <c r="B475" s="11"/>
+      <c r="C475" s="11"/>
     </row>
     <row r="476" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A476" s="19"/>
-      <c r="B476" s="17"/>
-      <c r="C476" s="17"/>
+      <c r="A476" s="13"/>
+      <c r="B476" s="11"/>
+      <c r="C476" s="11"/>
     </row>
     <row r="477" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A477" s="19"/>
-      <c r="B477" s="17"/>
-      <c r="C477" s="17"/>
+      <c r="A477" s="13"/>
+      <c r="B477" s="11"/>
+      <c r="C477" s="11"/>
     </row>
     <row r="478" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A478" s="19"/>
-      <c r="B478" s="17"/>
-      <c r="C478" s="17"/>
+      <c r="A478" s="13"/>
+      <c r="B478" s="11"/>
+      <c r="C478" s="11"/>
     </row>
     <row r="479" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A479" s="19"/>
-      <c r="B479" s="17"/>
-      <c r="C479" s="17"/>
+      <c r="A479" s="13"/>
+      <c r="B479" s="11"/>
+      <c r="C479" s="11"/>
     </row>
     <row r="480" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A480" s="19"/>
-      <c r="B480" s="17"/>
-      <c r="C480" s="17"/>
+      <c r="A480" s="13"/>
+      <c r="B480" s="11"/>
+      <c r="C480" s="11"/>
     </row>
     <row r="481" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A481" s="19"/>
-      <c r="B481" s="17"/>
-      <c r="C481" s="17"/>
+      <c r="A481" s="13"/>
+      <c r="B481" s="11"/>
+      <c r="C481" s="11"/>
     </row>
     <row r="482" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A482" s="19"/>
-      <c r="B482" s="17"/>
-      <c r="C482" s="17"/>
+      <c r="A482" s="13"/>
+      <c r="B482" s="11"/>
+      <c r="C482" s="11"/>
     </row>
     <row r="483" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A483" s="19"/>
-      <c r="B483" s="17"/>
-      <c r="C483" s="17"/>
+      <c r="A483" s="13"/>
+      <c r="B483" s="11"/>
+      <c r="C483" s="11"/>
     </row>
     <row r="484" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A484" s="19"/>
-      <c r="B484" s="17"/>
-      <c r="C484" s="17"/>
+      <c r="A484" s="13"/>
+      <c r="B484" s="11"/>
+      <c r="C484" s="11"/>
     </row>
     <row r="485" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A485" s="19"/>
-      <c r="B485" s="17"/>
-      <c r="C485" s="17"/>
+      <c r="A485" s="13"/>
+      <c r="B485" s="11"/>
+      <c r="C485" s="11"/>
     </row>
     <row r="486" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A486" s="19"/>
-      <c r="B486" s="17"/>
-      <c r="C486" s="17"/>
+      <c r="A486" s="13"/>
+      <c r="B486" s="11"/>
+      <c r="C486" s="11"/>
     </row>
     <row r="487" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A487" s="19"/>
-      <c r="B487" s="17"/>
-      <c r="C487" s="17"/>
+      <c r="A487" s="13"/>
+      <c r="B487" s="11"/>
+      <c r="C487" s="11"/>
     </row>
     <row r="488" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A488" s="19"/>
-      <c r="B488" s="17"/>
-      <c r="C488" s="17"/>
+      <c r="A488" s="13"/>
+      <c r="B488" s="11"/>
+      <c r="C488" s="11"/>
     </row>
     <row r="489" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A489" s="19"/>
-      <c r="B489" s="17"/>
-      <c r="C489" s="17"/>
+      <c r="A489" s="13"/>
+      <c r="B489" s="11"/>
+      <c r="C489" s="11"/>
     </row>
     <row r="490" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A490" s="19"/>
-      <c r="B490" s="17"/>
-      <c r="C490" s="17"/>
+      <c r="A490" s="13"/>
+      <c r="B490" s="11"/>
+      <c r="C490" s="11"/>
     </row>
     <row r="491" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A491" s="19"/>
-      <c r="B491" s="17"/>
-      <c r="C491" s="17"/>
+      <c r="A491" s="13"/>
+      <c r="B491" s="11"/>
+      <c r="C491" s="11"/>
     </row>
     <row r="492" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A492" s="19"/>
-      <c r="B492" s="17"/>
-      <c r="C492" s="17"/>
+      <c r="A492" s="13"/>
+      <c r="B492" s="11"/>
+      <c r="C492" s="11"/>
     </row>
     <row r="493" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A493" s="19"/>
-      <c r="B493" s="17"/>
-      <c r="C493" s="17"/>
+      <c r="A493" s="13"/>
+      <c r="B493" s="11"/>
+      <c r="C493" s="11"/>
     </row>
     <row r="494" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A494" s="19"/>
-      <c r="B494" s="17"/>
-      <c r="C494" s="17"/>
+      <c r="A494" s="13"/>
+      <c r="B494" s="11"/>
+      <c r="C494" s="11"/>
     </row>
     <row r="495" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A495" s="19"/>
-      <c r="B495" s="17"/>
-      <c r="C495" s="17"/>
+      <c r="A495" s="13"/>
+      <c r="B495" s="11"/>
+      <c r="C495" s="11"/>
     </row>
     <row r="496" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A496" s="19"/>
-      <c r="B496" s="17"/>
-      <c r="C496" s="17"/>
+      <c r="A496" s="13"/>
+      <c r="B496" s="11"/>
+      <c r="C496" s="11"/>
     </row>
     <row r="497" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A497" s="19"/>
-      <c r="B497" s="17"/>
-      <c r="C497" s="17"/>
+      <c r="A497" s="13"/>
+      <c r="B497" s="11"/>
+      <c r="C497" s="11"/>
     </row>
     <row r="498" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A498" s="19"/>
-      <c r="B498" s="17"/>
-      <c r="C498" s="17"/>
+      <c r="A498" s="13"/>
+      <c r="B498" s="11"/>
+      <c r="C498" s="11"/>
     </row>
     <row r="499" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A499" s="19"/>
-      <c r="B499" s="17"/>
-      <c r="C499" s="17"/>
+      <c r="A499" s="13"/>
+      <c r="B499" s="11"/>
+      <c r="C499" s="11"/>
     </row>
     <row r="500" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A500" s="19"/>
-      <c r="B500" s="17"/>
-      <c r="C500" s="17"/>
+      <c r="A500" s="13"/>
+      <c r="B500" s="11"/>
+      <c r="C500" s="11"/>
     </row>
     <row r="501" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A501" s="19"/>
-      <c r="B501" s="17"/>
-      <c r="C501" s="17"/>
+      <c r="A501" s="13"/>
+      <c r="B501" s="11"/>
+      <c r="C501" s="11"/>
     </row>
     <row r="502" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A502" s="19"/>
-      <c r="B502" s="17"/>
-      <c r="C502" s="17"/>
+      <c r="A502" s="13"/>
+      <c r="B502" s="11"/>
+      <c r="C502" s="11"/>
     </row>
     <row r="503" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A503" s="19"/>
-      <c r="B503" s="17"/>
-      <c r="C503" s="17"/>
+      <c r="A503" s="13"/>
+      <c r="B503" s="11"/>
+      <c r="C503" s="11"/>
     </row>
     <row r="504" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A504" s="19"/>
-      <c r="B504" s="17"/>
-      <c r="C504" s="17"/>
+      <c r="A504" s="13"/>
+      <c r="B504" s="11"/>
+      <c r="C504" s="11"/>
     </row>
     <row r="505" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A505" s="19"/>
-      <c r="B505" s="17"/>
-      <c r="C505" s="17"/>
+      <c r="A505" s="13"/>
+      <c r="B505" s="11"/>
+      <c r="C505" s="11"/>
     </row>
     <row r="506" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A506" s="19"/>
-      <c r="B506" s="17"/>
-      <c r="C506" s="17"/>
+      <c r="A506" s="13"/>
+      <c r="B506" s="11"/>
+      <c r="C506" s="11"/>
     </row>
     <row r="507" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A507" s="19"/>
-      <c r="B507" s="17"/>
-      <c r="C507" s="17"/>
+      <c r="A507" s="13"/>
+      <c r="B507" s="11"/>
+      <c r="C507" s="11"/>
     </row>
     <row r="508" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A508" s="19"/>
-      <c r="B508" s="17"/>
-      <c r="C508" s="17"/>
+      <c r="A508" s="13"/>
+      <c r="B508" s="11"/>
+      <c r="C508" s="11"/>
     </row>
     <row r="509" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A509" s="19"/>
-      <c r="B509" s="17"/>
-      <c r="C509" s="17"/>
+      <c r="A509" s="13"/>
+      <c r="B509" s="11"/>
+      <c r="C509" s="11"/>
     </row>
     <row r="510" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A510" s="19"/>
-      <c r="B510" s="17"/>
-      <c r="C510" s="17"/>
+      <c r="A510" s="13"/>
+      <c r="B510" s="11"/>
+      <c r="C510" s="11"/>
     </row>
     <row r="511" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A511" s="19"/>
-      <c r="B511" s="17"/>
-      <c r="C511" s="17"/>
+      <c r="A511" s="13"/>
+      <c r="B511" s="11"/>
+      <c r="C511" s="11"/>
     </row>
     <row r="512" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A512" s="19"/>
-      <c r="B512" s="17"/>
-      <c r="C512" s="17"/>
+      <c r="A512" s="13"/>
+      <c r="B512" s="11"/>
+      <c r="C512" s="11"/>
     </row>
     <row r="513" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A513" s="19"/>
-      <c r="B513" s="17"/>
-      <c r="C513" s="17"/>
+      <c r="A513" s="13"/>
+      <c r="B513" s="11"/>
+      <c r="C513" s="11"/>
     </row>
     <row r="514" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A514" s="19"/>
-      <c r="B514" s="17"/>
-      <c r="C514" s="17"/>
+      <c r="A514" s="13"/>
+      <c r="B514" s="11"/>
+      <c r="C514" s="11"/>
     </row>
     <row r="515" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A515" s="19"/>
-      <c r="B515" s="17"/>
-      <c r="C515" s="17"/>
+      <c r="A515" s="13"/>
+      <c r="B515" s="11"/>
+      <c r="C515" s="11"/>
     </row>
     <row r="516" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A516" s="19"/>
-      <c r="B516" s="17"/>
-      <c r="C516" s="17"/>
+      <c r="A516" s="13"/>
+      <c r="B516" s="11"/>
+      <c r="C516" s="11"/>
     </row>
     <row r="517" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A517" s="19"/>
-      <c r="B517" s="17"/>
-      <c r="C517" s="17"/>
+      <c r="A517" s="13"/>
+      <c r="B517" s="11"/>
+      <c r="C517" s="11"/>
     </row>
     <row r="518" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A518" s="19"/>
-      <c r="B518" s="17"/>
-      <c r="C518" s="17"/>
+      <c r="A518" s="13"/>
+      <c r="B518" s="11"/>
+      <c r="C518" s="11"/>
     </row>
     <row r="519" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A519" s="19"/>
-      <c r="B519" s="17"/>
-      <c r="C519" s="17"/>
+      <c r="A519" s="13"/>
+      <c r="B519" s="11"/>
+      <c r="C519" s="11"/>
     </row>
     <row r="520" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A520" s="19"/>
-      <c r="B520" s="17"/>
-      <c r="C520" s="17"/>
+      <c r="A520" s="13"/>
+      <c r="B520" s="11"/>
+      <c r="C520" s="11"/>
     </row>
     <row r="521" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A521" s="19"/>
-      <c r="B521" s="17"/>
-      <c r="C521" s="17"/>
+      <c r="A521" s="13"/>
+      <c r="B521" s="11"/>
+      <c r="C521" s="11"/>
     </row>
     <row r="522" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A522" s="19"/>
-      <c r="B522" s="17"/>
-      <c r="C522" s="17"/>
+      <c r="A522" s="13"/>
+      <c r="B522" s="11"/>
+      <c r="C522" s="11"/>
     </row>
     <row r="523" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A523" s="19"/>
-      <c r="B523" s="17"/>
-      <c r="C523" s="17"/>
+      <c r="A523" s="13"/>
+      <c r="B523" s="11"/>
+      <c r="C523" s="11"/>
     </row>
     <row r="524" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A524" s="19"/>
-      <c r="B524" s="17"/>
-      <c r="C524" s="17"/>
+      <c r="A524" s="13"/>
+      <c r="B524" s="11"/>
+      <c r="C524" s="11"/>
     </row>
     <row r="525" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A525" s="19"/>
-      <c r="B525" s="17"/>
-      <c r="C525" s="17"/>
+      <c r="A525" s="13"/>
+      <c r="B525" s="11"/>
+      <c r="C525" s="11"/>
     </row>
     <row r="526" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A526" s="19"/>
-      <c r="B526" s="17"/>
-      <c r="C526" s="17"/>
+      <c r="A526" s="13"/>
+      <c r="B526" s="11"/>
+      <c r="C526" s="11"/>
     </row>
     <row r="527" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A527" s="19"/>
-      <c r="B527" s="17"/>
-      <c r="C527" s="17"/>
+      <c r="A527" s="13"/>
+      <c r="B527" s="11"/>
+      <c r="C527" s="11"/>
     </row>
     <row r="528" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A528" s="19"/>
-      <c r="B528" s="17"/>
-      <c r="C528" s="17"/>
+      <c r="A528" s="13"/>
+      <c r="B528" s="11"/>
+      <c r="C528" s="11"/>
     </row>
     <row r="529" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A529" s="19"/>
-      <c r="B529" s="17"/>
-      <c r="C529" s="17"/>
+      <c r="A529" s="13"/>
+      <c r="B529" s="11"/>
+      <c r="C529" s="11"/>
     </row>
     <row r="530" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A530" s="19"/>
-      <c r="B530" s="17"/>
-      <c r="C530" s="17"/>
+      <c r="A530" s="13"/>
+      <c r="B530" s="11"/>
+      <c r="C530" s="11"/>
     </row>
     <row r="531" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A531" s="19"/>
-      <c r="B531" s="17"/>
-      <c r="C531" s="17"/>
+      <c r="A531" s="13"/>
+      <c r="B531" s="11"/>
+      <c r="C531" s="11"/>
     </row>
     <row r="532" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A532" s="19"/>
-      <c r="B532" s="17"/>
-      <c r="C532" s="17"/>
+      <c r="A532" s="13"/>
+      <c r="B532" s="11"/>
+      <c r="C532" s="11"/>
     </row>
     <row r="533" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A533" s="19"/>
-      <c r="B533" s="17"/>
-      <c r="C533" s="17"/>
+      <c r="A533" s="13"/>
+      <c r="B533" s="11"/>
+      <c r="C533" s="11"/>
     </row>
     <row r="534" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A534" s="19"/>
-      <c r="B534" s="17"/>
-      <c r="C534" s="17"/>
+      <c r="A534" s="13"/>
+      <c r="B534" s="11"/>
+      <c r="C534" s="11"/>
     </row>
     <row r="535" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A535" s="19"/>
-      <c r="B535" s="17"/>
-      <c r="C535" s="17"/>
+      <c r="A535" s="13"/>
+      <c r="B535" s="11"/>
+      <c r="C535" s="11"/>
     </row>
     <row r="536" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A536" s="19"/>
-      <c r="B536" s="17"/>
-      <c r="C536" s="17"/>
+      <c r="A536" s="13"/>
+      <c r="B536" s="11"/>
+      <c r="C536" s="11"/>
     </row>
     <row r="537" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A537" s="19"/>
-      <c r="B537" s="17"/>
-      <c r="C537" s="17"/>
+      <c r="A537" s="13"/>
+      <c r="B537" s="11"/>
+      <c r="C537" s="11"/>
     </row>
     <row r="538" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A538" s="19"/>
-      <c r="B538" s="17"/>
-      <c r="C538" s="17"/>
+      <c r="A538" s="13"/>
+      <c r="B538" s="11"/>
+      <c r="C538" s="11"/>
     </row>
     <row r="539" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A539" s="19"/>
-      <c r="B539" s="17"/>
-      <c r="C539" s="17"/>
+      <c r="A539" s="13"/>
+      <c r="B539" s="11"/>
+      <c r="C539" s="11"/>
     </row>
     <row r="540" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A540" s="19"/>
-      <c r="B540" s="17"/>
-      <c r="C540" s="17"/>
+      <c r="A540" s="13"/>
+      <c r="B540" s="11"/>
+      <c r="C540" s="11"/>
     </row>
     <row r="541" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A541" s="19"/>
-      <c r="B541" s="17"/>
-      <c r="C541" s="17"/>
+      <c r="A541" s="13"/>
+      <c r="B541" s="11"/>
+      <c r="C541" s="11"/>
     </row>
     <row r="542" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A542" s="19"/>
-      <c r="B542" s="17"/>
-      <c r="C542" s="17"/>
+      <c r="A542" s="13"/>
+      <c r="B542" s="11"/>
+      <c r="C542" s="11"/>
     </row>
     <row r="543" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A543" s="19"/>
-      <c r="B543" s="17"/>
-      <c r="C543" s="17"/>
+      <c r="A543" s="13"/>
+      <c r="B543" s="11"/>
+      <c r="C543" s="11"/>
     </row>
     <row r="544" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A544" s="19"/>
-      <c r="B544" s="17"/>
-      <c r="C544" s="17"/>
+      <c r="A544" s="13"/>
+      <c r="B544" s="11"/>
+      <c r="C544" s="11"/>
     </row>
     <row r="545" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A545" s="19"/>
-      <c r="B545" s="17"/>
-      <c r="C545" s="17"/>
+      <c r="A545" s="13"/>
+      <c r="B545" s="11"/>
+      <c r="C545" s="11"/>
     </row>
     <row r="546" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A546" s="19"/>
-      <c r="B546" s="17"/>
-      <c r="C546" s="17"/>
+      <c r="A546" s="13"/>
+      <c r="B546" s="11"/>
+      <c r="C546" s="11"/>
     </row>
     <row r="547" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A547" s="19"/>
-      <c r="B547" s="17"/>
-      <c r="C547" s="17"/>
+      <c r="A547" s="13"/>
+      <c r="B547" s="11"/>
+      <c r="C547" s="11"/>
     </row>
     <row r="548" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A548" s="19"/>
-      <c r="B548" s="17"/>
-      <c r="C548" s="17"/>
+      <c r="A548" s="13"/>
+      <c r="B548" s="11"/>
+      <c r="C548" s="11"/>
     </row>
     <row r="549" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A549" s="19"/>
-      <c r="B549" s="17"/>
-      <c r="C549" s="17"/>
+      <c r="A549" s="13"/>
+      <c r="B549" s="11"/>
+      <c r="C549" s="11"/>
     </row>
     <row r="550" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A550" s="19"/>
-      <c r="B550" s="17"/>
-      <c r="C550" s="17"/>
+      <c r="A550" s="13"/>
+      <c r="B550" s="11"/>
+      <c r="C550" s="11"/>
     </row>
     <row r="551" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A551" s="19"/>
-      <c r="B551" s="17"/>
-      <c r="C551" s="17"/>
+      <c r="A551" s="13"/>
+      <c r="B551" s="11"/>
+      <c r="C551" s="11"/>
     </row>
     <row r="552" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A552" s="19"/>
-      <c r="B552" s="17"/>
-      <c r="C552" s="17"/>
+      <c r="A552" s="13"/>
+      <c r="B552" s="11"/>
+      <c r="C552" s="11"/>
     </row>
     <row r="553" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A553" s="19"/>
-      <c r="B553" s="17"/>
-      <c r="C553" s="17"/>
+      <c r="A553" s="13"/>
+      <c r="B553" s="11"/>
+      <c r="C553" s="11"/>
     </row>
     <row r="554" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A554" s="19"/>
-      <c r="B554" s="17"/>
-      <c r="C554" s="17"/>
+      <c r="A554" s="13"/>
+      <c r="B554" s="11"/>
+      <c r="C554" s="11"/>
     </row>
     <row r="555" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A555" s="19"/>
-      <c r="B555" s="17"/>
-      <c r="C555" s="17"/>
+      <c r="A555" s="13"/>
+      <c r="B555" s="11"/>
+      <c r="C555" s="11"/>
     </row>
     <row r="556" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A556" s="19"/>
-      <c r="B556" s="17"/>
-      <c r="C556" s="17"/>
+      <c r="A556" s="13"/>
+      <c r="B556" s="11"/>
+      <c r="C556" s="11"/>
     </row>
     <row r="557" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A557" s="19"/>
-      <c r="B557" s="17"/>
-      <c r="C557" s="17"/>
+      <c r="A557" s="13"/>
+      <c r="B557" s="11"/>
+      <c r="C557" s="11"/>
     </row>
     <row r="558" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A558" s="19"/>
-      <c r="B558" s="17"/>
-      <c r="C558" s="17"/>
+      <c r="A558" s="13"/>
+      <c r="B558" s="11"/>
+      <c r="C558" s="11"/>
     </row>
     <row r="559" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A559" s="19"/>
-      <c r="B559" s="17"/>
-      <c r="C559" s="17"/>
+      <c r="A559" s="13"/>
+      <c r="B559" s="11"/>
+      <c r="C559" s="11"/>
     </row>
     <row r="560" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A560" s="19"/>
-      <c r="B560" s="17"/>
-      <c r="C560" s="17"/>
+      <c r="A560" s="13"/>
+      <c r="B560" s="11"/>
+      <c r="C560" s="11"/>
     </row>
     <row r="561" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A561" s="19"/>
-      <c r="B561" s="17"/>
-      <c r="C561" s="17"/>
+      <c r="A561" s="13"/>
+      <c r="B561" s="11"/>
+      <c r="C561" s="11"/>
     </row>
     <row r="562" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A562" s="19"/>
-      <c r="B562" s="17"/>
-      <c r="C562" s="17"/>
+      <c r="A562" s="13"/>
+      <c r="B562" s="11"/>
+      <c r="C562" s="11"/>
     </row>
     <row r="563" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A563" s="19"/>
-      <c r="B563" s="17"/>
-      <c r="C563" s="17"/>
+      <c r="A563" s="13"/>
+      <c r="B563" s="11"/>
+      <c r="C563" s="11"/>
     </row>
     <row r="564" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A564" s="19"/>
-      <c r="B564" s="17"/>
-      <c r="C564" s="17"/>
+      <c r="A564" s="13"/>
+      <c r="B564" s="11"/>
+      <c r="C564" s="11"/>
     </row>
     <row r="565" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A565" s="19"/>
-      <c r="B565" s="17"/>
-      <c r="C565" s="17"/>
+      <c r="A565" s="13"/>
+      <c r="B565" s="11"/>
+      <c r="C565" s="11"/>
     </row>
     <row r="566" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A566" s="19"/>
-      <c r="B566" s="17"/>
-      <c r="C566" s="17"/>
+      <c r="A566" s="13"/>
+      <c r="B566" s="11"/>
+      <c r="C566" s="11"/>
     </row>
     <row r="567" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A567" s="19"/>
-      <c r="B567" s="17"/>
-      <c r="C567" s="17"/>
+      <c r="A567" s="13"/>
+      <c r="B567" s="11"/>
+      <c r="C567" s="11"/>
     </row>
     <row r="568" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A568" s="19"/>
-      <c r="B568" s="17"/>
-      <c r="C568" s="17"/>
+      <c r="A568" s="13"/>
+      <c r="B568" s="11"/>
+      <c r="C568" s="11"/>
     </row>
     <row r="569" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A569" s="19"/>
-      <c r="B569" s="17"/>
-      <c r="C569" s="17"/>
+      <c r="A569" s="13"/>
+      <c r="B569" s="11"/>
+      <c r="C569" s="11"/>
     </row>
     <row r="570" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A570" s="19"/>
-      <c r="B570" s="17"/>
-      <c r="C570" s="17"/>
+      <c r="A570" s="13"/>
+      <c r="B570" s="11"/>
+      <c r="C570" s="11"/>
     </row>
     <row r="571" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A571" s="19"/>
-      <c r="B571" s="17"/>
-      <c r="C571" s="17"/>
+      <c r="A571" s="13"/>
+      <c r="B571" s="11"/>
+      <c r="C571" s="11"/>
     </row>
     <row r="572" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A572" s="19"/>
-      <c r="B572" s="17"/>
-      <c r="C572" s="17"/>
+      <c r="A572" s="13"/>
+      <c r="B572" s="11"/>
+      <c r="C572" s="11"/>
     </row>
     <row r="573" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A573" s="19"/>
-      <c r="B573" s="17"/>
-      <c r="C573" s="17"/>
+      <c r="A573" s="13"/>
+      <c r="B573" s="11"/>
+      <c r="C573" s="11"/>
     </row>
     <row r="574" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A574" s="19"/>
-      <c r="B574" s="17"/>
-      <c r="C574" s="17"/>
+      <c r="A574" s="13"/>
+      <c r="B574" s="11"/>
+      <c r="C574" s="11"/>
     </row>
     <row r="575" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A575" s="19"/>
-      <c r="B575" s="17"/>
-      <c r="C575" s="17"/>
+      <c r="A575" s="13"/>
+      <c r="B575" s="11"/>
+      <c r="C575" s="11"/>
     </row>
     <row r="576" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A576" s="19"/>
-      <c r="B576" s="17"/>
-      <c r="C576" s="17"/>
+      <c r="A576" s="13"/>
+      <c r="B576" s="11"/>
+      <c r="C576" s="11"/>
     </row>
     <row r="577" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A577" s="19"/>
-      <c r="B577" s="17"/>
-      <c r="C577" s="17"/>
+      <c r="A577" s="13"/>
+      <c r="B577" s="11"/>
+      <c r="C577" s="11"/>
     </row>
     <row r="578" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A578" s="19"/>
-      <c r="B578" s="17"/>
-      <c r="C578" s="17"/>
+      <c r="A578" s="13"/>
+      <c r="B578" s="11"/>
+      <c r="C578" s="11"/>
     </row>
     <row r="579" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A579" s="19"/>
-      <c r="B579" s="17"/>
-      <c r="C579" s="17"/>
+      <c r="A579" s="13"/>
+      <c r="B579" s="11"/>
+      <c r="C579" s="11"/>
     </row>
     <row r="580" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A580" s="19"/>
-      <c r="B580" s="17"/>
-      <c r="C580" s="17"/>
+      <c r="A580" s="13"/>
+      <c r="B580" s="11"/>
+      <c r="C580" s="11"/>
     </row>
     <row r="581" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A581" s="19"/>
-      <c r="B581" s="17"/>
-      <c r="C581" s="17"/>
+      <c r="A581" s="13"/>
+      <c r="B581" s="11"/>
+      <c r="C581" s="11"/>
     </row>
     <row r="582" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A582" s="19"/>
-      <c r="B582" s="17"/>
-      <c r="C582" s="17"/>
+      <c r="A582" s="13"/>
+      <c r="B582" s="11"/>
+      <c r="C582" s="11"/>
     </row>
     <row r="583" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A583" s="19"/>
-      <c r="B583" s="17"/>
-      <c r="C583" s="17"/>
+      <c r="A583" s="13"/>
+      <c r="B583" s="11"/>
+      <c r="C583" s="11"/>
     </row>
     <row r="584" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A584" s="19"/>
-      <c r="B584" s="17"/>
-      <c r="C584" s="17"/>
+      <c r="A584" s="13"/>
+      <c r="B584" s="11"/>
+      <c r="C584" s="11"/>
     </row>
     <row r="585" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A585" s="19"/>
-      <c r="B585" s="17"/>
-      <c r="C585" s="17"/>
+      <c r="A585" s="13"/>
+      <c r="B585" s="11"/>
+      <c r="C585" s="11"/>
     </row>
     <row r="586" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A586" s="19"/>
-      <c r="B586" s="17"/>
-      <c r="C586" s="17"/>
+      <c r="A586" s="13"/>
+      <c r="B586" s="11"/>
+      <c r="C586" s="11"/>
     </row>
     <row r="587" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A587" s="19"/>
-      <c r="B587" s="17"/>
-      <c r="C587" s="17"/>
+      <c r="A587" s="13"/>
+      <c r="B587" s="11"/>
+      <c r="C587" s="11"/>
     </row>
     <row r="588" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A588" s="19"/>
-      <c r="B588" s="17"/>
-      <c r="C588" s="17"/>
+      <c r="A588" s="13"/>
+      <c r="B588" s="11"/>
+      <c r="C588" s="11"/>
     </row>
     <row r="589" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A589" s="19"/>
-      <c r="B589" s="17"/>
-      <c r="C589" s="17"/>
+      <c r="A589" s="13"/>
+      <c r="B589" s="11"/>
+      <c r="C589" s="11"/>
     </row>
     <row r="590" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A590" s="19"/>
-      <c r="B590" s="17"/>
-      <c r="C590" s="17"/>
+      <c r="A590" s="13"/>
+      <c r="B590" s="11"/>
+      <c r="C590" s="11"/>
     </row>
     <row r="591" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A591" s="19"/>
-      <c r="B591" s="17"/>
-      <c r="C591" s="17"/>
+      <c r="A591" s="13"/>
+      <c r="B591" s="11"/>
+      <c r="C591" s="11"/>
     </row>
     <row r="592" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A592" s="19"/>
-      <c r="B592" s="17"/>
-      <c r="C592" s="17"/>
+      <c r="A592" s="13"/>
+      <c r="B592" s="11"/>
+      <c r="C592" s="11"/>
     </row>
     <row r="593" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A593" s="19"/>
-      <c r="B593" s="17"/>
-      <c r="C593" s="17"/>
+      <c r="A593" s="13"/>
+      <c r="B593" s="11"/>
+      <c r="C593" s="11"/>
     </row>
     <row r="594" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A594" s="19"/>
-      <c r="B594" s="17"/>
-      <c r="C594" s="17"/>
+      <c r="A594" s="13"/>
+      <c r="B594" s="11"/>
+      <c r="C594" s="11"/>
     </row>
     <row r="595" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A595" s="19"/>
-      <c r="B595" s="17"/>
-      <c r="C595" s="17"/>
+      <c r="A595" s="13"/>
+      <c r="B595" s="11"/>
+      <c r="C595" s="11"/>
     </row>
     <row r="596" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A596" s="19"/>
-      <c r="B596" s="17"/>
-      <c r="C596" s="17"/>
+      <c r="A596" s="13"/>
+      <c r="B596" s="11"/>
+      <c r="C596" s="11"/>
     </row>
     <row r="597" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A597" s="19"/>
-      <c r="B597" s="17"/>
-      <c r="C597" s="17"/>
+      <c r="A597" s="13"/>
+      <c r="B597" s="11"/>
+      <c r="C597" s="11"/>
     </row>
     <row r="598" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A598" s="19"/>
-      <c r="B598" s="17"/>
-      <c r="C598" s="17"/>
+      <c r="A598" s="13"/>
+      <c r="B598" s="11"/>
+      <c r="C598" s="11"/>
     </row>
     <row r="599" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A599" s="19"/>
-      <c r="B599" s="17"/>
-      <c r="C599" s="17"/>
+      <c r="A599" s="13"/>
+      <c r="B599" s="11"/>
+      <c r="C599" s="11"/>
     </row>
     <row r="600" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A600" s="19"/>
-      <c r="B600" s="17"/>
-      <c r="C600" s="17"/>
+      <c r="A600" s="13"/>
+      <c r="B600" s="11"/>
+      <c r="C600" s="11"/>
     </row>
     <row r="601" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A601" s="19"/>
-      <c r="B601" s="17"/>
-      <c r="C601" s="17"/>
+      <c r="A601" s="13"/>
+      <c r="B601" s="11"/>
+      <c r="C601" s="11"/>
     </row>
     <row r="602" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A602" s="19"/>
-      <c r="B602" s="17"/>
-      <c r="C602" s="17"/>
+      <c r="A602" s="13"/>
+      <c r="B602" s="11"/>
+      <c r="C602" s="11"/>
     </row>
     <row r="603" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A603" s="19"/>
-      <c r="B603" s="17"/>
-      <c r="C603" s="17"/>
+      <c r="A603" s="13"/>
+      <c r="B603" s="11"/>
+      <c r="C603" s="11"/>
     </row>
     <row r="604" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A604" s="19"/>
-      <c r="B604" s="17"/>
-      <c r="C604" s="17"/>
+      <c r="A604" s="13"/>
+      <c r="B604" s="11"/>
+      <c r="C604" s="11"/>
     </row>
     <row r="605" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A605" s="19"/>
-      <c r="B605" s="17"/>
-      <c r="C605" s="17"/>
+      <c r="A605" s="13"/>
+      <c r="B605" s="11"/>
+      <c r="C605" s="11"/>
     </row>
     <row r="606" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A606" s="19"/>
-      <c r="B606" s="17"/>
-      <c r="C606" s="17"/>
+      <c r="A606" s="13"/>
+      <c r="B606" s="11"/>
+      <c r="C606" s="11"/>
     </row>
     <row r="607" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A607" s="19"/>
-      <c r="B607" s="17"/>
-      <c r="C607" s="17"/>
+      <c r="A607" s="13"/>
+      <c r="B607" s="11"/>
+      <c r="C607" s="11"/>
     </row>
     <row r="608" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A608" s="19"/>
-      <c r="B608" s="17"/>
-      <c r="C608" s="17"/>
+      <c r="A608" s="13"/>
+      <c r="B608" s="11"/>
+      <c r="C608" s="11"/>
     </row>
     <row r="609" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A609" s="19"/>
-      <c r="B609" s="17"/>
-      <c r="C609" s="17"/>
+      <c r="A609" s="13"/>
+      <c r="B609" s="11"/>
+      <c r="C609" s="11"/>
     </row>
     <row r="610" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A610" s="19"/>
-      <c r="B610" s="17"/>
-      <c r="C610" s="17"/>
+      <c r="A610" s="13"/>
+      <c r="B610" s="11"/>
+      <c r="C610" s="11"/>
     </row>
     <row r="611" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A611" s="19"/>
-      <c r="B611" s="17"/>
-      <c r="C611" s="17"/>
+      <c r="A611" s="13"/>
+      <c r="B611" s="11"/>
+      <c r="C611" s="11"/>
     </row>
     <row r="612" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A612" s="19"/>
-      <c r="B612" s="17"/>
-      <c r="C612" s="17"/>
+      <c r="A612" s="13"/>
+      <c r="B612" s="11"/>
+      <c r="C612" s="11"/>
     </row>
     <row r="613" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A613" s="19"/>
-      <c r="B613" s="17"/>
-      <c r="C613" s="17"/>
+      <c r="A613" s="13"/>
+      <c r="B613" s="11"/>
+      <c r="C613" s="11"/>
     </row>
     <row r="614" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A614" s="19"/>
-      <c r="B614" s="17"/>
-      <c r="C614" s="17"/>
+      <c r="A614" s="13"/>
+      <c r="B614" s="11"/>
+      <c r="C614" s="11"/>
     </row>
     <row r="615" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A615" s="19"/>
-      <c r="B615" s="17"/>
-      <c r="C615" s="17"/>
+      <c r="A615" s="13"/>
+      <c r="B615" s="11"/>
+      <c r="C615" s="11"/>
     </row>
     <row r="616" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A616" s="19"/>
-      <c r="B616" s="17"/>
-      <c r="C616" s="17"/>
+      <c r="A616" s="13"/>
+      <c r="B616" s="11"/>
+      <c r="C616" s="11"/>
     </row>
     <row r="617" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A617" s="19"/>
-      <c r="B617" s="17"/>
-      <c r="C617" s="17"/>
+      <c r="A617" s="13"/>
+      <c r="B617" s="11"/>
+      <c r="C617" s="11"/>
     </row>
     <row r="618" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A618" s="19"/>
-      <c r="B618" s="17"/>
-      <c r="C618" s="17"/>
+      <c r="A618" s="13"/>
+      <c r="B618" s="11"/>
+      <c r="C618" s="11"/>
     </row>
     <row r="619" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A619" s="19"/>
-      <c r="B619" s="17"/>
-      <c r="C619" s="17"/>
+      <c r="A619" s="13"/>
+      <c r="B619" s="11"/>
+      <c r="C619" s="11"/>
     </row>
     <row r="620" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A620" s="19"/>
-      <c r="B620" s="17"/>
-      <c r="C620" s="17"/>
+      <c r="A620" s="13"/>
+      <c r="B620" s="11"/>
+      <c r="C620" s="11"/>
     </row>
     <row r="621" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A621" s="19"/>
-      <c r="B621" s="17"/>
-      <c r="C621" s="17"/>
+      <c r="A621" s="13"/>
+      <c r="B621" s="11"/>
+      <c r="C621" s="11"/>
     </row>
     <row r="622" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A622" s="19"/>
-      <c r="B622" s="17"/>
-      <c r="C622" s="17"/>
+      <c r="A622" s="13"/>
+      <c r="B622" s="11"/>
+      <c r="C622" s="11"/>
     </row>
     <row r="623" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A623" s="19"/>
-      <c r="B623" s="17"/>
-      <c r="C623" s="17"/>
+      <c r="A623" s="13"/>
+      <c r="B623" s="11"/>
+      <c r="C623" s="11"/>
     </row>
     <row r="624" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A624" s="19"/>
-      <c r="B624" s="17"/>
-      <c r="C624" s="17"/>
+      <c r="A624" s="13"/>
+      <c r="B624" s="11"/>
+      <c r="C624" s="11"/>
     </row>
     <row r="625" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A625" s="19"/>
-      <c r="B625" s="17"/>
-      <c r="C625" s="17"/>
+      <c r="A625" s="13"/>
+      <c r="B625" s="11"/>
+      <c r="C625" s="11"/>
     </row>
     <row r="626" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A626" s="19"/>
-      <c r="B626" s="17"/>
-      <c r="C626" s="17"/>
+      <c r="A626" s="13"/>
+      <c r="B626" s="11"/>
+      <c r="C626" s="11"/>
     </row>
     <row r="627" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A627" s="19"/>
-      <c r="B627" s="17"/>
-      <c r="C627" s="17"/>
+      <c r="A627" s="13"/>
+      <c r="B627" s="11"/>
+      <c r="C627" s="11"/>
     </row>
     <row r="628" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A628" s="19"/>
-      <c r="B628" s="17"/>
-      <c r="C628" s="17"/>
+      <c r="A628" s="13"/>
+      <c r="B628" s="11"/>
+      <c r="C628" s="11"/>
     </row>
     <row r="629" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A629" s="19"/>
-      <c r="B629" s="17"/>
-      <c r="C629" s="17"/>
+      <c r="A629" s="13"/>
+      <c r="B629" s="11"/>
+      <c r="C629" s="11"/>
     </row>
     <row r="630" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A630" s="19"/>
-      <c r="B630" s="17"/>
-      <c r="C630" s="17"/>
+      <c r="A630" s="13"/>
+      <c r="B630" s="11"/>
+      <c r="C630" s="11"/>
     </row>
     <row r="631" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A631" s="19"/>
-      <c r="B631" s="17"/>
-      <c r="C631" s="17"/>
+      <c r="A631" s="13"/>
+      <c r="B631" s="11"/>
+      <c r="C631" s="11"/>
     </row>
     <row r="632" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A632" s="19"/>
-      <c r="B632" s="17"/>
-      <c r="C632" s="17"/>
+      <c r="A632" s="13"/>
+      <c r="B632" s="11"/>
+      <c r="C632" s="11"/>
     </row>
     <row r="633" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A633" s="19"/>
-      <c r="B633" s="17"/>
-      <c r="C633" s="17"/>
+      <c r="A633" s="13"/>
+      <c r="B633" s="11"/>
+      <c r="C633" s="11"/>
     </row>
     <row r="634" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A634" s="19"/>
-      <c r="B634" s="17"/>
-      <c r="C634" s="17"/>
+      <c r="A634" s="13"/>
+      <c r="B634" s="11"/>
+      <c r="C634" s="11"/>
     </row>
     <row r="635" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A635" s="19"/>
-      <c r="B635" s="17"/>
-      <c r="C635" s="17"/>
+      <c r="A635" s="13"/>
+      <c r="B635" s="11"/>
+      <c r="C635" s="11"/>
     </row>
     <row r="636" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A636" s="19"/>
-      <c r="B636" s="17"/>
-      <c r="C636" s="17"/>
+      <c r="A636" s="13"/>
+      <c r="B636" s="11"/>
+      <c r="C636" s="11"/>
     </row>
     <row r="637" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A637" s="19"/>
-      <c r="B637" s="17"/>
-      <c r="C637" s="17"/>
+      <c r="A637" s="13"/>
+      <c r="B637" s="11"/>
+      <c r="C637" s="11"/>
     </row>
     <row r="638" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A638" s="19"/>
-      <c r="B638" s="17"/>
-      <c r="C638" s="17"/>
+      <c r="A638" s="13"/>
+      <c r="B638" s="11"/>
+      <c r="C638" s="11"/>
     </row>
     <row r="639" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A639" s="19"/>
-      <c r="B639" s="17"/>
-      <c r="C639" s="17"/>
+      <c r="A639" s="13"/>
+      <c r="B639" s="11"/>
+      <c r="C639" s="11"/>
     </row>
     <row r="640" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A640" s="19"/>
-      <c r="B640" s="17"/>
-      <c r="C640" s="17"/>
+      <c r="A640" s="13"/>
+      <c r="B640" s="11"/>
+      <c r="C640" s="11"/>
     </row>
     <row r="641" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A641" s="19"/>
-      <c r="B641" s="17"/>
-      <c r="C641" s="17"/>
+      <c r="A641" s="13"/>
+      <c r="B641" s="11"/>
+      <c r="C641" s="11"/>
     </row>
     <row r="642" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A642" s="19"/>
-      <c r="B642" s="17"/>
-      <c r="C642" s="17"/>
+      <c r="A642" s="13"/>
+      <c r="B642" s="11"/>
+      <c r="C642" s="11"/>
     </row>
     <row r="643" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A643" s="19"/>
-      <c r="B643" s="17"/>
-      <c r="C643" s="17"/>
+      <c r="A643" s="13"/>
+      <c r="B643" s="11"/>
+      <c r="C643" s="11"/>
     </row>
     <row r="644" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A644" s="19"/>
-      <c r="B644" s="17"/>
-      <c r="C644" s="17"/>
+      <c r="A644" s="13"/>
+      <c r="B644" s="11"/>
+      <c r="C644" s="11"/>
     </row>
     <row r="645" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A645" s="19"/>
-      <c r="B645" s="17"/>
-      <c r="C645" s="17"/>
+      <c r="A645" s="13"/>
+      <c r="B645" s="11"/>
+      <c r="C645" s="11"/>
     </row>
     <row r="646" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A646" s="19"/>
-      <c r="B646" s="17"/>
-      <c r="C646" s="17"/>
+      <c r="A646" s="13"/>
+      <c r="B646" s="11"/>
+      <c r="C646" s="11"/>
     </row>
     <row r="647" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A647" s="19"/>
-      <c r="B647" s="17"/>
-      <c r="C647" s="17"/>
+      <c r="A647" s="13"/>
+      <c r="B647" s="11"/>
+      <c r="C647" s="11"/>
     </row>
     <row r="648" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A648" s="19"/>
-      <c r="B648" s="17"/>
-      <c r="C648" s="17"/>
+      <c r="A648" s="13"/>
+      <c r="B648" s="11"/>
+      <c r="C648" s="11"/>
     </row>
     <row r="649" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A649" s="19"/>
-      <c r="B649" s="17"/>
-      <c r="C649" s="17"/>
+      <c r="A649" s="13"/>
+      <c r="B649" s="11"/>
+      <c r="C649" s="11"/>
     </row>
     <row r="650" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A650" s="19"/>
-      <c r="B650" s="17"/>
-      <c r="C650" s="17"/>
+      <c r="A650" s="13"/>
+      <c r="B650" s="11"/>
+      <c r="C650" s="11"/>
     </row>
     <row r="651" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A651" s="19"/>
-      <c r="B651" s="17"/>
-      <c r="C651" s="17"/>
+      <c r="A651" s="13"/>
+      <c r="B651" s="11"/>
+      <c r="C651" s="11"/>
     </row>
     <row r="652" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A652" s="19"/>
-      <c r="B652" s="17"/>
-      <c r="C652" s="17"/>
+      <c r="A652" s="13"/>
+      <c r="B652" s="11"/>
+      <c r="C652" s="11"/>
     </row>
     <row r="653" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A653" s="19"/>
-      <c r="B653" s="17"/>
-      <c r="C653" s="17"/>
+      <c r="A653" s="13"/>
+      <c r="B653" s="11"/>
+      <c r="C653" s="11"/>
     </row>
     <row r="654" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A654" s="19"/>
-      <c r="B654" s="17"/>
-      <c r="C654" s="17"/>
+      <c r="A654" s="13"/>
+      <c r="B654" s="11"/>
+      <c r="C654" s="11"/>
     </row>
     <row r="655" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A655" s="19"/>
-      <c r="B655" s="17"/>
-      <c r="C655" s="17"/>
+      <c r="A655" s="13"/>
+      <c r="B655" s="11"/>
+      <c r="C655" s="11"/>
     </row>
     <row r="656" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A656" s="19"/>
-      <c r="B656" s="17"/>
-      <c r="C656" s="17"/>
+      <c r="A656" s="13"/>
+      <c r="B656" s="11"/>
+      <c r="C656" s="11"/>
     </row>
     <row r="657" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A657" s="19"/>
-      <c r="B657" s="17"/>
-      <c r="C657" s="17"/>
+      <c r="A657" s="13"/>
+      <c r="B657" s="11"/>
+      <c r="C657" s="11"/>
     </row>
     <row r="658" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A658" s="19"/>
-      <c r="B658" s="17"/>
-      <c r="C658" s="17"/>
+      <c r="A658" s="13"/>
+      <c r="B658" s="11"/>
+      <c r="C658" s="11"/>
     </row>
     <row r="659" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A659" s="19"/>
-      <c r="B659" s="17"/>
-      <c r="C659" s="17"/>
+      <c r="A659" s="13"/>
+      <c r="B659" s="11"/>
+      <c r="C659" s="11"/>
     </row>
     <row r="660" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A660" s="19"/>
-      <c r="B660" s="17"/>
-      <c r="C660" s="17"/>
+      <c r="A660" s="13"/>
+      <c r="B660" s="11"/>
+      <c r="C660" s="11"/>
     </row>
     <row r="661" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A661" s="19"/>
-      <c r="B661" s="17"/>
-      <c r="C661" s="17"/>
+      <c r="A661" s="13"/>
+      <c r="B661" s="11"/>
+      <c r="C661" s="11"/>
     </row>
     <row r="662" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A662" s="19"/>
-      <c r="B662" s="17"/>
-      <c r="C662" s="17"/>
+      <c r="A662" s="13"/>
+      <c r="B662" s="11"/>
+      <c r="C662" s="11"/>
     </row>
     <row r="663" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A663" s="19"/>
-      <c r="B663" s="17"/>
-      <c r="C663" s="17"/>
+      <c r="A663" s="13"/>
+      <c r="B663" s="11"/>
+      <c r="C663" s="11"/>
     </row>
     <row r="664" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A664" s="19"/>
-      <c r="B664" s="17"/>
-      <c r="C664" s="17"/>
+      <c r="A664" s="13"/>
+      <c r="B664" s="11"/>
+      <c r="C664" s="11"/>
     </row>
     <row r="665" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A665" s="19"/>
-      <c r="B665" s="17"/>
-      <c r="C665" s="17"/>
+      <c r="A665" s="13"/>
+      <c r="B665" s="11"/>
+      <c r="C665" s="11"/>
     </row>
     <row r="666" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A666" s="19"/>
-      <c r="B666" s="17"/>
-      <c r="C666" s="17"/>
+      <c r="A666" s="13"/>
+      <c r="B666" s="11"/>
+      <c r="C666" s="11"/>
     </row>
     <row r="667" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A667" s="19"/>
-      <c r="B667" s="17"/>
-      <c r="C667" s="17"/>
+      <c r="A667" s="13"/>
+      <c r="B667" s="11"/>
+      <c r="C667" s="11"/>
     </row>
     <row r="668" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A668" s="19"/>
-      <c r="B668" s="17"/>
-      <c r="C668" s="17"/>
+      <c r="A668" s="13"/>
+      <c r="B668" s="11"/>
+      <c r="C668" s="11"/>
     </row>
     <row r="669" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A669" s="19"/>
-      <c r="B669" s="17"/>
-      <c r="C669" s="17"/>
+      <c r="A669" s="13"/>
+      <c r="B669" s="11"/>
+      <c r="C669" s="11"/>
     </row>
     <row r="670" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A670" s="19"/>
-      <c r="B670" s="17"/>
-      <c r="C670" s="17"/>
+      <c r="A670" s="13"/>
+      <c r="B670" s="11"/>
+      <c r="C670" s="11"/>
     </row>
     <row r="671" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A671" s="19"/>
-      <c r="B671" s="17"/>
-      <c r="C671" s="17"/>
+      <c r="A671" s="13"/>
+      <c r="B671" s="11"/>
+      <c r="C671" s="11"/>
     </row>
     <row r="672" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A672" s="19"/>
-      <c r="B672" s="17"/>
-      <c r="C672" s="17"/>
+      <c r="A672" s="13"/>
+      <c r="B672" s="11"/>
+      <c r="C672" s="11"/>
     </row>
     <row r="673" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A673" s="19"/>
-      <c r="B673" s="17"/>
-      <c r="C673" s="17"/>
+      <c r="A673" s="13"/>
+      <c r="B673" s="11"/>
+      <c r="C673" s="11"/>
     </row>
     <row r="674" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A674" s="19"/>
-      <c r="B674" s="17"/>
-      <c r="C674" s="17"/>
+      <c r="A674" s="13"/>
+      <c r="B674" s="11"/>
+      <c r="C674" s="11"/>
     </row>
     <row r="675" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A675" s="19"/>
-      <c r="B675" s="17"/>
-      <c r="C675" s="17"/>
+      <c r="A675" s="13"/>
+      <c r="B675" s="11"/>
+      <c r="C675" s="11"/>
     </row>
     <row r="676" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A676" s="19"/>
-      <c r="B676" s="17"/>
-      <c r="C676" s="17"/>
+      <c r="A676" s="13"/>
+      <c r="B676" s="11"/>
+      <c r="C676" s="11"/>
     </row>
     <row r="677" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A677" s="19"/>
-      <c r="B677" s="17"/>
-      <c r="C677" s="17"/>
+      <c r="A677" s="13"/>
+      <c r="B677" s="11"/>
+      <c r="C677" s="11"/>
     </row>
     <row r="678" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A678" s="19"/>
-      <c r="B678" s="17"/>
-      <c r="C678" s="17"/>
+      <c r="A678" s="13"/>
+      <c r="B678" s="11"/>
+      <c r="C678" s="11"/>
     </row>
     <row r="679" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A679" s="19"/>
-      <c r="B679" s="17"/>
-      <c r="C679" s="17"/>
+      <c r="A679" s="13"/>
+      <c r="B679" s="11"/>
+      <c r="C679" s="11"/>
     </row>
     <row r="680" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A680" s="19"/>
-      <c r="B680" s="17"/>
-      <c r="C680" s="17"/>
+      <c r="A680" s="13"/>
+      <c r="B680" s="11"/>
+      <c r="C680" s="11"/>
     </row>
     <row r="681" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A681" s="19"/>
-      <c r="B681" s="17"/>
-      <c r="C681" s="17"/>
+      <c r="A681" s="13"/>
+      <c r="B681" s="11"/>
+      <c r="C681" s="11"/>
     </row>
     <row r="682" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A682" s="19"/>
-      <c r="B682" s="17"/>
-      <c r="C682" s="17"/>
+      <c r="A682" s="13"/>
+      <c r="B682" s="11"/>
+      <c r="C682" s="11"/>
     </row>
     <row r="683" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A683" s="19"/>
-      <c r="B683" s="17"/>
-      <c r="C683" s="17"/>
+      <c r="A683" s="13"/>
+      <c r="B683" s="11"/>
+      <c r="C683" s="11"/>
     </row>
     <row r="684" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A684" s="19"/>
-      <c r="B684" s="17"/>
-      <c r="C684" s="17"/>
+      <c r="A684" s="13"/>
+      <c r="B684" s="11"/>
+      <c r="C684" s="11"/>
     </row>
     <row r="685" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A685" s="19"/>
-      <c r="B685" s="17"/>
-      <c r="C685" s="17"/>
+      <c r="A685" s="13"/>
+      <c r="B685" s="11"/>
+      <c r="C685" s="11"/>
     </row>
     <row r="686" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A686" s="19"/>
-      <c r="B686" s="17"/>
-      <c r="C686" s="17"/>
+      <c r="A686" s="13"/>
+      <c r="B686" s="11"/>
+      <c r="C686" s="11"/>
     </row>
     <row r="687" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A687" s="19"/>
-      <c r="B687" s="17"/>
-      <c r="C687" s="17"/>
+      <c r="A687" s="13"/>
+      <c r="B687" s="11"/>
+      <c r="C687" s="11"/>
     </row>
     <row r="688" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A688" s="19"/>
-      <c r="B688" s="17"/>
-      <c r="C688" s="17"/>
+      <c r="A688" s="13"/>
+      <c r="B688" s="11"/>
+      <c r="C688" s="11"/>
     </row>
     <row r="689" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A689" s="19"/>
-      <c r="B689" s="17"/>
-      <c r="C689" s="17"/>
+      <c r="A689" s="13"/>
+      <c r="B689" s="11"/>
+      <c r="C689" s="11"/>
     </row>
     <row r="690" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A690" s="19"/>
-      <c r="B690" s="17"/>
-      <c r="C690" s="17"/>
+      <c r="A690" s="13"/>
+      <c r="B690" s="11"/>
+      <c r="C690" s="11"/>
     </row>
     <row r="691" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A691" s="19"/>
-      <c r="B691" s="17"/>
-      <c r="C691" s="17"/>
+      <c r="A691" s="13"/>
+      <c r="B691" s="11"/>
+      <c r="C691" s="11"/>
     </row>
     <row r="692" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A692" s="19"/>
-      <c r="B692" s="17"/>
-      <c r="C692" s="17"/>
+      <c r="A692" s="13"/>
+      <c r="B692" s="11"/>
+      <c r="C692" s="11"/>
     </row>
     <row r="693" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A693" s="19"/>
-      <c r="B693" s="17"/>
-      <c r="C693" s="17"/>
+      <c r="A693" s="13"/>
+      <c r="B693" s="11"/>
+      <c r="C693" s="11"/>
     </row>
     <row r="694" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A694" s="19"/>
-      <c r="B694" s="17"/>
-      <c r="C694" s="17"/>
+      <c r="A694" s="13"/>
+      <c r="B694" s="11"/>
+      <c r="C694" s="11"/>
     </row>
     <row r="695" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A695" s="19"/>
-      <c r="B695" s="17"/>
-      <c r="C695" s="17"/>
+      <c r="A695" s="13"/>
+      <c r="B695" s="11"/>
+      <c r="C695" s="11"/>
     </row>
     <row r="696" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A696" s="19"/>
-      <c r="B696" s="17"/>
-      <c r="C696" s="17"/>
+      <c r="A696" s="13"/>
+      <c r="B696" s="11"/>
+      <c r="C696" s="11"/>
     </row>
     <row r="697" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A697" s="19"/>
-      <c r="B697" s="17"/>
-      <c r="C697" s="17"/>
+      <c r="A697" s="13"/>
+      <c r="B697" s="11"/>
+      <c r="C697" s="11"/>
     </row>
     <row r="698" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A698" s="19"/>
-      <c r="B698" s="17"/>
-      <c r="C698" s="17"/>
+      <c r="A698" s="13"/>
+      <c r="B698" s="11"/>
+      <c r="C698" s="11"/>
     </row>
     <row r="699" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A699" s="19"/>
-      <c r="B699" s="17"/>
-      <c r="C699" s="17"/>
+      <c r="A699" s="13"/>
+      <c r="B699" s="11"/>
+      <c r="C699" s="11"/>
     </row>
     <row r="700" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A700" s="19"/>
-      <c r="B700" s="17"/>
-      <c r="C700" s="17"/>
+      <c r="A700" s="13"/>
+      <c r="B700" s="11"/>
+      <c r="C700" s="11"/>
     </row>
     <row r="701" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A701" s="19"/>
-      <c r="B701" s="17"/>
-      <c r="C701" s="17"/>
+      <c r="A701" s="13"/>
+      <c r="B701" s="11"/>
+      <c r="C701" s="11"/>
     </row>
     <row r="702" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A702" s="19"/>
-      <c r="B702" s="17"/>
-      <c r="C702" s="17"/>
+      <c r="A702" s="13"/>
+      <c r="B702" s="11"/>
+      <c r="C702" s="11"/>
     </row>
     <row r="703" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A703" s="19"/>
-      <c r="B703" s="17"/>
-      <c r="C703" s="17"/>
+      <c r="A703" s="13"/>
+      <c r="B703" s="11"/>
+      <c r="C703" s="11"/>
     </row>
     <row r="704" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A704" s="19"/>
-      <c r="B704" s="17"/>
-      <c r="C704" s="17"/>
+      <c r="A704" s="13"/>
+      <c r="B704" s="11"/>
+      <c r="C704" s="11"/>
     </row>
     <row r="705" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A705" s="19"/>
-      <c r="B705" s="17"/>
-      <c r="C705" s="17"/>
+      <c r="A705" s="13"/>
+      <c r="B705" s="11"/>
+      <c r="C705" s="11"/>
     </row>
     <row r="706" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A706" s="19"/>
-      <c r="B706" s="17"/>
-      <c r="C706" s="17"/>
+      <c r="A706" s="13"/>
+      <c r="B706" s="11"/>
+      <c r="C706" s="11"/>
     </row>
     <row r="707" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A707" s="19"/>
-      <c r="B707" s="17"/>
-      <c r="C707" s="17"/>
+      <c r="A707" s="13"/>
+      <c r="B707" s="11"/>
+      <c r="C707" s="11"/>
     </row>
     <row r="708" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A708" s="19"/>
-      <c r="B708" s="17"/>
-      <c r="C708" s="17"/>
+      <c r="A708" s="13"/>
+      <c r="B708" s="11"/>
+      <c r="C708" s="11"/>
     </row>
     <row r="709" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A709" s="19"/>
-      <c r="B709" s="17"/>
-      <c r="C709" s="17"/>
+      <c r="A709" s="13"/>
+      <c r="B709" s="11"/>
+      <c r="C709" s="11"/>
     </row>
     <row r="710" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A710" s="19"/>
-      <c r="B710" s="17"/>
-      <c r="C710" s="17"/>
+      <c r="A710" s="13"/>
+      <c r="B710" s="11"/>
+      <c r="C710" s="11"/>
     </row>
     <row r="711" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A711" s="19"/>
-      <c r="B711" s="17"/>
-      <c r="C711" s="17"/>
+      <c r="A711" s="13"/>
+      <c r="B711" s="11"/>
+      <c r="C711" s="11"/>
     </row>
     <row r="712" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A712" s="19"/>
-      <c r="B712" s="17"/>
-      <c r="C712" s="17"/>
+      <c r="A712" s="13"/>
+      <c r="B712" s="11"/>
+      <c r="C712" s="11"/>
     </row>
     <row r="713" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A713" s="19"/>
-      <c r="B713" s="17"/>
-      <c r="C713" s="17"/>
+      <c r="A713" s="13"/>
+      <c r="B713" s="11"/>
+      <c r="C713" s="11"/>
     </row>
     <row r="714" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A714" s="19"/>
-      <c r="B714" s="17"/>
-      <c r="C714" s="17"/>
+      <c r="A714" s="13"/>
+      <c r="B714" s="11"/>
+      <c r="C714" s="11"/>
     </row>
     <row r="715" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A715" s="19"/>
-      <c r="B715" s="17"/>
-      <c r="C715" s="17"/>
+      <c r="A715" s="13"/>
+      <c r="B715" s="11"/>
+      <c r="C715" s="11"/>
     </row>
     <row r="716" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A716" s="19"/>
-      <c r="B716" s="17"/>
-      <c r="C716" s="17"/>
+      <c r="A716" s="13"/>
+      <c r="B716" s="11"/>
+      <c r="C716" s="11"/>
     </row>
     <row r="717" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A717" s="19"/>
-      <c r="B717" s="17"/>
-      <c r="C717" s="17"/>
+      <c r="A717" s="13"/>
+      <c r="B717" s="11"/>
+      <c r="C717" s="11"/>
     </row>
     <row r="718" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A718" s="19"/>
-      <c r="B718" s="17"/>
-      <c r="C718" s="17"/>
+      <c r="A718" s="13"/>
+      <c r="B718" s="11"/>
+      <c r="C718" s="11"/>
     </row>
     <row r="719" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A719" s="19"/>
-      <c r="B719" s="17"/>
-      <c r="C719" s="17"/>
+      <c r="A719" s="13"/>
+      <c r="B719" s="11"/>
+      <c r="C719" s="11"/>
     </row>
     <row r="720" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A720" s="19"/>
-      <c r="B720" s="17"/>
-      <c r="C720" s="17"/>
+      <c r="A720" s="13"/>
+      <c r="B720" s="11"/>
+      <c r="C720" s="11"/>
     </row>
     <row r="721" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A721" s="19"/>
-      <c r="B721" s="17"/>
-      <c r="C721" s="17"/>
+      <c r="A721" s="13"/>
+      <c r="B721" s="11"/>
+      <c r="C721" s="11"/>
     </row>
     <row r="722" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A722" s="19"/>
-      <c r="B722" s="17"/>
-      <c r="C722" s="17"/>
+      <c r="A722" s="13"/>
+      <c r="B722" s="11"/>
+      <c r="C722" s="11"/>
     </row>
     <row r="723" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A723" s="19"/>
-      <c r="B723" s="17"/>
-      <c r="C723" s="17"/>
+      <c r="A723" s="13"/>
+      <c r="B723" s="11"/>
+      <c r="C723" s="11"/>
     </row>
     <row r="724" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A724" s="19"/>
-      <c r="B724" s="17"/>
-      <c r="C724" s="17"/>
+      <c r="A724" s="13"/>
+      <c r="B724" s="11"/>
+      <c r="C724" s="11"/>
     </row>
     <row r="725" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A725" s="19"/>
-      <c r="B725" s="17"/>
-      <c r="C725" s="17"/>
+      <c r="A725" s="13"/>
+      <c r="B725" s="11"/>
+      <c r="C725" s="11"/>
     </row>
     <row r="726" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A726" s="19"/>
-      <c r="B726" s="17"/>
-      <c r="C726" s="17"/>
+      <c r="A726" s="13"/>
+      <c r="B726" s="11"/>
+      <c r="C726" s="11"/>
     </row>
     <row r="727" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A727" s="19"/>
-      <c r="B727" s="17"/>
-      <c r="C727" s="17"/>
+      <c r="A727" s="13"/>
+      <c r="B727" s="11"/>
+      <c r="C727" s="11"/>
     </row>
     <row r="728" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A728" s="19"/>
-      <c r="B728" s="17"/>
-      <c r="C728" s="17"/>
+      <c r="A728" s="13"/>
+      <c r="B728" s="11"/>
+      <c r="C728" s="11"/>
     </row>
     <row r="729" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A729" s="19"/>
-      <c r="B729" s="17"/>
-      <c r="C729" s="17"/>
+      <c r="A729" s="13"/>
+      <c r="B729" s="11"/>
+      <c r="C729" s="11"/>
     </row>
     <row r="730" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A730" s="19"/>
-      <c r="B730" s="17"/>
-      <c r="C730" s="17"/>
+      <c r="A730" s="13"/>
+      <c r="B730" s="11"/>
+      <c r="C730" s="11"/>
     </row>
     <row r="731" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A731" s="19"/>
-      <c r="B731" s="17"/>
-      <c r="C731" s="17"/>
+      <c r="A731" s="13"/>
+      <c r="B731" s="11"/>
+      <c r="C731" s="11"/>
     </row>
     <row r="732" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A732" s="19"/>
-      <c r="B732" s="17"/>
-      <c r="C732" s="17"/>
+      <c r="A732" s="13"/>
+      <c r="B732" s="11"/>
+      <c r="C732" s="11"/>
     </row>
     <row r="733" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A733" s="19"/>
-      <c r="B733" s="17"/>
-      <c r="C733" s="17"/>
+      <c r="A733" s="13"/>
+      <c r="B733" s="11"/>
+      <c r="C733" s="11"/>
     </row>
     <row r="734" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A734" s="19"/>
-      <c r="B734" s="17"/>
-      <c r="C734" s="17"/>
+      <c r="A734" s="13"/>
+      <c r="B734" s="11"/>
+      <c r="C734" s="11"/>
     </row>
     <row r="735" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A735" s="19"/>
-      <c r="B735" s="17"/>
-      <c r="C735" s="17"/>
+      <c r="A735" s="13"/>
+      <c r="B735" s="11"/>
+      <c r="C735" s="11"/>
     </row>
     <row r="736" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A736" s="19"/>
-      <c r="B736" s="17"/>
-      <c r="C736" s="17"/>
+      <c r="A736" s="13"/>
+      <c r="B736" s="11"/>
+      <c r="C736" s="11"/>
     </row>
     <row r="737" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A737" s="19"/>
-      <c r="B737" s="17"/>
-      <c r="C737" s="17"/>
+      <c r="A737" s="13"/>
+      <c r="B737" s="11"/>
+      <c r="C737" s="11"/>
     </row>
     <row r="738" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A738" s="19"/>
-      <c r="B738" s="17"/>
-      <c r="C738" s="17"/>
+      <c r="A738" s="13"/>
+      <c r="B738" s="11"/>
+      <c r="C738" s="11"/>
     </row>
     <row r="739" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A739" s="19"/>
-      <c r="B739" s="17"/>
-      <c r="C739" s="17"/>
+      <c r="A739" s="13"/>
+      <c r="B739" s="11"/>
+      <c r="C739" s="11"/>
     </row>
     <row r="740" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A740" s="19"/>
-      <c r="B740" s="17"/>
-      <c r="C740" s="17"/>
+      <c r="A740" s="13"/>
+      <c r="B740" s="11"/>
+      <c r="C740" s="11"/>
     </row>
     <row r="741" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A741" s="19"/>
-      <c r="B741" s="17"/>
-      <c r="C741" s="17"/>
+      <c r="A741" s="13"/>
+      <c r="B741" s="11"/>
+      <c r="C741" s="11"/>
     </row>
     <row r="742" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A742" s="19"/>
-      <c r="B742" s="17"/>
-      <c r="C742" s="17"/>
+      <c r="A742" s="13"/>
+      <c r="B742" s="11"/>
+      <c r="C742" s="11"/>
     </row>
     <row r="743" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A743" s="19"/>
-      <c r="B743" s="17"/>
-      <c r="C743" s="17"/>
+      <c r="A743" s="13"/>
+      <c r="B743" s="11"/>
+      <c r="C743" s="11"/>
     </row>
     <row r="744" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A744" s="19"/>
-      <c r="B744" s="17"/>
-      <c r="C744" s="17"/>
+      <c r="A744" s="13"/>
+      <c r="B744" s="11"/>
+      <c r="C744" s="11"/>
     </row>
     <row r="745" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A745" s="19"/>
-      <c r="B745" s="17"/>
-      <c r="C745" s="17"/>
+      <c r="A745" s="13"/>
+      <c r="B745" s="11"/>
+      <c r="C745" s="11"/>
     </row>
     <row r="746" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A746" s="19"/>
-      <c r="B746" s="17"/>
-      <c r="C746" s="17"/>
+      <c r="A746" s="13"/>
+      <c r="B746" s="11"/>
+      <c r="C746" s="11"/>
     </row>
     <row r="747" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A747" s="19"/>
-      <c r="B747" s="17"/>
-      <c r="C747" s="17"/>
+      <c r="A747" s="13"/>
+      <c r="B747" s="11"/>
+      <c r="C747" s="11"/>
     </row>
     <row r="748" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A748" s="19"/>
-      <c r="B748" s="17"/>
-      <c r="C748" s="17"/>
+      <c r="A748" s="13"/>
+      <c r="B748" s="11"/>
+      <c r="C748" s="11"/>
     </row>
     <row r="749" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A749" s="19"/>
-      <c r="B749" s="17"/>
-      <c r="C749" s="17"/>
+      <c r="A749" s="13"/>
+      <c r="B749" s="11"/>
+      <c r="C749" s="11"/>
     </row>
     <row r="750" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A750" s="19"/>
-      <c r="B750" s="17"/>
-      <c r="C750" s="17"/>
+      <c r="A750" s="13"/>
+      <c r="B750" s="11"/>
+      <c r="C750" s="11"/>
     </row>
     <row r="751" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A751" s="19"/>
-      <c r="B751" s="17"/>
-      <c r="C751" s="17"/>
+      <c r="A751" s="13"/>
+      <c r="B751" s="11"/>
+      <c r="C751" s="11"/>
     </row>
     <row r="752" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A752" s="19"/>
-      <c r="B752" s="17"/>
-      <c r="C752" s="17"/>
+      <c r="A752" s="13"/>
+      <c r="B752" s="11"/>
+      <c r="C752" s="11"/>
     </row>
     <row r="753" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A753" s="19"/>
-      <c r="B753" s="17"/>
-      <c r="C753" s="17"/>
+      <c r="A753" s="13"/>
+      <c r="B753" s="11"/>
+      <c r="C753" s="11"/>
     </row>
     <row r="754" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A754" s="19"/>
-      <c r="B754" s="17"/>
-      <c r="C754" s="17"/>
+      <c r="A754" s="13"/>
+      <c r="B754" s="11"/>
+      <c r="C754" s="11"/>
     </row>
     <row r="755" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A755" s="19"/>
-      <c r="B755" s="17"/>
-      <c r="C755" s="17"/>
+      <c r="A755" s="13"/>
+      <c r="B755" s="11"/>
+      <c r="C755" s="11"/>
     </row>
     <row r="756" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A756" s="19"/>
-      <c r="B756" s="17"/>
-      <c r="C756" s="17"/>
+      <c r="A756" s="13"/>
+      <c r="B756" s="11"/>
+      <c r="C756" s="11"/>
     </row>
     <row r="757" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A757" s="19"/>
-      <c r="B757" s="17"/>
-      <c r="C757" s="17"/>
+      <c r="A757" s="13"/>
+      <c r="B757" s="11"/>
+      <c r="C757" s="11"/>
     </row>
     <row r="758" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A758" s="19"/>
-      <c r="B758" s="17"/>
-      <c r="C758" s="17"/>
+      <c r="A758" s="13"/>
+      <c r="B758" s="11"/>
+      <c r="C758" s="11"/>
     </row>
     <row r="759" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A759" s="19"/>
-      <c r="B759" s="17"/>
-      <c r="C759" s="17"/>
+      <c r="A759" s="13"/>
+      <c r="B759" s="11"/>
+      <c r="C759" s="11"/>
     </row>
     <row r="760" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A760" s="19"/>
-      <c r="B760" s="17"/>
-      <c r="C760" s="17"/>
+      <c r="A760" s="13"/>
+      <c r="B760" s="11"/>
+      <c r="C760" s="11"/>
     </row>
     <row r="761" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A761" s="19"/>
-      <c r="B761" s="17"/>
-      <c r="C761" s="17"/>
+      <c r="A761" s="13"/>
+      <c r="B761" s="11"/>
+      <c r="C761" s="11"/>
     </row>
     <row r="762" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A762" s="19"/>
-      <c r="B762" s="17"/>
-      <c r="C762" s="17"/>
+      <c r="A762" s="13"/>
+      <c r="B762" s="11"/>
+      <c r="C762" s="11"/>
     </row>
     <row r="763" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A763" s="19"/>
-      <c r="B763" s="17"/>
-      <c r="C763" s="17"/>
+      <c r="A763" s="13"/>
+      <c r="B763" s="11"/>
+      <c r="C763" s="11"/>
     </row>
     <row r="764" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A764" s="19"/>
-      <c r="B764" s="17"/>
-      <c r="C764" s="17"/>
+      <c r="A764" s="13"/>
+      <c r="B764" s="11"/>
+      <c r="C764" s="11"/>
     </row>
     <row r="765" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A765" s="19"/>
-      <c r="B765" s="17"/>
-      <c r="C765" s="17"/>
+      <c r="A765" s="13"/>
+      <c r="B765" s="11"/>
+      <c r="C765" s="11"/>
     </row>
     <row r="766" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A766" s="19"/>
-      <c r="B766" s="17"/>
-      <c r="C766" s="17"/>
+      <c r="A766" s="13"/>
+      <c r="B766" s="11"/>
+      <c r="C766" s="11"/>
     </row>
     <row r="767" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A767" s="19"/>
-      <c r="B767" s="17"/>
-      <c r="C767" s="17"/>
+      <c r="A767" s="13"/>
+      <c r="B767" s="11"/>
+      <c r="C767" s="11"/>
     </row>
     <row r="768" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A768" s="19"/>
-      <c r="B768" s="17"/>
-      <c r="C768" s="17"/>
+      <c r="A768" s="13"/>
+      <c r="B768" s="11"/>
+      <c r="C768" s="11"/>
     </row>
     <row r="769" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A769" s="19"/>
-      <c r="B769" s="17"/>
-      <c r="C769" s="17"/>
+      <c r="A769" s="13"/>
+      <c r="B769" s="11"/>
+      <c r="C769" s="11"/>
     </row>
     <row r="770" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A770" s="19"/>
-      <c r="B770" s="17"/>
-      <c r="C770" s="17"/>
+      <c r="A770" s="13"/>
+      <c r="B770" s="11"/>
+      <c r="C770" s="11"/>
     </row>
     <row r="771" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A771" s="19"/>
-      <c r="B771" s="17"/>
-      <c r="C771" s="17"/>
+      <c r="A771" s="13"/>
+      <c r="B771" s="11"/>
+      <c r="C771" s="11"/>
     </row>
     <row r="772" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A772" s="19"/>
-      <c r="B772" s="17"/>
-      <c r="C772" s="17"/>
+      <c r="A772" s="13"/>
+      <c r="B772" s="11"/>
+      <c r="C772" s="11"/>
     </row>
     <row r="773" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A773" s="19"/>
-      <c r="B773" s="17"/>
-      <c r="C773" s="17"/>
+      <c r="A773" s="13"/>
+      <c r="B773" s="11"/>
+      <c r="C773" s="11"/>
     </row>
     <row r="774" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A774" s="19"/>
-      <c r="B774" s="17"/>
-      <c r="C774" s="17"/>
+      <c r="A774" s="13"/>
+      <c r="B774" s="11"/>
+      <c r="C774" s="11"/>
     </row>
     <row r="775" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A775" s="19"/>
-      <c r="B775" s="17"/>
-      <c r="C775" s="17"/>
+      <c r="A775" s="13"/>
+      <c r="B775" s="11"/>
+      <c r="C775" s="11"/>
     </row>
     <row r="776" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A776" s="19"/>
-      <c r="B776" s="17"/>
-      <c r="C776" s="17"/>
+      <c r="A776" s="13"/>
+      <c r="B776" s="11"/>
+      <c r="C776" s="11"/>
     </row>
     <row r="777" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A777" s="19"/>
-      <c r="B777" s="17"/>
-      <c r="C777" s="17"/>
+      <c r="A777" s="13"/>
+      <c r="B777" s="11"/>
+      <c r="C777" s="11"/>
     </row>
     <row r="778" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A778" s="19"/>
-      <c r="B778" s="17"/>
-      <c r="C778" s="17"/>
+      <c r="A778" s="13"/>
+      <c r="B778" s="11"/>
+      <c r="C778" s="11"/>
     </row>
     <row r="779" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A779" s="19"/>
-      <c r="B779" s="17"/>
-      <c r="C779" s="17"/>
+      <c r="A779" s="13"/>
+      <c r="B779" s="11"/>
+      <c r="C779" s="11"/>
     </row>
     <row r="780" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A780" s="19"/>
-      <c r="B780" s="17"/>
-      <c r="C780" s="17"/>
+      <c r="A780" s="13"/>
+      <c r="B780" s="11"/>
+      <c r="C780" s="11"/>
     </row>
     <row r="781" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A781" s="19"/>
-      <c r="B781" s="17"/>
-      <c r="C781" s="17"/>
+      <c r="A781" s="13"/>
+      <c r="B781" s="11"/>
+      <c r="C781" s="11"/>
     </row>
     <row r="782" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A782" s="19"/>
-      <c r="B782" s="17"/>
-      <c r="C782" s="17"/>
+      <c r="A782" s="13"/>
+      <c r="B782" s="11"/>
+      <c r="C782" s="11"/>
     </row>
     <row r="783" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A783" s="19"/>
-      <c r="B783" s="17"/>
-      <c r="C783" s="17"/>
+      <c r="A783" s="13"/>
+      <c r="B783" s="11"/>
+      <c r="C783" s="11"/>
     </row>
     <row r="784" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A784" s="19"/>
-      <c r="B784" s="17"/>
-      <c r="C784" s="17"/>
+      <c r="A784" s="13"/>
+      <c r="B784" s="11"/>
+      <c r="C784" s="11"/>
     </row>
     <row r="785" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A785" s="19"/>
-      <c r="B785" s="17"/>
-      <c r="C785" s="17"/>
+      <c r="A785" s="13"/>
+      <c r="B785" s="11"/>
+      <c r="C785" s="11"/>
     </row>
     <row r="786" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A786" s="19"/>
-      <c r="B786" s="17"/>
-      <c r="C786" s="17"/>
+      <c r="A786" s="13"/>
+      <c r="B786" s="11"/>
+      <c r="C786" s="11"/>
     </row>
     <row r="787" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A787" s="19"/>
-      <c r="B787" s="17"/>
-      <c r="C787" s="17"/>
+      <c r="A787" s="13"/>
+      <c r="B787" s="11"/>
+      <c r="C787" s="11"/>
     </row>
     <row r="788" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A788" s="19"/>
-      <c r="B788" s="17"/>
-      <c r="C788" s="17"/>
+      <c r="A788" s="13"/>
+      <c r="B788" s="11"/>
+      <c r="C788" s="11"/>
     </row>
     <row r="789" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A789" s="19"/>
-      <c r="B789" s="17"/>
-      <c r="C789" s="17"/>
+      <c r="A789" s="13"/>
+      <c r="B789" s="11"/>
+      <c r="C789" s="11"/>
     </row>
     <row r="790" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A790" s="19"/>
-      <c r="B790" s="17"/>
-      <c r="C790" s="17"/>
+      <c r="A790" s="13"/>
+      <c r="B790" s="11"/>
+      <c r="C790" s="11"/>
     </row>
     <row r="791" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A791" s="19"/>
-      <c r="B791" s="17"/>
-      <c r="C791" s="17"/>
+      <c r="A791" s="13"/>
+      <c r="B791" s="11"/>
+      <c r="C791" s="11"/>
     </row>
     <row r="792" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A792" s="19"/>
-      <c r="B792" s="17"/>
-      <c r="C792" s="17"/>
+      <c r="A792" s="13"/>
+      <c r="B792" s="11"/>
+      <c r="C792" s="11"/>
     </row>
     <row r="793" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A793" s="19"/>
-      <c r="B793" s="17"/>
-      <c r="C793" s="17"/>
+      <c r="A793" s="13"/>
+      <c r="B793" s="11"/>
+      <c r="C793" s="11"/>
     </row>
     <row r="794" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A794" s="19"/>
-      <c r="B794" s="17"/>
-      <c r="C794" s="17"/>
+      <c r="A794" s="13"/>
+      <c r="B794" s="11"/>
+      <c r="C794" s="11"/>
     </row>
     <row r="795" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A795" s="19"/>
-      <c r="B795" s="17"/>
-      <c r="C795" s="17"/>
+      <c r="A795" s="13"/>
+      <c r="B795" s="11"/>
+      <c r="C795" s="11"/>
     </row>
     <row r="796" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A796" s="19"/>
-      <c r="B796" s="17"/>
-      <c r="C796" s="17"/>
+      <c r="A796" s="13"/>
+      <c r="B796" s="11"/>
+      <c r="C796" s="11"/>
     </row>
     <row r="797" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A797" s="19"/>
-      <c r="B797" s="17"/>
-      <c r="C797" s="17"/>
+      <c r="A797" s="13"/>
+      <c r="B797" s="11"/>
+      <c r="C797" s="11"/>
     </row>
     <row r="798" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A798" s="19"/>
-      <c r="B798" s="17"/>
-      <c r="C798" s="17"/>
+      <c r="A798" s="13"/>
+      <c r="B798" s="11"/>
+      <c r="C798" s="11"/>
     </row>
     <row r="799" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A799" s="19"/>
-      <c r="B799" s="17"/>
-      <c r="C799" s="17"/>
+      <c r="A799" s="13"/>
+      <c r="B799" s="11"/>
+      <c r="C799" s="11"/>
     </row>
     <row r="800" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A800" s="19"/>
-      <c r="B800" s="17"/>
-      <c r="C800" s="17"/>
+      <c r="A800" s="13"/>
+      <c r="B800" s="11"/>
+      <c r="C800" s="11"/>
     </row>
     <row r="801" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A801" s="19"/>
-      <c r="B801" s="17"/>
-      <c r="C801" s="17"/>
+      <c r="A801" s="13"/>
+      <c r="B801" s="11"/>
+      <c r="C801" s="11"/>
     </row>
     <row r="802" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A802" s="19"/>
-      <c r="B802" s="17"/>
-      <c r="C802" s="17"/>
+      <c r="A802" s="13"/>
+      <c r="B802" s="11"/>
+      <c r="C802" s="11"/>
     </row>
     <row r="803" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A803" s="19"/>
-      <c r="B803" s="17"/>
-      <c r="C803" s="17"/>
+      <c r="A803" s="13"/>
+      <c r="B803" s="11"/>
+      <c r="C803" s="11"/>
     </row>
     <row r="804" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A804" s="19"/>
-      <c r="B804" s="17"/>
-      <c r="C804" s="17"/>
+      <c r="A804" s="13"/>
+      <c r="B804" s="11"/>
+      <c r="C804" s="11"/>
     </row>
     <row r="805" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A805" s="19"/>
-      <c r="B805" s="17"/>
-      <c r="C805" s="17"/>
+      <c r="A805" s="13"/>
+      <c r="B805" s="11"/>
+      <c r="C805" s="11"/>
     </row>
     <row r="806" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A806" s="19"/>
-      <c r="B806" s="17"/>
-      <c r="C806" s="17"/>
+      <c r="A806" s="13"/>
+      <c r="B806" s="11"/>
+      <c r="C806" s="11"/>
     </row>
     <row r="807" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A807" s="19"/>
-      <c r="B807" s="17"/>
-      <c r="C807" s="17"/>
+      <c r="A807" s="13"/>
+      <c r="B807" s="11"/>
+      <c r="C807" s="11"/>
     </row>
     <row r="808" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A808" s="19"/>
-      <c r="B808" s="17"/>
-      <c r="C808" s="17"/>
+      <c r="A808" s="13"/>
+      <c r="B808" s="11"/>
+      <c r="C808" s="11"/>
     </row>
     <row r="809" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A809" s="19"/>
-      <c r="B809" s="17"/>
-      <c r="C809" s="17"/>
+      <c r="A809" s="13"/>
+      <c r="B809" s="11"/>
+      <c r="C809" s="11"/>
     </row>
     <row r="810" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A810" s="19"/>
-      <c r="B810" s="17"/>
-      <c r="C810" s="17"/>
+      <c r="A810" s="13"/>
+      <c r="B810" s="11"/>
+      <c r="C810" s="11"/>
     </row>
     <row r="811" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A811" s="19"/>
-      <c r="B811" s="17"/>
-      <c r="C811" s="17"/>
+      <c r="A811" s="13"/>
+      <c r="B811" s="11"/>
+      <c r="C811" s="11"/>
     </row>
     <row r="812" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A812" s="19"/>
-      <c r="B812" s="17"/>
-      <c r="C812" s="17"/>
+      <c r="A812" s="13"/>
+      <c r="B812" s="11"/>
+      <c r="C812" s="11"/>
     </row>
     <row r="813" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A813" s="19"/>
-      <c r="B813" s="17"/>
-      <c r="C813" s="17"/>
+      <c r="A813" s="13"/>
+      <c r="B813" s="11"/>
+      <c r="C813" s="11"/>
     </row>
     <row r="814" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A814" s="19"/>
-      <c r="B814" s="17"/>
-      <c r="C814" s="17"/>
+      <c r="A814" s="13"/>
+      <c r="B814" s="11"/>
+      <c r="C814" s="11"/>
     </row>
     <row r="815" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A815" s="19"/>
-      <c r="B815" s="17"/>
-      <c r="C815" s="17"/>
+      <c r="A815" s="13"/>
+      <c r="B815" s="11"/>
+      <c r="C815" s="11"/>
     </row>
     <row r="816" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A816" s="19"/>
-      <c r="B816" s="17"/>
-      <c r="C816" s="17"/>
+      <c r="A816" s="13"/>
+      <c r="B816" s="11"/>
+      <c r="C816" s="11"/>
     </row>
     <row r="817" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A817" s="19"/>
-      <c r="B817" s="17"/>
-      <c r="C817" s="17"/>
+      <c r="A817" s="13"/>
+      <c r="B817" s="11"/>
+      <c r="C817" s="11"/>
     </row>
     <row r="818" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A818" s="19"/>
-      <c r="B818" s="17"/>
-      <c r="C818" s="17"/>
+      <c r="A818" s="13"/>
+      <c r="B818" s="11"/>
+      <c r="C818" s="11"/>
     </row>
     <row r="819" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A819" s="19"/>
-      <c r="B819" s="17"/>
-      <c r="C819" s="17"/>
+      <c r="A819" s="13"/>
+      <c r="B819" s="11"/>
+      <c r="C819" s="11"/>
     </row>
     <row r="820" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A820" s="19"/>
-      <c r="B820" s="17"/>
-      <c r="C820" s="17"/>
+      <c r="A820" s="13"/>
+      <c r="B820" s="11"/>
+      <c r="C820" s="11"/>
     </row>
     <row r="821" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A821" s="19"/>
-      <c r="B821" s="17"/>
-      <c r="C821" s="17"/>
+      <c r="A821" s="13"/>
+      <c r="B821" s="11"/>
+      <c r="C821" s="11"/>
     </row>
     <row r="822" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A822" s="19"/>
-      <c r="B822" s="17"/>
-      <c r="C822" s="17"/>
+      <c r="A822" s="13"/>
+      <c r="B822" s="11"/>
+      <c r="C822" s="11"/>
     </row>
     <row r="823" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A823" s="19"/>
-      <c r="B823" s="17"/>
-      <c r="C823" s="17"/>
+      <c r="A823" s="13"/>
+      <c r="B823" s="11"/>
+      <c r="C823" s="11"/>
     </row>
     <row r="824" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A824" s="19"/>
-      <c r="B824" s="17"/>
-      <c r="C824" s="17"/>
+      <c r="A824" s="13"/>
+      <c r="B824" s="11"/>
+      <c r="C824" s="11"/>
     </row>
     <row r="825" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A825" s="19"/>
-      <c r="B825" s="17"/>
-      <c r="C825" s="17"/>
+      <c r="A825" s="13"/>
+      <c r="B825" s="11"/>
+      <c r="C825" s="11"/>
     </row>
     <row r="826" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A826" s="19"/>
-      <c r="B826" s="17"/>
-      <c r="C826" s="17"/>
+      <c r="A826" s="13"/>
+      <c r="B826" s="11"/>
+      <c r="C826" s="11"/>
     </row>
     <row r="827" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A827" s="19"/>
-      <c r="B827" s="17"/>
-      <c r="C827" s="17"/>
+      <c r="A827" s="13"/>
+      <c r="B827" s="11"/>
+      <c r="C827" s="11"/>
     </row>
     <row r="828" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A828" s="19"/>
-      <c r="B828" s="17"/>
-      <c r="C828" s="17"/>
+      <c r="A828" s="13"/>
+      <c r="B828" s="11"/>
+      <c r="C828" s="11"/>
     </row>
     <row r="829" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A829" s="19"/>
-      <c r="B829" s="17"/>
-      <c r="C829" s="17"/>
+      <c r="A829" s="13"/>
+      <c r="B829" s="11"/>
+      <c r="C829" s="11"/>
     </row>
     <row r="830" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A830" s="19"/>
-      <c r="B830" s="17"/>
-      <c r="C830" s="17"/>
+      <c r="A830" s="13"/>
+      <c r="B830" s="11"/>
+      <c r="C830" s="11"/>
     </row>
     <row r="831" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A831" s="19"/>
-      <c r="B831" s="17"/>
-      <c r="C831" s="17"/>
+      <c r="A831" s="13"/>
+      <c r="B831" s="11"/>
+      <c r="C831" s="11"/>
     </row>
     <row r="832" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A832" s="19"/>
-      <c r="B832" s="17"/>
-      <c r="C832" s="17"/>
+      <c r="A832" s="13"/>
+      <c r="B832" s="11"/>
+      <c r="C832" s="11"/>
     </row>
     <row r="833" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A833" s="19"/>
-      <c r="B833" s="17"/>
-      <c r="C833" s="17"/>
+      <c r="A833" s="13"/>
+      <c r="B833" s="11"/>
+      <c r="C833" s="11"/>
     </row>
     <row r="834" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A834" s="19"/>
-      <c r="B834" s="17"/>
-      <c r="C834" s="17"/>
+      <c r="A834" s="13"/>
+      <c r="B834" s="11"/>
+      <c r="C834" s="11"/>
     </row>
     <row r="835" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A835" s="19"/>
-      <c r="B835" s="17"/>
-      <c r="C835" s="17"/>
+      <c r="A835" s="13"/>
+      <c r="B835" s="11"/>
+      <c r="C835" s="11"/>
     </row>
     <row r="836" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A836" s="19"/>
-      <c r="B836" s="17"/>
-      <c r="C836" s="17"/>
+      <c r="A836" s="13"/>
+      <c r="B836" s="11"/>
+      <c r="C836" s="11"/>
     </row>
     <row r="837" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A837" s="19"/>
-      <c r="B837" s="17"/>
-      <c r="C837" s="17"/>
+      <c r="A837" s="13"/>
+      <c r="B837" s="11"/>
+      <c r="C837" s="11"/>
     </row>
     <row r="838" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A838" s="19"/>
-      <c r="B838" s="17"/>
-      <c r="C838" s="17"/>
+      <c r="A838" s="13"/>
+      <c r="B838" s="11"/>
+      <c r="C838" s="11"/>
     </row>
     <row r="839" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A839" s="19"/>
-      <c r="B839" s="17"/>
-      <c r="C839" s="17"/>
+      <c r="A839" s="13"/>
+      <c r="B839" s="11"/>
+      <c r="C839" s="11"/>
     </row>
     <row r="840" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A840" s="19"/>
-      <c r="B840" s="17"/>
-      <c r="C840" s="17"/>
+      <c r="A840" s="13"/>
+      <c r="B840" s="11"/>
+      <c r="C840" s="11"/>
     </row>
     <row r="841" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A841" s="19"/>
-      <c r="B841" s="17"/>
-      <c r="C841" s="17"/>
+      <c r="A841" s="13"/>
+      <c r="B841" s="11"/>
+      <c r="C841" s="11"/>
     </row>
     <row r="842" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A842" s="19"/>
-      <c r="B842" s="17"/>
-      <c r="C842" s="17"/>
+      <c r="A842" s="13"/>
+      <c r="B842" s="11"/>
+      <c r="C842" s="11"/>
     </row>
     <row r="843" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A843" s="19"/>
-      <c r="B843" s="17"/>
-      <c r="C843" s="17"/>
+      <c r="A843" s="13"/>
+      <c r="B843" s="11"/>
+      <c r="C843" s="11"/>
     </row>
     <row r="844" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A844" s="19"/>
-      <c r="B844" s="17"/>
-      <c r="C844" s="17"/>
+      <c r="A844" s="13"/>
+      <c r="B844" s="11"/>
+      <c r="C844" s="11"/>
     </row>
     <row r="845" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A845" s="19"/>
-      <c r="B845" s="17"/>
-      <c r="C845" s="17"/>
+      <c r="A845" s="13"/>
+      <c r="B845" s="11"/>
+      <c r="C845" s="11"/>
     </row>
     <row r="846" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A846" s="19"/>
-      <c r="B846" s="17"/>
-      <c r="C846" s="17"/>
+      <c r="A846" s="13"/>
+      <c r="B846" s="11"/>
+      <c r="C846" s="11"/>
     </row>
     <row r="847" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A847" s="19"/>
-      <c r="B847" s="17"/>
-      <c r="C847" s="17"/>
+      <c r="A847" s="13"/>
+      <c r="B847" s="11"/>
+      <c r="C847" s="11"/>
     </row>
     <row r="848" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A848" s="19"/>
-      <c r="B848" s="17"/>
-      <c r="C848" s="17"/>
+      <c r="A848" s="13"/>
+      <c r="B848" s="11"/>
+      <c r="C848" s="11"/>
     </row>
     <row r="849" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A849" s="19"/>
-      <c r="B849" s="17"/>
-      <c r="C849" s="17"/>
+      <c r="A849" s="13"/>
+      <c r="B849" s="11"/>
+      <c r="C849" s="11"/>
     </row>
     <row r="850" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A850" s="19"/>
-      <c r="B850" s="17"/>
-      <c r="C850" s="17"/>
+      <c r="A850" s="13"/>
+      <c r="B850" s="11"/>
+      <c r="C850" s="11"/>
     </row>
     <row r="851" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A851" s="19"/>
-      <c r="B851" s="17"/>
-      <c r="C851" s="17"/>
+      <c r="A851" s="13"/>
+      <c r="B851" s="11"/>
+      <c r="C851" s="11"/>
     </row>
     <row r="852" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A852" s="19"/>
-      <c r="B852" s="17"/>
-      <c r="C852" s="17"/>
+      <c r="A852" s="13"/>
+      <c r="B852" s="11"/>
+      <c r="C852" s="11"/>
     </row>
     <row r="853" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A853" s="19"/>
-      <c r="B853" s="17"/>
-      <c r="C853" s="17"/>
+      <c r="A853" s="13"/>
+      <c r="B853" s="11"/>
+      <c r="C853" s="11"/>
     </row>
     <row r="854" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A854" s="19"/>
-      <c r="B854" s="17"/>
-      <c r="C854" s="17"/>
+      <c r="A854" s="13"/>
+      <c r="B854" s="11"/>
+      <c r="C854" s="11"/>
     </row>
     <row r="855" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A855" s="19"/>
-      <c r="B855" s="17"/>
-      <c r="C855" s="17"/>
+      <c r="A855" s="13"/>
+      <c r="B855" s="11"/>
+      <c r="C855" s="11"/>
     </row>
     <row r="856" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A856" s="19"/>
-      <c r="B856" s="17"/>
-      <c r="C856" s="17"/>
+      <c r="A856" s="13"/>
+      <c r="B856" s="11"/>
+      <c r="C856" s="11"/>
     </row>
     <row r="857" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A857" s="19"/>
-      <c r="B857" s="17"/>
-      <c r="C857" s="17"/>
+      <c r="A857" s="13"/>
+      <c r="B857" s="11"/>
+      <c r="C857" s="11"/>
     </row>
     <row r="858" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A858" s="19"/>
-      <c r="B858" s="17"/>
-      <c r="C858" s="17"/>
+      <c r="A858" s="13"/>
+      <c r="B858" s="11"/>
+      <c r="C858" s="11"/>
     </row>
     <row r="859" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A859" s="19"/>
-      <c r="B859" s="17"/>
-      <c r="C859" s="17"/>
+      <c r="A859" s="13"/>
+      <c r="B859" s="11"/>
+      <c r="C859" s="11"/>
     </row>
     <row r="860" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A860" s="19"/>
-      <c r="B860" s="17"/>
-      <c r="C860" s="17"/>
+      <c r="A860" s="13"/>
+      <c r="B860" s="11"/>
+      <c r="C860" s="11"/>
     </row>
     <row r="861" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A861" s="19"/>
-      <c r="B861" s="17"/>
-      <c r="C861" s="17"/>
+      <c r="A861" s="13"/>
+      <c r="B861" s="11"/>
+      <c r="C861" s="11"/>
     </row>
     <row r="862" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A862" s="19"/>
-      <c r="B862" s="17"/>
-      <c r="C862" s="17"/>
+      <c r="A862" s="13"/>
+      <c r="B862" s="11"/>
+      <c r="C862" s="11"/>
     </row>
     <row r="863" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A863" s="19"/>
-      <c r="B863" s="17"/>
-      <c r="C863" s="17"/>
+      <c r="A863" s="13"/>
+      <c r="B863" s="11"/>
+      <c r="C863" s="11"/>
     </row>
     <row r="864" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A864" s="19"/>
-      <c r="B864" s="17"/>
-      <c r="C864" s="17"/>
+      <c r="A864" s="13"/>
+      <c r="B864" s="11"/>
+      <c r="C864" s="11"/>
     </row>
     <row r="865" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A865" s="19"/>
-      <c r="B865" s="17"/>
-      <c r="C865" s="17"/>
+      <c r="A865" s="13"/>
+      <c r="B865" s="11"/>
+      <c r="C865" s="11"/>
     </row>
     <row r="866" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A866" s="19"/>
-      <c r="B866" s="17"/>
-      <c r="C866" s="17"/>
+      <c r="A866" s="13"/>
+      <c r="B866" s="11"/>
+      <c r="C866" s="11"/>
     </row>
     <row r="867" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A867" s="19"/>
-      <c r="B867" s="17"/>
-      <c r="C867" s="17"/>
+      <c r="A867" s="13"/>
+      <c r="B867" s="11"/>
+      <c r="C867" s="11"/>
     </row>
     <row r="868" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A868" s="19"/>
-      <c r="B868" s="17"/>
-      <c r="C868" s="17"/>
+      <c r="A868" s="13"/>
+      <c r="B868" s="11"/>
+      <c r="C868" s="11"/>
     </row>
     <row r="869" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A869" s="19"/>
-      <c r="B869" s="17"/>
-      <c r="C869" s="17"/>
+      <c r="A869" s="13"/>
+      <c r="B869" s="11"/>
+      <c r="C869" s="11"/>
     </row>
     <row r="870" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A870" s="19"/>
-      <c r="B870" s="17"/>
-      <c r="C870" s="17"/>
+      <c r="A870" s="13"/>
+      <c r="B870" s="11"/>
+      <c r="C870" s="11"/>
     </row>
     <row r="871" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A871" s="19"/>
-      <c r="B871" s="17"/>
-      <c r="C871" s="17"/>
+      <c r="A871" s="13"/>
+      <c r="B871" s="11"/>
+      <c r="C871" s="11"/>
     </row>
     <row r="872" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A872" s="19"/>
-      <c r="B872" s="17"/>
-      <c r="C872" s="17"/>
+      <c r="A872" s="13"/>
+      <c r="B872" s="11"/>
+      <c r="C872" s="11"/>
     </row>
     <row r="873" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A873" s="19"/>
-      <c r="B873" s="17"/>
-      <c r="C873" s="17"/>
+      <c r="A873" s="13"/>
+      <c r="B873" s="11"/>
+      <c r="C873" s="11"/>
     </row>
     <row r="874" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A874" s="19"/>
-      <c r="B874" s="17"/>
-      <c r="C874" s="17"/>
+      <c r="A874" s="13"/>
+      <c r="B874" s="11"/>
+      <c r="C874" s="11"/>
     </row>
     <row r="875" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A875" s="19"/>
-      <c r="B875" s="17"/>
-      <c r="C875" s="17"/>
+      <c r="A875" s="13"/>
+      <c r="B875" s="11"/>
+      <c r="C875" s="11"/>
     </row>
     <row r="876" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A876" s="19"/>
-      <c r="B876" s="17"/>
-      <c r="C876" s="17"/>
+      <c r="A876" s="13"/>
+      <c r="B876" s="11"/>
+      <c r="C876" s="11"/>
     </row>
     <row r="877" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A877" s="19"/>
-      <c r="B877" s="17"/>
-      <c r="C877" s="17"/>
+      <c r="A877" s="13"/>
+      <c r="B877" s="11"/>
+      <c r="C877" s="11"/>
     </row>
     <row r="878" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A878" s="19"/>
-      <c r="B878" s="17"/>
-      <c r="C878" s="17"/>
+      <c r="A878" s="13"/>
+      <c r="B878" s="11"/>
+      <c r="C878" s="11"/>
     </row>
     <row r="879" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A879" s="19"/>
-      <c r="B879" s="17"/>
-      <c r="C879" s="17"/>
+      <c r="A879" s="13"/>
+      <c r="B879" s="11"/>
+      <c r="C879" s="11"/>
     </row>
     <row r="880" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A880" s="19"/>
-      <c r="B880" s="17"/>
-      <c r="C880" s="17"/>
+      <c r="A880" s="13"/>
+      <c r="B880" s="11"/>
+      <c r="C880" s="11"/>
     </row>
     <row r="881" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A881" s="19"/>
-      <c r="B881" s="17"/>
-      <c r="C881" s="17"/>
+      <c r="A881" s="13"/>
+      <c r="B881" s="11"/>
+      <c r="C881" s="11"/>
     </row>
     <row r="882" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A882" s="19"/>
-      <c r="B882" s="17"/>
-      <c r="C882" s="17"/>
+      <c r="A882" s="13"/>
+      <c r="B882" s="11"/>
+      <c r="C882" s="11"/>
     </row>
     <row r="883" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A883" s="19"/>
-      <c r="B883" s="17"/>
-      <c r="C883" s="17"/>
+      <c r="A883" s="13"/>
+      <c r="B883" s="11"/>
+      <c r="C883" s="11"/>
     </row>
     <row r="884" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A884" s="19"/>
-      <c r="B884" s="17"/>
-      <c r="C884" s="17"/>
+      <c r="A884" s="13"/>
+      <c r="B884" s="11"/>
+      <c r="C884" s="11"/>
     </row>
     <row r="885" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A885" s="19"/>
-      <c r="B885" s="17"/>
-      <c r="C885" s="17"/>
+      <c r="A885" s="13"/>
+      <c r="B885" s="11"/>
+      <c r="C885" s="11"/>
     </row>
     <row r="886" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A886" s="19"/>
-      <c r="B886" s="17"/>
-      <c r="C886" s="17"/>
+      <c r="A886" s="13"/>
+      <c r="B886" s="11"/>
+      <c r="C886" s="11"/>
     </row>
     <row r="887" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A887" s="19"/>
-      <c r="B887" s="17"/>
-      <c r="C887" s="17"/>
+      <c r="A887" s="13"/>
+      <c r="B887" s="11"/>
+      <c r="C887" s="11"/>
     </row>
     <row r="888" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A888" s="19"/>
-      <c r="B888" s="17"/>
-      <c r="C888" s="17"/>
+      <c r="A888" s="13"/>
+      <c r="B888" s="11"/>
+      <c r="C888" s="11"/>
     </row>
     <row r="889" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A889" s="19"/>
-      <c r="B889" s="17"/>
-      <c r="C889" s="17"/>
+      <c r="A889" s="13"/>
+      <c r="B889" s="11"/>
+      <c r="C889" s="11"/>
     </row>
     <row r="890" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A890" s="19"/>
-      <c r="B890" s="17"/>
-      <c r="C890" s="17"/>
+      <c r="A890" s="13"/>
+      <c r="B890" s="11"/>
+      <c r="C890" s="11"/>
     </row>
     <row r="891" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A891" s="19"/>
-      <c r="B891" s="17"/>
-      <c r="C891" s="17"/>
+      <c r="A891" s="13"/>
+      <c r="B891" s="11"/>
+      <c r="C891" s="11"/>
     </row>
     <row r="892" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A892" s="19"/>
-      <c r="B892" s="17"/>
-      <c r="C892" s="17"/>
+      <c r="A892" s="13"/>
+      <c r="B892" s="11"/>
+      <c r="C892" s="11"/>
     </row>
     <row r="893" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A893" s="19"/>
-      <c r="B893" s="17"/>
-      <c r="C893" s="17"/>
+      <c r="A893" s="13"/>
+      <c r="B893" s="11"/>
+      <c r="C893" s="11"/>
     </row>
     <row r="894" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A894" s="19"/>
-      <c r="B894" s="17"/>
-      <c r="C894" s="17"/>
+      <c r="A894" s="13"/>
+      <c r="B894" s="11"/>
+      <c r="C894" s="11"/>
     </row>
     <row r="895" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A895" s="19"/>
-      <c r="B895" s="17"/>
-      <c r="C895" s="17"/>
+      <c r="A895" s="13"/>
+      <c r="B895" s="11"/>
+      <c r="C895" s="11"/>
     </row>
     <row r="896" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A896" s="19"/>
-      <c r="B896" s="17"/>
-      <c r="C896" s="17"/>
+      <c r="A896" s="13"/>
+      <c r="B896" s="11"/>
+      <c r="C896" s="11"/>
     </row>
     <row r="897" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A897" s="19"/>
-      <c r="B897" s="17"/>
-      <c r="C897" s="17"/>
+      <c r="A897" s="13"/>
+      <c r="B897" s="11"/>
+      <c r="C897" s="11"/>
     </row>
     <row r="898" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A898" s="19"/>
-      <c r="B898" s="17"/>
-      <c r="C898" s="17"/>
+      <c r="A898" s="13"/>
+      <c r="B898" s="11"/>
+      <c r="C898" s="11"/>
     </row>
     <row r="899" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A899" s="19"/>
-      <c r="B899" s="17"/>
-      <c r="C899" s="17"/>
+      <c r="A899" s="13"/>
+      <c r="B899" s="11"/>
+      <c r="C899" s="11"/>
     </row>
     <row r="900" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A900" s="19"/>
-      <c r="B900" s="17"/>
-      <c r="C900" s="17"/>
+      <c r="A900" s="13"/>
+      <c r="B900" s="11"/>
+      <c r="C900" s="11"/>
     </row>
     <row r="901" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A901" s="19"/>
-      <c r="B901" s="17"/>
-      <c r="C901" s="17"/>
+      <c r="A901" s="13"/>
+      <c r="B901" s="11"/>
+      <c r="C901" s="11"/>
     </row>
     <row r="902" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A902" s="19"/>
-      <c r="B902" s="17"/>
-      <c r="C902" s="17"/>
+      <c r="A902" s="13"/>
+      <c r="B902" s="11"/>
+      <c r="C902" s="11"/>
     </row>
     <row r="903" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A903" s="19"/>
-      <c r="B903" s="17"/>
-      <c r="C903" s="17"/>
+      <c r="A903" s="13"/>
+      <c r="B903" s="11"/>
+      <c r="C903" s="11"/>
     </row>
     <row r="904" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A904" s="19"/>
-      <c r="B904" s="17"/>
-      <c r="C904" s="17"/>
+      <c r="A904" s="13"/>
+      <c r="B904" s="11"/>
+      <c r="C904" s="11"/>
     </row>
     <row r="905" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A905" s="19"/>
-      <c r="B905" s="17"/>
-      <c r="C905" s="17"/>
+      <c r="A905" s="13"/>
+      <c r="B905" s="11"/>
+      <c r="C905" s="11"/>
     </row>
     <row r="906" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A906" s="19"/>
-      <c r="B906" s="17"/>
-      <c r="C906" s="17"/>
+      <c r="A906" s="13"/>
+      <c r="B906" s="11"/>
+      <c r="C906" s="11"/>
     </row>
     <row r="907" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A907" s="19"/>
-      <c r="B907" s="17"/>
-      <c r="C907" s="17"/>
+      <c r="A907" s="13"/>
+      <c r="B907" s="11"/>
+      <c r="C907" s="11"/>
     </row>
     <row r="908" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A908" s="19"/>
-      <c r="B908" s="17"/>
-      <c r="C908" s="17"/>
+      <c r="A908" s="13"/>
+      <c r="B908" s="11"/>
+      <c r="C908" s="11"/>
     </row>
     <row r="909" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A909" s="19"/>
-      <c r="B909" s="17"/>
-      <c r="C909" s="17"/>
+      <c r="A909" s="13"/>
+      <c r="B909" s="11"/>
+      <c r="C909" s="11"/>
     </row>
     <row r="910" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A910" s="19"/>
-      <c r="B910" s="17"/>
-      <c r="C910" s="17"/>
+      <c r="A910" s="13"/>
+      <c r="B910" s="11"/>
+      <c r="C910" s="11"/>
     </row>
     <row r="911" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A911" s="19"/>
-      <c r="B911" s="17"/>
-      <c r="C911" s="17"/>
+      <c r="A911" s="13"/>
+      <c r="B911" s="11"/>
+      <c r="C911" s="11"/>
     </row>
     <row r="912" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A912" s="19"/>
-      <c r="B912" s="17"/>
-      <c r="C912" s="17"/>
+      <c r="A912" s="13"/>
+      <c r="B912" s="11"/>
+      <c r="C912" s="11"/>
     </row>
     <row r="913" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A913" s="19"/>
-      <c r="B913" s="17"/>
-      <c r="C913" s="17"/>
+      <c r="A913" s="13"/>
+      <c r="B913" s="11"/>
+      <c r="C913" s="11"/>
     </row>
     <row r="914" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A914" s="19"/>
-      <c r="B914" s="17"/>
-      <c r="C914" s="17"/>
+      <c r="A914" s="13"/>
+      <c r="B914" s="11"/>
+      <c r="C914" s="11"/>
     </row>
     <row r="915" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A915" s="19"/>
-      <c r="B915" s="17"/>
-      <c r="C915" s="17"/>
+      <c r="A915" s="13"/>
+      <c r="B915" s="11"/>
+      <c r="C915" s="11"/>
     </row>
     <row r="916" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A916" s="19"/>
-      <c r="B916" s="17"/>
-      <c r="C916" s="17"/>
+      <c r="A916" s="13"/>
+      <c r="B916" s="11"/>
+      <c r="C916" s="11"/>
     </row>
     <row r="917" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A917" s="19"/>
-      <c r="B917" s="17"/>
-      <c r="C917" s="17"/>
+      <c r="A917" s="13"/>
+      <c r="B917" s="11"/>
+      <c r="C917" s="11"/>
     </row>
     <row r="918" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A918" s="19"/>
-      <c r="B918" s="17"/>
-      <c r="C918" s="17"/>
+      <c r="A918" s="13"/>
+      <c r="B918" s="11"/>
+      <c r="C918" s="11"/>
     </row>
     <row r="919" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A919" s="19"/>
-      <c r="B919" s="17"/>
-      <c r="C919" s="17"/>
+      <c r="A919" s="13"/>
+      <c r="B919" s="11"/>
+      <c r="C919" s="11"/>
     </row>
     <row r="920" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A920" s="19"/>
-      <c r="B920" s="17"/>
-      <c r="C920" s="17"/>
+      <c r="A920" s="13"/>
+      <c r="B920" s="11"/>
+      <c r="C920" s="11"/>
     </row>
     <row r="921" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A921" s="19"/>
-      <c r="B921" s="17"/>
-      <c r="C921" s="17"/>
+      <c r="A921" s="13"/>
+      <c r="B921" s="11"/>
+      <c r="C921" s="11"/>
     </row>
     <row r="922" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A922" s="19"/>
-      <c r="B922" s="17"/>
-      <c r="C922" s="17"/>
+      <c r="A922" s="13"/>
+      <c r="B922" s="11"/>
+      <c r="C922" s="11"/>
     </row>
     <row r="923" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A923" s="19"/>
-      <c r="B923" s="17"/>
-      <c r="C923" s="17"/>
+      <c r="A923" s="13"/>
+      <c r="B923" s="11"/>
+      <c r="C923" s="11"/>
     </row>
     <row r="924" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A924" s="19"/>
-      <c r="B924" s="17"/>
-      <c r="C924" s="17"/>
+      <c r="A924" s="13"/>
+      <c r="B924" s="11"/>
+      <c r="C924" s="11"/>
     </row>
     <row r="925" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A925" s="19"/>
-      <c r="B925" s="17"/>
-      <c r="C925" s="17"/>
+      <c r="A925" s="13"/>
+      <c r="B925" s="11"/>
+      <c r="C925" s="11"/>
     </row>
     <row r="926" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A926" s="19"/>
-      <c r="B926" s="17"/>
-      <c r="C926" s="17"/>
+      <c r="A926" s="13"/>
+      <c r="B926" s="11"/>
+      <c r="C926" s="11"/>
     </row>
     <row r="927" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A927" s="19"/>
-      <c r="B927" s="17"/>
-      <c r="C927" s="17"/>
+      <c r="A927" s="13"/>
+      <c r="B927" s="11"/>
+      <c r="C927" s="11"/>
     </row>
     <row r="928" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A928" s="19"/>
-      <c r="B928" s="17"/>
-      <c r="C928" s="17"/>
+      <c r="A928" s="13"/>
+      <c r="B928" s="11"/>
+      <c r="C928" s="11"/>
     </row>
     <row r="929" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A929" s="19"/>
-      <c r="B929" s="17"/>
-      <c r="C929" s="17"/>
+      <c r="A929" s="13"/>
+      <c r="B929" s="11"/>
+      <c r="C929" s="11"/>
     </row>
     <row r="930" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A930" s="19"/>
-      <c r="B930" s="17"/>
-      <c r="C930" s="17"/>
+      <c r="A930" s="13"/>
+      <c r="B930" s="11"/>
+      <c r="C930" s="11"/>
     </row>
     <row r="931" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A931" s="19"/>
-      <c r="B931" s="17"/>
-      <c r="C931" s="17"/>
+      <c r="A931" s="13"/>
+      <c r="B931" s="11"/>
+      <c r="C931" s="11"/>
     </row>
     <row r="932" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A932" s="19"/>
-      <c r="B932" s="17"/>
-      <c r="C932" s="17"/>
+      <c r="A932" s="13"/>
+      <c r="B932" s="11"/>
+      <c r="C932" s="11"/>
     </row>
     <row r="933" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A933" s="19"/>
-      <c r="B933" s="17"/>
-      <c r="C933" s="17"/>
+      <c r="A933" s="13"/>
+      <c r="B933" s="11"/>
+      <c r="C933" s="11"/>
     </row>
     <row r="934" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A934" s="19"/>
-      <c r="B934" s="17"/>
-      <c r="C934" s="17"/>
+      <c r="A934" s="13"/>
+      <c r="B934" s="11"/>
+      <c r="C934" s="11"/>
     </row>
     <row r="935" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A935" s="19"/>
-      <c r="B935" s="17"/>
-      <c r="C935" s="17"/>
+      <c r="A935" s="13"/>
+      <c r="B935" s="11"/>
+      <c r="C935" s="11"/>
     </row>
     <row r="936" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A936" s="19"/>
-      <c r="B936" s="17"/>
-      <c r="C936" s="17"/>
+      <c r="A936" s="13"/>
+      <c r="B936" s="11"/>
+      <c r="C936" s="11"/>
     </row>
     <row r="937" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A937" s="19"/>
-      <c r="B937" s="17"/>
-      <c r="C937" s="17"/>
+      <c r="A937" s="13"/>
+      <c r="B937" s="11"/>
+      <c r="C937" s="11"/>
     </row>
     <row r="938" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A938" s="19"/>
-      <c r="B938" s="17"/>
-      <c r="C938" s="17"/>
+      <c r="A938" s="13"/>
+      <c r="B938" s="11"/>
+      <c r="C938" s="11"/>
     </row>
     <row r="939" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A939" s="19"/>
-      <c r="B939" s="17"/>
-      <c r="C939" s="17"/>
+      <c r="A939" s="13"/>
+      <c r="B939" s="11"/>
+      <c r="C939" s="11"/>
     </row>
     <row r="940" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A940" s="19"/>
-      <c r="B940" s="17"/>
-      <c r="C940" s="17"/>
+      <c r="A940" s="13"/>
+      <c r="B940" s="11"/>
+      <c r="C940" s="11"/>
     </row>
     <row r="941" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A941" s="19"/>
-      <c r="B941" s="17"/>
-      <c r="C941" s="17"/>
+      <c r="A941" s="13"/>
+      <c r="B941" s="11"/>
+      <c r="C941" s="11"/>
     </row>
     <row r="942" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A942" s="19"/>
-      <c r="B942" s="17"/>
-      <c r="C942" s="17"/>
+      <c r="A942" s="13"/>
+      <c r="B942" s="11"/>
+      <c r="C942" s="11"/>
     </row>
     <row r="943" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A943" s="19"/>
-      <c r="B943" s="17"/>
-      <c r="C943" s="17"/>
+      <c r="A943" s="13"/>
+      <c r="B943" s="11"/>
+      <c r="C943" s="11"/>
     </row>
     <row r="944" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A944" s="19"/>
-      <c r="B944" s="17"/>
-      <c r="C944" s="17"/>
+      <c r="A944" s="13"/>
+      <c r="B944" s="11"/>
+      <c r="C944" s="11"/>
     </row>
     <row r="945" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A945" s="19"/>
-      <c r="B945" s="17"/>
-      <c r="C945" s="17"/>
+      <c r="A945" s="13"/>
+      <c r="B945" s="11"/>
+      <c r="C945" s="11"/>
     </row>
     <row r="946" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A946" s="19"/>
-      <c r="B946" s="17"/>
-      <c r="C946" s="17"/>
+      <c r="A946" s="13"/>
+      <c r="B946" s="11"/>
+      <c r="C946" s="11"/>
     </row>
     <row r="947" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A947" s="19"/>
-      <c r="B947" s="17"/>
-      <c r="C947" s="17"/>
+      <c r="A947" s="13"/>
+      <c r="B947" s="11"/>
+      <c r="C947" s="11"/>
     </row>
     <row r="948" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A948" s="19"/>
-      <c r="B948" s="17"/>
-      <c r="C948" s="17"/>
+      <c r="A948" s="13"/>
+      <c r="B948" s="11"/>
+      <c r="C948" s="11"/>
     </row>
     <row r="949" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A949" s="19"/>
-      <c r="B949" s="17"/>
-      <c r="C949" s="17"/>
+      <c r="A949" s="13"/>
+      <c r="B949" s="11"/>
+      <c r="C949" s="11"/>
     </row>
     <row r="950" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A950" s="19"/>
-      <c r="B950" s="17"/>
-      <c r="C950" s="17"/>
+      <c r="A950" s="13"/>
+      <c r="B950" s="11"/>
+      <c r="C950" s="11"/>
     </row>
     <row r="951" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A951" s="19"/>
-      <c r="B951" s="17"/>
-      <c r="C951" s="17"/>
+      <c r="A951" s="13"/>
+      <c r="B951" s="11"/>
+      <c r="C951" s="11"/>
     </row>
     <row r="952" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A952" s="19"/>
-      <c r="B952" s="17"/>
-      <c r="C952" s="17"/>
+      <c r="A952" s="13"/>
+      <c r="B952" s="11"/>
+      <c r="C952" s="11"/>
     </row>
     <row r="953" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A953" s="19"/>
-      <c r="B953" s="17"/>
-      <c r="C953" s="17"/>
+      <c r="A953" s="13"/>
+      <c r="B953" s="11"/>
+      <c r="C953" s="11"/>
     </row>
     <row r="954" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A954" s="19"/>
-      <c r="B954" s="17"/>
-      <c r="C954" s="17"/>
+      <c r="A954" s="13"/>
+      <c r="B954" s="11"/>
+      <c r="C954" s="11"/>
     </row>
     <row r="955" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A955" s="19"/>
-      <c r="B955" s="17"/>
-      <c r="C955" s="17"/>
+      <c r="A955" s="13"/>
+      <c r="B955" s="11"/>
+      <c r="C955" s="11"/>
     </row>
     <row r="956" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A956" s="19"/>
-      <c r="B956" s="17"/>
-      <c r="C956" s="17"/>
+      <c r="A956" s="13"/>
+      <c r="B956" s="11"/>
+      <c r="C956" s="11"/>
     </row>
     <row r="957" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A957" s="19"/>
-      <c r="B957" s="17"/>
-      <c r="C957" s="17"/>
+      <c r="A957" s="13"/>
+      <c r="B957" s="11"/>
+      <c r="C957" s="11"/>
     </row>
     <row r="958" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A958" s="19"/>
-      <c r="B958" s="17"/>
-      <c r="C958" s="17"/>
+      <c r="A958" s="13"/>
+      <c r="B958" s="11"/>
+      <c r="C958" s="11"/>
     </row>
     <row r="959" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A959" s="19"/>
-      <c r="B959" s="17"/>
-      <c r="C959" s="17"/>
+      <c r="A959" s="13"/>
+      <c r="B959" s="11"/>
+      <c r="C959" s="11"/>
     </row>
     <row r="960" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A960" s="19"/>
-      <c r="B960" s="17"/>
-      <c r="C960" s="17"/>
+      <c r="A960" s="13"/>
+      <c r="B960" s="11"/>
+      <c r="C960" s="11"/>
     </row>
     <row r="961" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A961" s="19"/>
-      <c r="B961" s="17"/>
-      <c r="C961" s="17"/>
+      <c r="A961" s="13"/>
+      <c r="B961" s="11"/>
+      <c r="C961" s="11"/>
     </row>
     <row r="962" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A962" s="19"/>
-      <c r="B962" s="17"/>
-      <c r="C962" s="17"/>
+      <c r="A962" s="13"/>
+      <c r="B962" s="11"/>
+      <c r="C962" s="11"/>
     </row>
     <row r="963" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A963" s="19"/>
-      <c r="B963" s="17"/>
-      <c r="C963" s="17"/>
+      <c r="A963" s="13"/>
+      <c r="B963" s="11"/>
+      <c r="C963" s="11"/>
     </row>
     <row r="964" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A964" s="19"/>
-      <c r="B964" s="17"/>
-      <c r="C964" s="17"/>
+      <c r="A964" s="13"/>
+      <c r="B964" s="11"/>
+      <c r="C964" s="11"/>
     </row>
     <row r="965" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A965" s="19"/>
-      <c r="B965" s="17"/>
-      <c r="C965" s="17"/>
+      <c r="A965" s="13"/>
+      <c r="B965" s="11"/>
+      <c r="C965" s="11"/>
     </row>
     <row r="966" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A966" s="19"/>
-      <c r="B966" s="17"/>
-      <c r="C966" s="17"/>
+      <c r="A966" s="13"/>
+      <c r="B966" s="11"/>
+      <c r="C966" s="11"/>
     </row>
     <row r="967" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A967" s="19"/>
-      <c r="B967" s="17"/>
-      <c r="C967" s="17"/>
+      <c r="A967" s="13"/>
+      <c r="B967" s="11"/>
+      <c r="C967" s="11"/>
     </row>
     <row r="968" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A968" s="19"/>
-      <c r="B968" s="17"/>
-      <c r="C968" s="17"/>
+      <c r="A968" s="13"/>
+      <c r="B968" s="11"/>
+      <c r="C968" s="11"/>
     </row>
     <row r="969" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A969" s="19"/>
-      <c r="B969" s="17"/>
-      <c r="C969" s="17"/>
+      <c r="A969" s="13"/>
+      <c r="B969" s="11"/>
+      <c r="C969" s="11"/>
     </row>
     <row r="970" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A970" s="19"/>
-      <c r="B970" s="17"/>
-      <c r="C970" s="17"/>
+      <c r="A970" s="13"/>
+      <c r="B970" s="11"/>
+      <c r="C970" s="11"/>
     </row>
     <row r="971" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A971" s="19"/>
-      <c r="B971" s="17"/>
-      <c r="C971" s="17"/>
+      <c r="A971" s="13"/>
+      <c r="B971" s="11"/>
+      <c r="C971" s="11"/>
     </row>
     <row r="972" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A972" s="19"/>
-      <c r="B972" s="17"/>
-      <c r="C972" s="17"/>
+      <c r="A972" s="13"/>
+      <c r="B972" s="11"/>
+      <c r="C972" s="11"/>
     </row>
     <row r="973" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A973" s="19"/>
-      <c r="B973" s="17"/>
-      <c r="C973" s="17"/>
+      <c r="A973" s="13"/>
+      <c r="B973" s="11"/>
+      <c r="C973" s="11"/>
     </row>
     <row r="974" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A974" s="19"/>
-      <c r="B974" s="17"/>
-      <c r="C974" s="17"/>
+      <c r="A974" s="13"/>
+      <c r="B974" s="11"/>
+      <c r="C974" s="11"/>
     </row>
     <row r="975" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A975" s="19"/>
-      <c r="B975" s="17"/>
-      <c r="C975" s="17"/>
+      <c r="A975" s="13"/>
+      <c r="B975" s="11"/>
+      <c r="C975" s="11"/>
     </row>
     <row r="976" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A976" s="19"/>
-      <c r="B976" s="17"/>
-      <c r="C976" s="17"/>
+      <c r="A976" s="13"/>
+      <c r="B976" s="11"/>
+      <c r="C976" s="11"/>
     </row>
     <row r="977" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A977" s="19"/>
-      <c r="B977" s="17"/>
-      <c r="C977" s="17"/>
+      <c r="A977" s="13"/>
+      <c r="B977" s="11"/>
+      <c r="C977" s="11"/>
     </row>
     <row r="978" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A978" s="19"/>
-      <c r="B978" s="17"/>
-      <c r="C978" s="17"/>
+      <c r="A978" s="13"/>
+      <c r="B978" s="11"/>
+      <c r="C978" s="11"/>
     </row>
     <row r="979" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A979" s="19"/>
-      <c r="B979" s="17"/>
-      <c r="C979" s="17"/>
+      <c r="A979" s="13"/>
+      <c r="B979" s="11"/>
+      <c r="C979" s="11"/>
     </row>
     <row r="980" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A980" s="19"/>
-      <c r="B980" s="17"/>
-      <c r="C980" s="17"/>
+      <c r="A980" s="13"/>
+      <c r="B980" s="11"/>
+      <c r="C980" s="11"/>
     </row>
     <row r="981" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A981" s="19"/>
-      <c r="B981" s="17"/>
-      <c r="C981" s="17"/>
+      <c r="A981" s="13"/>
+      <c r="B981" s="11"/>
+      <c r="C981" s="11"/>
     </row>
     <row r="982" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A982" s="19"/>
-      <c r="B982" s="17"/>
-      <c r="C982" s="17"/>
+      <c r="A982" s="13"/>
+      <c r="B982" s="11"/>
+      <c r="C982" s="11"/>
     </row>
     <row r="983" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A983" s="19"/>
-      <c r="B983" s="17"/>
-      <c r="C983" s="17"/>
+      <c r="A983" s="13"/>
+      <c r="B983" s="11"/>
+      <c r="C983" s="11"/>
     </row>
     <row r="984" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A984" s="19"/>
-      <c r="B984" s="17"/>
-      <c r="C984" s="17"/>
+      <c r="A984" s="13"/>
+      <c r="B984" s="11"/>
+      <c r="C984" s="11"/>
     </row>
     <row r="985" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A985" s="19"/>
-      <c r="B985" s="17"/>
-      <c r="C985" s="17"/>
+      <c r="A985" s="13"/>
+      <c r="B985" s="11"/>
+      <c r="C985" s="11"/>
     </row>
     <row r="986" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A986" s="19"/>
-      <c r="B986" s="17"/>
-      <c r="C986" s="17"/>
+      <c r="A986" s="13"/>
+      <c r="B986" s="11"/>
+      <c r="C986" s="11"/>
     </row>
     <row r="987" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A987" s="19"/>
-      <c r="B987" s="17"/>
-      <c r="C987" s="17"/>
+      <c r="A987" s="13"/>
+      <c r="B987" s="11"/>
+      <c r="C987" s="11"/>
     </row>
     <row r="988" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A988" s="19"/>
-      <c r="B988" s="17"/>
-      <c r="C988" s="17"/>
+      <c r="A988" s="13"/>
+      <c r="B988" s="11"/>
+      <c r="C988" s="11"/>
     </row>
     <row r="989" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A989" s="19"/>
-      <c r="B989" s="17"/>
-      <c r="C989" s="17"/>
+      <c r="A989" s="13"/>
+      <c r="B989" s="11"/>
+      <c r="C989" s="11"/>
     </row>
     <row r="990" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A990" s="19"/>
-      <c r="B990" s="17"/>
-      <c r="C990" s="17"/>
+      <c r="A990" s="13"/>
+      <c r="B990" s="11"/>
+      <c r="C990" s="11"/>
     </row>
     <row r="991" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A991" s="19"/>
-      <c r="B991" s="17"/>
-      <c r="C991" s="17"/>
+      <c r="A991" s="13"/>
+      <c r="B991" s="11"/>
+      <c r="C991" s="11"/>
     </row>
     <row r="992" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A992" s="19"/>
-      <c r="B992" s="17"/>
-      <c r="C992" s="17"/>
+      <c r="A992" s="13"/>
+      <c r="B992" s="11"/>
+      <c r="C992" s="11"/>
     </row>
     <row r="993" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A993" s="19"/>
-      <c r="B993" s="17"/>
-      <c r="C993" s="17"/>
+      <c r="A993" s="13"/>
+      <c r="B993" s="11"/>
+      <c r="C993" s="11"/>
     </row>
     <row r="994" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A994" s="19"/>
-      <c r="B994" s="17"/>
-      <c r="C994" s="17"/>
+      <c r="A994" s="13"/>
+      <c r="B994" s="11"/>
+      <c r="C994" s="11"/>
     </row>
     <row r="995" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A995" s="19"/>
-      <c r="B995" s="17"/>
-      <c r="C995" s="17"/>
+      <c r="A995" s="13"/>
+      <c r="B995" s="11"/>
+      <c r="C995" s="11"/>
     </row>
     <row r="996" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A996" s="19"/>
-      <c r="B996" s="17"/>
-      <c r="C996" s="17"/>
+      <c r="A996" s="13"/>
+      <c r="B996" s="11"/>
+      <c r="C996" s="11"/>
     </row>
     <row r="997" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A997" s="19"/>
-      <c r="B997" s="17"/>
-      <c r="C997" s="17"/>
+      <c r="A997" s="13"/>
+      <c r="B997" s="11"/>
+      <c r="C997" s="11"/>
     </row>
     <row r="998" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A998" s="19"/>
-      <c r="B998" s="17"/>
-      <c r="C998" s="17"/>
+      <c r="A998" s="13"/>
+      <c r="B998" s="11"/>
+      <c r="C998" s="11"/>
     </row>
     <row r="999" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A999" s="19"/>
-      <c r="B999" s="17"/>
-      <c r="C999" s="17"/>
+      <c r="A999" s="13"/>
+      <c r="B999" s="11"/>
+      <c r="C999" s="11"/>
     </row>
     <row r="1000" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A1000" s="19"/>
-      <c r="B1000" s="17"/>
-      <c r="C1000" s="17"/>
+      <c r="A1000" s="13"/>
+      <c r="B1000" s="11"/>
+      <c r="C1000" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -7124,74 +7144,81 @@
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="24" t="s">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A3" s="23" t="s">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="15" t="s">
+      <c r="B7" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A8" s="14" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="B8" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="24" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A9" s="16" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="12" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="13" spans="1:2" ht="15.75" customHeight="1"/>
@@ -8190,6 +8217,7 @@
     <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
     <hyperlink ref="B8" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
     <hyperlink ref="B9" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="B10" r:id="rId7" xr:uid="{8D66515C-87A0-8844-8F74-8D5A00AD06AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -8206,18 +8234,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>65</v>
+      <c r="A2" s="16" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A3" s="22" t="s">
-        <v>67</v>
+      <c r="A3" s="16" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.75" customHeight="1"/>

--- a/tests/integration/test_data/mappings_attributions_for_tests.xlsx
+++ b/tests/integration/test_data/mappings_attributions_for_tests.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/amendements-intelligents/tests/integration/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BACA60-9038-5B49-BEE8-F2251AB66127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236BB80D-8312-3740-A4F0-54402370A91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Code et Article" sheetId="1" r:id="rId1"/>
     <sheet name="Mots clés" sheetId="2" r:id="rId2"/>
     <sheet name="Prénom Nom Mail" sheetId="3" r:id="rId3"/>
     <sheet name="Attribution par défaut" sheetId="4" r:id="rId4"/>
+    <sheet name="Acronymes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Code et Article'!$E$1:$E$773</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="337">
   <si>
     <t>Bureau</t>
   </si>
@@ -257,6 +258,792 @@
   <si>
     <t>jmm@sante.gouv.fr</t>
   </si>
+  <si>
+    <t>Acronyme</t>
+  </si>
+  <si>
+    <t>Développement</t>
+  </si>
+  <si>
+    <t>AAH</t>
+  </si>
+  <si>
+    <t>allocation aux adultes handicapés</t>
+  </si>
+  <si>
+    <t>ACCRE</t>
+  </si>
+  <si>
+    <t>aide à la création ou à la reprise d'une entreprise</t>
+  </si>
+  <si>
+    <t>ACS</t>
+  </si>
+  <si>
+    <t>aide au paiement d'une complémentaire santé</t>
+  </si>
+  <si>
+    <t>AEEH</t>
+  </si>
+  <si>
+    <t>allocation d'éducation de l'enfant handicapé</t>
+  </si>
+  <si>
+    <t>AJPE</t>
+  </si>
+  <si>
+    <t>allocation journalière du proche aidant</t>
+  </si>
+  <si>
+    <t>AJPP</t>
+  </si>
+  <si>
+    <t>allocation journalière de présence parentale</t>
+  </si>
+  <si>
+    <t>ALD</t>
+  </si>
+  <si>
+    <t>affection longue durée</t>
+  </si>
+  <si>
+    <t>AME</t>
+  </si>
+  <si>
+    <t>aide médicale d'Etat</t>
+  </si>
+  <si>
+    <t>ANAP</t>
+  </si>
+  <si>
+    <t>agence nationale d'appui à la performance des établissements de santé et médico-sociaux</t>
+  </si>
+  <si>
+    <t>ANGDM</t>
+  </si>
+  <si>
+    <t>agence nationale de garantie des droits des mineurs</t>
+  </si>
+  <si>
+    <t>APL</t>
+  </si>
+  <si>
+    <t>aide personnalisée au logement</t>
+  </si>
+  <si>
+    <t>ASI</t>
+  </si>
+  <si>
+    <t>allocation supplémentaire d'invalidité</t>
+  </si>
+  <si>
+    <t>ASPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allocation de solidarité aux personnes âgées </t>
+  </si>
+  <si>
+    <t>AT/MP</t>
+  </si>
+  <si>
+    <t>acidents du travail - maladies professionnelles</t>
+  </si>
+  <si>
+    <t>ATIH</t>
+  </si>
+  <si>
+    <t>agence technique de l'information sur l'hospitalisation</t>
+  </si>
+  <si>
+    <t>AVA</t>
+  </si>
+  <si>
+    <t>assurance vieillesse des aidants</t>
+  </si>
+  <si>
+    <t>AVPF</t>
+  </si>
+  <si>
+    <t>assurance vieillesse des parents au foyer</t>
+  </si>
+  <si>
+    <t>C2S</t>
+  </si>
+  <si>
+    <t>complémentaire santé solidaire</t>
+  </si>
+  <si>
+    <t>C3S</t>
+  </si>
+  <si>
+    <t>contribution sociale de solidarité des sociétés</t>
+  </si>
+  <si>
+    <t>CADES</t>
+  </si>
+  <si>
+    <t>caisse d'amortissement de la dette sociale</t>
+  </si>
+  <si>
+    <t>CAF</t>
+  </si>
+  <si>
+    <t>caisse d'allocations familiales</t>
+  </si>
+  <si>
+    <t>CAMSP</t>
+  </si>
+  <si>
+    <t>centre d'action médico-sociale précoce</t>
+  </si>
+  <si>
+    <t>CANSSM</t>
+  </si>
+  <si>
+    <t>caisse autonome nationale de la sécurité sociale dans les mines</t>
+  </si>
+  <si>
+    <t>CARMF</t>
+  </si>
+  <si>
+    <t>caisse autonome de retraite des médecins de France</t>
+  </si>
+  <si>
+    <t>CARPIMKO</t>
+  </si>
+  <si>
+    <t>caisse autonome de retraite et de prévoyance des infirmiers, masseurs-kinésithérapeutes, orthophonistes, orthoptistes et pédicures-podologues</t>
+  </si>
+  <si>
+    <t>CARPV</t>
+  </si>
+  <si>
+    <t>caisse autonome de retraite et de prévoyance des vétérinaires</t>
+  </si>
+  <si>
+    <t>CAVAMAC</t>
+  </si>
+  <si>
+    <t>Caisse d’Allocation Vieillesse des Agents Généraux et des Mandataires non-salariés d’Assurance et de Capitalisation</t>
+  </si>
+  <si>
+    <t>CAVEC</t>
+  </si>
+  <si>
+    <t>Caisse d'assurance vieillesse des Experts-Comptables et des Commissaires aux comptes</t>
+  </si>
+  <si>
+    <t>CAVOM</t>
+  </si>
+  <si>
+    <t>caisse d'assurance vieillesse des officiers ministériels</t>
+  </si>
+  <si>
+    <t>CAVP</t>
+  </si>
+  <si>
+    <t>caisse d'assurance vieillesse des pharmaciens</t>
+  </si>
+  <si>
+    <t>CCAM</t>
+  </si>
+  <si>
+    <t>classification commune des actes médicaux</t>
+  </si>
+  <si>
+    <t>CCSF</t>
+  </si>
+  <si>
+    <t>commission des chefs des services financiers</t>
+  </si>
+  <si>
+    <t>CDAPH</t>
+  </si>
+  <si>
+    <t>commission des droits et de l'autonomie des personnes</t>
+  </si>
+  <si>
+    <t>CEPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comité économique des produits de santé </t>
+  </si>
+  <si>
+    <t>CER</t>
+  </si>
+  <si>
+    <t>cumul emploi retraite</t>
+  </si>
+  <si>
+    <t>CFE</t>
+  </si>
+  <si>
+    <t>caisse des français de l'étranger</t>
+  </si>
+  <si>
+    <t>CHM</t>
+  </si>
+  <si>
+    <t>centre hospitalier de Mayotte</t>
+  </si>
+  <si>
+    <t>CIAAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectif inter-associatif des aidants familiaux </t>
+  </si>
+  <si>
+    <t>CICE</t>
+  </si>
+  <si>
+    <t>crédit d'impôt compétitivité emploi</t>
+  </si>
+  <si>
+    <t>CIPAV</t>
+  </si>
+  <si>
+    <t>Caisse Interprofessionnelle de Prévoyance et d'Assurance Vieilless</t>
+  </si>
+  <si>
+    <t>CJUE</t>
+  </si>
+  <si>
+    <t>cour de justice de l'union européenne</t>
+  </si>
+  <si>
+    <t>CMU</t>
+  </si>
+  <si>
+    <t>couverture maladie universelle</t>
+  </si>
+  <si>
+    <t>CMU-C ACS</t>
+  </si>
+  <si>
+    <t>couverture maladie universelle complémentaire</t>
+  </si>
+  <si>
+    <t>CNAV</t>
+  </si>
+  <si>
+    <t>caisse nationale d'assurance vieillesse</t>
+  </si>
+  <si>
+    <t>CNG</t>
+  </si>
+  <si>
+    <t>centre national de gestion</t>
+  </si>
+  <si>
+    <t>CNH</t>
+  </si>
+  <si>
+    <t>commission nationale du handicap</t>
+  </si>
+  <si>
+    <t>CNSA</t>
+  </si>
+  <si>
+    <t>caisse nationale de solidarité pour l'autonomie</t>
+  </si>
+  <si>
+    <t>CNSE</t>
+  </si>
+  <si>
+    <t>centre national de soins à l'étranger</t>
+  </si>
+  <si>
+    <t>COR</t>
+  </si>
+  <si>
+    <t>conseil d'orientation des retraites</t>
+  </si>
+  <si>
+    <t>COREM</t>
+  </si>
+  <si>
+    <t>complément de retraite mutualiste</t>
+  </si>
+  <si>
+    <t>CPRN</t>
+  </si>
+  <si>
+    <t>caisse obligatoire de Prévoyance et de Retraite des Notaires libéraux</t>
+  </si>
+  <si>
+    <t>CRDS</t>
+  </si>
+  <si>
+    <t>contribution pour le remboursement de la dette sociale</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>contribution solidarité autonomie</t>
+  </si>
+  <si>
+    <t>CSG</t>
+  </si>
+  <si>
+    <t>contribution sociale généralisée</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>cotisation subsidiaire maladie</t>
+  </si>
+  <si>
+    <t>CSS</t>
+  </si>
+  <si>
+    <t>code de la sécurité sociale</t>
+  </si>
+  <si>
+    <t>CUMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coopératives d’utilisation de matériel agricole </t>
+  </si>
+  <si>
+    <t>CURPS</t>
+  </si>
+  <si>
+    <t>contribution aux unions régionales des professionnels de santé</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>espace économique européen</t>
+  </si>
+  <si>
+    <t>EHESP</t>
+  </si>
+  <si>
+    <t>école des hautes études en santé publique</t>
+  </si>
+  <si>
+    <t>EHPAD</t>
+  </si>
+  <si>
+    <t>établissement d'hébergement pour personnes âgées dépendantes</t>
+  </si>
+  <si>
+    <t>ESMS</t>
+  </si>
+  <si>
+    <t>établissement ou service médico-social</t>
+  </si>
+  <si>
+    <t>ETP</t>
+  </si>
+  <si>
+    <t>équivalent temps plein</t>
+  </si>
+  <si>
+    <t>FGTI</t>
+  </si>
+  <si>
+    <t>fonds de garantie des victimes de terrorisme et d'autres infractions</t>
+  </si>
+  <si>
+    <t>FHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fédération hospitalière française </t>
+  </si>
+  <si>
+    <t>FIDES</t>
+  </si>
+  <si>
+    <t>facturation individuelle des établissements de santé</t>
+  </si>
+  <si>
+    <t>FIPU</t>
+  </si>
+  <si>
+    <t>fonds d'investissements dans la prévention de l'usure professionnelle</t>
+  </si>
+  <si>
+    <t>FIVA</t>
+  </si>
+  <si>
+    <t>fonds d'indemnisation des victimes de l'amiante</t>
+  </si>
+  <si>
+    <t>FMIS</t>
+  </si>
+  <si>
+    <t>fonds pour la modernisation et l'investissement en santé</t>
+  </si>
+  <si>
+    <t>FONPEL</t>
+  </si>
+  <si>
+    <t>fonds de pension des élus</t>
+  </si>
+  <si>
+    <t>FSV</t>
+  </si>
+  <si>
+    <t>fonds de solidarité vieillesse</t>
+  </si>
+  <si>
+    <t>GAEC</t>
+  </si>
+  <si>
+    <t>groupement agricole d'exploitation en commun </t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>haute autorité de santé</t>
+  </si>
+  <si>
+    <t>HCAAM</t>
+  </si>
+  <si>
+    <t>haut conseil pour l'avenir de l'assurance maladie </t>
+  </si>
+  <si>
+    <t>HCFEA</t>
+  </si>
+  <si>
+    <t>haut conseil de la famille, de l’enfance et de l’âge</t>
+  </si>
+  <si>
+    <t>HCFiPS</t>
+  </si>
+  <si>
+    <t>haut conseil du financement de la protection sociale</t>
+  </si>
+  <si>
+    <t>IJ</t>
+  </si>
+  <si>
+    <t>indemnités journalières</t>
+  </si>
+  <si>
+    <t>IJSS</t>
+  </si>
+  <si>
+    <t>indemnités journalières de sécurité sociale</t>
+  </si>
+  <si>
+    <t>INSEE</t>
+  </si>
+  <si>
+    <t>institut national de la statistique et des études économiques</t>
+  </si>
+  <si>
+    <t>INSERM</t>
+  </si>
+  <si>
+    <t>institut national de la santé et de la recherche médicale</t>
+  </si>
+  <si>
+    <t>LAP</t>
+  </si>
+  <si>
+    <t>liste des actes et prescriptions</t>
+  </si>
+  <si>
+    <t>LFSS</t>
+  </si>
+  <si>
+    <t>loi de financement de la sécurité sociale</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>médecine, chirurgie, obstétrique</t>
+  </si>
+  <si>
+    <t>MDPH</t>
+  </si>
+  <si>
+    <t>maison départementale des personnes handicapées</t>
+  </si>
+  <si>
+    <t>MSA</t>
+  </si>
+  <si>
+    <t>mutualité sociale agricole</t>
+  </si>
+  <si>
+    <t>MTP</t>
+  </si>
+  <si>
+    <t>majoration pour tierce personne</t>
+  </si>
+  <si>
+    <t>NABM</t>
+  </si>
+  <si>
+    <t>nomenclature des actes de biologie médicale</t>
+  </si>
+  <si>
+    <t>NGAP</t>
+  </si>
+  <si>
+    <t>nomenclature générale des actes professionnels</t>
+  </si>
+  <si>
+    <t>OCDE</t>
+  </si>
+  <si>
+    <t>organisation de coopération et de développement économiques</t>
+  </si>
+  <si>
+    <t>OMS</t>
+  </si>
+  <si>
+    <t>organisation mondiale de la santé</t>
+  </si>
+  <si>
+    <t>ONDAM</t>
+  </si>
+  <si>
+    <t>objectif national de dépenses d'assurance maladie</t>
+  </si>
+  <si>
+    <t>OPTAM</t>
+  </si>
+  <si>
+    <t>option tarifaire maîtrisée</t>
+  </si>
+  <si>
+    <t>PADHUE</t>
+  </si>
+  <si>
+    <t>praticiens à diplôme hors UE</t>
+  </si>
+  <si>
+    <t>PAJE</t>
+  </si>
+  <si>
+    <t>prestation d'accueil du jeune enfant</t>
+  </si>
+  <si>
+    <t>PAMC</t>
+  </si>
+  <si>
+    <t>praticien et auxiliaire médical</t>
+  </si>
+  <si>
+    <t>PAP</t>
+  </si>
+  <si>
+    <t>projet annuel de performance</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>plafond annuel de la sécurité sociale</t>
+  </si>
+  <si>
+    <t>PEPS</t>
+  </si>
+  <si>
+    <t>paiement en équipe de professionnels de santé</t>
+  </si>
+  <si>
+    <t>PIB</t>
+  </si>
+  <si>
+    <t>produit intérieur brut</t>
+  </si>
+  <si>
+    <t>PLF</t>
+  </si>
+  <si>
+    <t>projet de loi de finances</t>
+  </si>
+  <si>
+    <t>PLFSS</t>
+  </si>
+  <si>
+    <t>projet de loi de financement de la sécurité sociale</t>
+  </si>
+  <si>
+    <t>PPL</t>
+  </si>
+  <si>
+    <t>proposition de loi</t>
+  </si>
+  <si>
+    <t>PPLO</t>
+  </si>
+  <si>
+    <t>proposition de loi organique</t>
+  </si>
+  <si>
+    <t>PPV</t>
+  </si>
+  <si>
+    <t>prime de partage de la valeur</t>
+  </si>
+  <si>
+    <t>PreParE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prestation partagée d’éducation de l’enfant </t>
+  </si>
+  <si>
+    <t>PREFON</t>
+  </si>
+  <si>
+    <t>caisse nationale de prévoyance de la fonction publique</t>
+  </si>
+  <si>
+    <t>PUMa / PUMA</t>
+  </si>
+  <si>
+    <t>protection universelle maladie</t>
+  </si>
+  <si>
+    <t>QVCT</t>
+  </si>
+  <si>
+    <t>qualité de vie et conditions de travail</t>
+  </si>
+  <si>
+    <t>RGD</t>
+  </si>
+  <si>
+    <t>réduction générale dégressive</t>
+  </si>
+  <si>
+    <t>RIHN</t>
+  </si>
+  <si>
+    <t>référentiel des actes innovants hors nomenclature</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>revenu de solidarité active</t>
+  </si>
+  <si>
+    <t>RSI</t>
+  </si>
+  <si>
+    <t>régime social des indépendants</t>
+  </si>
+  <si>
+    <t>RSPM</t>
+  </si>
+  <si>
+    <t>régime simplifié des professions médicales</t>
+  </si>
+  <si>
+    <t>SDREA</t>
+  </si>
+  <si>
+    <t>schéma directeur régional des exploitations agricoles</t>
+  </si>
+  <si>
+    <t>SAD</t>
+  </si>
+  <si>
+    <t>service autonomie à domicile</t>
+  </si>
+  <si>
+    <t>SMIC</t>
+  </si>
+  <si>
+    <t>salaire minimum interprofessionnel de croissance</t>
+  </si>
+  <si>
+    <t>SNGC</t>
+  </si>
+  <si>
+    <t>syndicat national de gérontologie clinique</t>
+  </si>
+  <si>
+    <t>SSIAD</t>
+  </si>
+  <si>
+    <t>services de soins infirmiers à domicile</t>
+  </si>
+  <si>
+    <t>T2A</t>
+  </si>
+  <si>
+    <t>tarification à l'activité</t>
+  </si>
+  <si>
+    <t>TND</t>
+  </si>
+  <si>
+    <t>troubles du neurodéveloppement</t>
+  </si>
+  <si>
+    <t>TO-DE</t>
+  </si>
+  <si>
+    <t>travailleurs occasionnels demandeurs d’emploi du secteur agricole</t>
+  </si>
+  <si>
+    <t>TPMR</t>
+  </si>
+  <si>
+    <t>transport de personnes à mobilité réduite</t>
+  </si>
+  <si>
+    <t>TPT</t>
+  </si>
+  <si>
+    <t>temps partiel pour raison thérapeutique</t>
+  </si>
+  <si>
+    <t>TSA</t>
+  </si>
+  <si>
+    <t>taxe de solidarité additionnelle</t>
+  </si>
+  <si>
+    <t>TVA</t>
+  </si>
+  <si>
+    <t>taxe sur la valeur ajoutée</t>
+  </si>
+  <si>
+    <t>UE</t>
+  </si>
+  <si>
+    <t>union européenne</t>
+  </si>
+  <si>
+    <t>UNAF</t>
+  </si>
+  <si>
+    <t>union nationale des associations familiales</t>
+  </si>
+  <si>
+    <t>URPS</t>
+  </si>
+  <si>
+    <t>union régionale des professionnels de santé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USLD </t>
+  </si>
+  <si>
+    <t>unités de soins de longue durée</t>
+  </si>
+  <si>
+    <t>VPH</t>
+  </si>
+  <si>
+    <t>véhicules pour personne en situation de handicap</t>
+  </si>
 </sst>
 </file>
 
@@ -266,7 +1053,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="165" formatCode="yyyy\-m"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -344,8 +1131,21 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,6 +1156,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -378,7 +1184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -441,6 +1247,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32245,4 +33056,1066 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E07DC06-BE6F-E74C-AC13-6CDBAAED5E7C}">
+  <dimension ref="A1:B131"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="104.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="B74" s="27" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="B86" s="27" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="B88" s="27" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B95" s="27" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="B96" s="27" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="B97" s="27" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B98" s="27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="B99" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B100" s="27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="B103" s="27" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="B104" s="27" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="27" t="s">
+        <v>291</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B110" s="27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B111" s="27" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="B112" s="27" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="B113" s="27" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="B114" s="27" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="B117" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B120" s="27" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B121" s="27" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="B122" s="27" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B123" s="27" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B128" s="27" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="27" t="s">
+        <v>331</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="27" t="s">
+        <v>333</v>
+      </c>
+      <c r="B130" s="27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/integration/test_data/mappings_attributions_for_tests.xlsx
+++ b/tests/integration/test_data/mappings_attributions_for_tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/amendements-intelligents/tests/integration/test_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/graal/tests/integration/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236BB80D-8312-3740-A4F0-54402370A91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE632D3-FA68-344C-AB70-2A63035DBCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Code et Article" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="342">
   <si>
     <t>Bureau</t>
   </si>
@@ -1044,6 +1044,21 @@
   <si>
     <t>véhicules pour personne en situation de handicap</t>
   </si>
+  <si>
+    <t>Entité pilote</t>
+  </si>
+  <si>
+    <t>MABC</t>
+  </si>
+  <si>
+    <t>NABC</t>
+  </si>
+  <si>
+    <t>JABC</t>
+  </si>
+  <si>
+    <t>EABC</t>
+  </si>
 </sst>
 </file>
 
@@ -30940,7 +30955,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B1000"/>
+  <dimension ref="A1:C999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.1640625" customWidth="1"/>
@@ -30948,92 +30963,112 @@
     <col min="3" max="26" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
       <c r="A2" s="21" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
       <c r="A3" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1">
       <c r="A4" s="21" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1">
       <c r="A5" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="C6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A7" s="17" t="s">
         <v>70</v>
       </c>
+      <c r="B7" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A8" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="B8" s="22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A9" s="23" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A9" s="24" t="s">
+        <v>60</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A10" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="22" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="12" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1"/>
+      <c r="C9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -32017,16 +32052,15 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
     <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="B9" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="B10" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/tests/integration/test_data/mappings_attributions_for_tests.xlsx
+++ b/tests/integration/test_data/mappings_attributions_for_tests.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Vidy/code/dnum/graal/tests/integration/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE632D3-FA68-344C-AB70-2A63035DBCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7DB789-95B7-724C-A485-307EEAA8B036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="346">
   <si>
     <t>Bureau</t>
   </si>
@@ -1045,9 +1045,6 @@
     <t>véhicules pour personne en situation de handicap</t>
   </si>
   <si>
-    <t>Entité pilote</t>
-  </si>
-  <si>
     <t>MABC</t>
   </si>
   <si>
@@ -1058,6 +1055,21 @@
   </si>
   <si>
     <t>EABC</t>
+  </si>
+  <si>
+    <t>Entité Pilote</t>
+  </si>
+  <si>
+    <t>Charlotte Legresy</t>
+  </si>
+  <si>
+    <t>établissement français du sang</t>
+  </si>
+  <si>
+    <t>charlotte.legresy@sante.gouv.fr</t>
+  </si>
+  <si>
+    <t>CABC</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1080,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="165" formatCode="yyyy\-m"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1124,21 +1136,9 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1157,6 +1157,26 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1196,10 +1216,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1255,20 +1276,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3200,8 +3232,12 @@
       <c r="Z9" s="13"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" s="15"/>
+      <c r="A10" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>342</v>
+      </c>
       <c r="C10" s="15"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -30964,105 +31000,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="28" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A2" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="29" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A4" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A3" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A5" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A7" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A8" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="29" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A4" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A5" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A9" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A10" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>345</v>
+      </c>
+    </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="12" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="13" spans="1:3" ht="15.75" customHeight="1"/>
@@ -32061,6 +32107,7 @@
     <hyperlink ref="B7" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
     <hyperlink ref="B8" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
     <hyperlink ref="B9" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{CFDE7F7F-C31D-A24F-BFF6-DB7DD59714EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -32077,17 +32124,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" customHeight="1">
-      <c r="A3" s="23"/>
+      <c r="A3" s="21"/>
     </row>
     <row r="4" spans="1:1" ht="15.75" customHeight="1"/>
     <row r="5" spans="1:1" ht="15.75" customHeight="1"/>
@@ -33102,1050 +33149,1050 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="24" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="24" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="24" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="24" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="24" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="24" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="24" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="24" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="24" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="24" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="24" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="24" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="24" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="24" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="24" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="24" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="24" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="24" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="24" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="24" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="24" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="24" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="24" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="24" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="24" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="24" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="24" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="24" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="27" t="s">
+      <c r="A33" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="24" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="24" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="27" t="s">
+      <c r="A35" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="24" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="24" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="24" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="27" t="s">
+      <c r="A38" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="24" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="24" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="24" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="24" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="24" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="24" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="24" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="27" t="s">
+      <c r="A45" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="24" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="24" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="24" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="24" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="24" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="24" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="24" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="24" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="24" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="24" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="24" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="24" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="24" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="24" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="24" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="24" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="24" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="27" t="s">
+      <c r="A62" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="24" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="24" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="24" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="24" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="24" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="24" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="27" t="s">
+      <c r="A68" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="24" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="24" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="24" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="24" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="24" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="27" t="s">
+      <c r="A73" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="24" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="27" t="s">
+      <c r="A74" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="24" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="27" t="s">
+      <c r="A75" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="24" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="27" t="s">
+      <c r="A76" s="24" t="s">
         <v>225</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="24" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="27" t="s">
+      <c r="A77" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="24" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="27" t="s">
+      <c r="A78" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="B78" s="27" t="s">
+      <c r="B78" s="24" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="27" t="s">
+      <c r="A79" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="24" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="27" t="s">
+      <c r="A80" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="24" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="24" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="27" t="s">
+      <c r="A82" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="B82" s="27" t="s">
+      <c r="B82" s="24" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="27" t="s">
+      <c r="A83" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="24" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="27" t="s">
+      <c r="A84" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="24" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="27" t="s">
+      <c r="A85" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="24" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="27" t="s">
+      <c r="A86" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="24" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="27" t="s">
+      <c r="A87" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="24" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="27" t="s">
+      <c r="A88" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="24" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="27" t="s">
+      <c r="A89" s="24" t="s">
         <v>251</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="24" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="27" t="s">
+      <c r="A90" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="24" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="27" t="s">
+      <c r="A91" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="24" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="27" t="s">
+      <c r="A92" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="24" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="27" t="s">
+      <c r="A93" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="B93" s="27" t="s">
+      <c r="B93" s="24" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="27" t="s">
+      <c r="A94" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="B94" s="27" t="s">
+      <c r="B94" s="24" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="27" t="s">
+      <c r="A95" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="B95" s="27" t="s">
+      <c r="B95" s="24" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="27" t="s">
+      <c r="A96" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="B96" s="27" t="s">
+      <c r="B96" s="24" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="27" t="s">
+      <c r="A97" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="B97" s="27" t="s">
+      <c r="B97" s="24" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="27" t="s">
+      <c r="A98" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="B98" s="27" t="s">
+      <c r="B98" s="24" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="27" t="s">
+      <c r="A99" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="24" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="27" t="s">
+      <c r="A100" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B100" s="24" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="27" t="s">
+      <c r="A101" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="B101" s="27" t="s">
+      <c r="B101" s="24" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="27" t="s">
+      <c r="A102" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="24" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="27" t="s">
+      <c r="A103" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="B103" s="27" t="s">
+      <c r="B103" s="24" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="27" t="s">
+      <c r="A104" s="24" t="s">
         <v>281</v>
       </c>
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="24" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="27" t="s">
+      <c r="A105" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="24" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="27" t="s">
+      <c r="A106" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B106" s="24" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="27" t="s">
+      <c r="A107" s="24" t="s">
         <v>287</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="24" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="27" t="s">
+      <c r="A108" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="24" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="27" t="s">
+      <c r="A109" s="24" t="s">
         <v>291</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="24" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="27" t="s">
+      <c r="A110" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="24" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="27" t="s">
+      <c r="A111" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="24" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="27" t="s">
+      <c r="A112" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="24" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="27" t="s">
+      <c r="A113" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="24" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="27" t="s">
+      <c r="A114" s="24" t="s">
         <v>301</v>
       </c>
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="24" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="27" t="s">
+      <c r="A115" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="B115" s="27" t="s">
+      <c r="B115" s="24" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="27" t="s">
+      <c r="A116" s="24" t="s">
         <v>305</v>
       </c>
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="24" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="27" t="s">
+      <c r="A117" s="24" t="s">
         <v>307</v>
       </c>
-      <c r="B117" s="27" t="s">
+      <c r="B117" s="24" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="27" t="s">
+      <c r="A118" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="B118" s="27" t="s">
+      <c r="B118" s="24" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="27" t="s">
+      <c r="A119" s="24" t="s">
         <v>311</v>
       </c>
-      <c r="B119" s="27" t="s">
+      <c r="B119" s="24" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="27" t="s">
+      <c r="A120" s="24" t="s">
         <v>313</v>
       </c>
-      <c r="B120" s="27" t="s">
+      <c r="B120" s="24" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="27" t="s">
+      <c r="A121" s="24" t="s">
         <v>315</v>
       </c>
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="24" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="27" t="s">
+      <c r="A122" s="24" t="s">
         <v>317</v>
       </c>
-      <c r="B122" s="27" t="s">
+      <c r="B122" s="24" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="27" t="s">
+      <c r="A123" s="24" t="s">
         <v>319</v>
       </c>
-      <c r="B123" s="27" t="s">
+      <c r="B123" s="24" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="27" t="s">
+      <c r="A124" s="24" t="s">
         <v>321</v>
       </c>
-      <c r="B124" s="27" t="s">
+      <c r="B124" s="24" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="27" t="s">
+      <c r="A125" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="B125" s="27" t="s">
+      <c r="B125" s="24" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="27" t="s">
+      <c r="A126" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="24" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="27" t="s">
+      <c r="A127" s="24" t="s">
         <v>327</v>
       </c>
-      <c r="B127" s="27" t="s">
+      <c r="B127" s="24" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="27" t="s">
+      <c r="A128" s="24" t="s">
         <v>329</v>
       </c>
-      <c r="B128" s="27" t="s">
+      <c r="B128" s="24" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="27" t="s">
+      <c r="A129" s="24" t="s">
         <v>331</v>
       </c>
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="24" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="27" t="s">
+      <c r="A130" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="24" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="27" t="s">
+      <c r="A131" s="24" t="s">
         <v>335</v>
       </c>
-      <c r="B131" s="27" t="s">
+      <c r="B131" s="24" t="s">
         <v>336</v>
       </c>
     </row>
